--- a/2024C/data/result1_1.xlsx
+++ b/2024C/data/result1_1.xlsx
@@ -1625,7 +1625,9 @@
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n"/>
-      <c r="H18" s="8" t="n"/>
+      <c r="H18" s="8" t="n">
+        <v>11.539</v>
+      </c>
       <c r="I18" s="8" t="n"/>
       <c r="J18" s="8" t="n">
         <v>22.895</v>
@@ -1635,7 +1637,9 @@
       </c>
       <c r="L18" s="8" t="n"/>
       <c r="M18" s="8" t="n"/>
-      <c r="N18" s="8" t="n"/>
+      <c r="N18" s="8" t="n">
+        <v>12.316</v>
+      </c>
       <c r="O18" s="8" t="n"/>
       <c r="P18" s="8" t="n"/>
       <c r="Q18" s="8" t="n"/>
@@ -1791,7 +1795,9 @@
         <v>5.286</v>
       </c>
       <c r="N21" s="9" t="n"/>
-      <c r="O21" s="9" t="n"/>
+      <c r="O21" s="9" t="n">
+        <v>0.593</v>
+      </c>
       <c r="P21" s="9" t="n"/>
       <c r="Q21" s="9" t="n"/>
       <c r="R21" s="9" t="n"/>
@@ -1834,17 +1840,21 @@
       <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
-      <c r="I22" s="8" t="n"/>
+      <c r="I22" s="8" t="n">
+        <v>10.056</v>
+      </c>
       <c r="J22" s="8" t="n"/>
       <c r="K22" s="8" t="n"/>
       <c r="L22" s="8" t="n"/>
       <c r="M22" s="8" t="n"/>
-      <c r="N22" s="8" t="n">
-        <v>15</v>
-      </c>
-      <c r="O22" s="8" t="n"/>
+      <c r="N22" s="8" t="n"/>
+      <c r="O22" s="8" t="n">
+        <v>1.797</v>
+      </c>
       <c r="P22" s="8" t="n"/>
-      <c r="Q22" s="8" t="n"/>
+      <c r="Q22" s="8" t="n">
+        <v>3.147</v>
+      </c>
       <c r="R22" s="8" t="n"/>
       <c r="S22" s="8" t="n"/>
       <c r="T22" s="8" t="n"/>
@@ -1885,9 +1895,7 @@
       <c r="F23" s="9" t="n"/>
       <c r="G23" s="9" t="n"/>
       <c r="H23" s="9" t="n"/>
-      <c r="I23" s="9" t="n">
-        <v>13</v>
-      </c>
+      <c r="I23" s="9" t="n"/>
       <c r="J23" s="9" t="n"/>
       <c r="K23" s="9" t="n"/>
       <c r="L23" s="9" t="n"/>
@@ -1895,7 +1903,9 @@
       <c r="N23" s="9" t="n"/>
       <c r="O23" s="9" t="n"/>
       <c r="P23" s="9" t="n"/>
-      <c r="Q23" s="9" t="n"/>
+      <c r="Q23" s="9" t="n">
+        <v>13</v>
+      </c>
       <c r="R23" s="9" t="n"/>
       <c r="S23" s="9" t="n"/>
       <c r="T23" s="9" t="n"/>
@@ -1937,7 +1947,9 @@
       </c>
       <c r="F24" s="8" t="n"/>
       <c r="G24" s="8" t="n"/>
-      <c r="H24" s="8" t="n"/>
+      <c r="H24" s="8" t="n">
+        <v>0.931</v>
+      </c>
       <c r="I24" s="8" t="n"/>
       <c r="J24" s="8" t="n"/>
       <c r="K24" s="8" t="n"/>
@@ -1983,14 +1995,14 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="C25" s="9" t="n"/>
+      <c r="C25" s="9" t="n">
+        <v>18</v>
+      </c>
       <c r="D25" s="9" t="n"/>
       <c r="E25" s="9" t="n"/>
       <c r="F25" s="9" t="n"/>
       <c r="G25" s="9" t="n"/>
-      <c r="H25" s="9" t="n">
-        <v>18</v>
-      </c>
+      <c r="H25" s="9" t="n"/>
       <c r="I25" s="9" t="n"/>
       <c r="J25" s="9" t="n"/>
       <c r="K25" s="9" t="n"/>
@@ -2320,7 +2332,9 @@
       <c r="Y31" s="9" t="n"/>
       <c r="Z31" s="9" t="n"/>
       <c r="AA31" s="9" t="n"/>
-      <c r="AB31" s="9" t="n"/>
+      <c r="AB31" s="9" t="n">
+        <v>0.43</v>
+      </c>
       <c r="AC31" s="9" t="n"/>
       <c r="AD31" s="9" t="n"/>
       <c r="AE31" s="9" t="n"/>
@@ -2328,7 +2342,9 @@
       <c r="AG31" s="9" t="n"/>
       <c r="AH31" s="9" t="n"/>
       <c r="AI31" s="9" t="n"/>
-      <c r="AJ31" s="9" t="n"/>
+      <c r="AJ31" s="9" t="n">
+        <v>0.038</v>
+      </c>
       <c r="AK31" s="9" t="n"/>
       <c r="AL31" s="9" t="n"/>
       <c r="AM31" s="9" t="n"/>
@@ -2422,8 +2438,12 @@
       <c r="W33" s="9" t="n"/>
       <c r="X33" s="9" t="n"/>
       <c r="Y33" s="9" t="n"/>
-      <c r="Z33" s="9" t="n"/>
-      <c r="AA33" s="9" t="n"/>
+      <c r="Z33" s="9" t="n">
+        <v>1.088</v>
+      </c>
+      <c r="AA33" s="9" t="n">
+        <v>1.091</v>
+      </c>
       <c r="AB33" s="9" t="n"/>
       <c r="AC33" s="9" t="n"/>
       <c r="AD33" s="9" t="n"/>
@@ -2463,26 +2483,32 @@
       <c r="O34" s="8" t="n"/>
       <c r="P34" s="8" t="n"/>
       <c r="Q34" s="8" t="n"/>
-      <c r="R34" s="8" t="n">
-        <v>22</v>
-      </c>
+      <c r="R34" s="8" t="n"/>
       <c r="S34" s="8" t="n"/>
       <c r="T34" s="8" t="n"/>
       <c r="U34" s="8" t="n"/>
       <c r="V34" s="8" t="n"/>
       <c r="W34" s="8" t="n"/>
-      <c r="X34" s="8" t="n"/>
+      <c r="X34" s="8" t="n">
+        <v>0.3</v>
+      </c>
       <c r="Y34" s="8" t="n"/>
       <c r="Z34" s="8" t="n"/>
       <c r="AA34" s="8" t="n"/>
       <c r="AB34" s="8" t="n"/>
-      <c r="AC34" s="8" t="n"/>
+      <c r="AC34" s="8" t="n">
+        <v>0.439</v>
+      </c>
       <c r="AD34" s="8" t="n"/>
       <c r="AE34" s="8" t="n"/>
       <c r="AF34" s="8" t="n"/>
-      <c r="AG34" s="8" t="n"/>
+      <c r="AG34" s="8" t="n">
+        <v>0.75</v>
+      </c>
       <c r="AH34" s="8" t="n"/>
-      <c r="AI34" s="8" t="n"/>
+      <c r="AI34" s="8" t="n">
+        <v>0.36</v>
+      </c>
       <c r="AJ34" s="8" t="n"/>
       <c r="AK34" s="8" t="n"/>
       <c r="AL34" s="8" t="n"/>
@@ -2514,16 +2540,16 @@
       <c r="O35" s="9" t="n"/>
       <c r="P35" s="9" t="n"/>
       <c r="Q35" s="9" t="n"/>
-      <c r="R35" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="R35" s="9" t="n"/>
       <c r="S35" s="9" t="n"/>
       <c r="T35" s="9" t="n"/>
       <c r="U35" s="9" t="n"/>
       <c r="V35" s="9" t="n"/>
       <c r="W35" s="9" t="n"/>
       <c r="X35" s="9" t="n"/>
-      <c r="Y35" s="9" t="n"/>
+      <c r="Y35" s="9" t="n">
+        <v>0.333</v>
+      </c>
       <c r="Z35" s="9" t="n"/>
       <c r="AA35" s="9" t="n"/>
       <c r="AB35" s="9" t="n"/>
@@ -2534,7 +2560,9 @@
       <c r="AG35" s="9" t="n"/>
       <c r="AH35" s="9" t="n"/>
       <c r="AI35" s="9" t="n"/>
-      <c r="AJ35" s="9" t="n"/>
+      <c r="AJ35" s="9" t="n">
+        <v>0.29</v>
+      </c>
       <c r="AK35" s="9" t="n"/>
       <c r="AL35" s="9" t="n"/>
       <c r="AM35" s="9" t="n"/>
@@ -2622,7 +2650,9 @@
       <c r="U37" s="9" t="n"/>
       <c r="V37" s="9" t="n"/>
       <c r="W37" s="9" t="n"/>
-      <c r="X37" s="9" t="n"/>
+      <c r="X37" s="9" t="n">
+        <v>0.03</v>
+      </c>
       <c r="Y37" s="9" t="n"/>
       <c r="Z37" s="9" t="n"/>
       <c r="AA37" s="9" t="n"/>
@@ -3915,7 +3945,9 @@
       <c r="AJ62" s="8" t="n"/>
       <c r="AK62" s="8" t="n"/>
       <c r="AL62" s="8" t="n"/>
-      <c r="AM62" s="8" t="n"/>
+      <c r="AM62" s="8" t="n">
+        <v>6</v>
+      </c>
       <c r="AN62" s="8" t="n"/>
       <c r="AO62" s="8" t="n"/>
       <c r="AP62" s="8" t="n"/>
@@ -3962,7 +3994,9 @@
       <c r="AI63" s="9" t="n"/>
       <c r="AJ63" s="9" t="n"/>
       <c r="AK63" s="9" t="n"/>
-      <c r="AL63" s="9" t="n"/>
+      <c r="AL63" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="AM63" s="9" t="n"/>
       <c r="AN63" s="9" t="n"/>
       <c r="AO63" s="9" t="n"/>
@@ -4946,15 +4980,15 @@
       <c r="U83" s="9" t="n"/>
       <c r="V83" s="9" t="n"/>
       <c r="W83" s="9" t="n"/>
-      <c r="X83" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="X83" s="9" t="n"/>
       <c r="Y83" s="9" t="n"/>
       <c r="Z83" s="9" t="n"/>
       <c r="AA83" s="9" t="n"/>
       <c r="AB83" s="9" t="n"/>
       <c r="AC83" s="9" t="n"/>
-      <c r="AD83" s="9" t="n"/>
+      <c r="AD83" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AE83" s="9" t="n"/>
       <c r="AF83" s="9" t="n"/>
       <c r="AG83" s="9" t="n"/>
@@ -5341,11 +5375,11 @@
         </is>
       </c>
       <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="n">
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="8" t="n"/>
+      <c r="F2" s="8" t="n">
         <v>80</v>
       </c>
-      <c r="E2" s="8" t="n"/>
-      <c r="F2" s="8" t="n"/>
       <c r="G2" s="8" t="n"/>
       <c r="H2" s="8" t="n"/>
       <c r="I2" s="8" t="n"/>
@@ -5400,13 +5434,13 @@
       <c r="I3" s="9" t="n"/>
       <c r="J3" s="9" t="n"/>
       <c r="K3" s="9" t="n">
-        <v>47.082</v>
+        <v>47.17</v>
       </c>
       <c r="L3" s="9" t="n"/>
       <c r="M3" s="9" t="n"/>
       <c r="N3" s="9" t="n"/>
       <c r="O3" s="9" t="n">
-        <v>7.918</v>
+        <v>7.83</v>
       </c>
       <c r="P3" s="9" t="n"/>
       <c r="Q3" s="9" t="n"/>
@@ -5444,14 +5478,12 @@
           <t>A3</t>
         </is>
       </c>
-      <c r="C4" s="8" t="n">
-        <v>1.263</v>
-      </c>
-      <c r="D4" s="8" t="n">
-        <v>31.481</v>
-      </c>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="8" t="n"/>
       <c r="E4" s="8" t="n"/>
-      <c r="F4" s="8" t="n"/>
+      <c r="F4" s="8" t="n">
+        <v>35</v>
+      </c>
       <c r="G4" s="8" t="n"/>
       <c r="H4" s="8" t="n"/>
       <c r="I4" s="8" t="n"/>
@@ -5551,7 +5583,7 @@
       <c r="C6" s="8" t="n"/>
       <c r="D6" s="8" t="n"/>
       <c r="E6" s="8" t="n">
-        <v>51.341</v>
+        <v>50.488</v>
       </c>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="n"/>
@@ -5561,7 +5593,7 @@
       <c r="K6" s="8" t="n"/>
       <c r="L6" s="8" t="n"/>
       <c r="M6" s="8" t="n">
-        <v>16.659</v>
+        <v>8.09</v>
       </c>
       <c r="N6" s="8" t="n"/>
       <c r="O6" s="8" t="n"/>
@@ -5606,10 +5638,10 @@
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="9" t="n"/>
       <c r="G7" s="9" t="n"/>
-      <c r="H7" s="9" t="n"/>
-      <c r="I7" s="9" t="n">
+      <c r="H7" s="9" t="n">
         <v>55</v>
       </c>
+      <c r="I7" s="9" t="n"/>
       <c r="J7" s="9" t="n"/>
       <c r="K7" s="9" t="n"/>
       <c r="L7" s="9" t="n"/>
@@ -5653,14 +5685,14 @@
         </is>
       </c>
       <c r="C8" s="8" t="n"/>
-      <c r="D8" s="8" t="n"/>
-      <c r="E8" s="8" t="n">
-        <v>12.141</v>
-      </c>
+      <c r="D8" s="8" t="n">
+        <v>30.193</v>
+      </c>
+      <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
       <c r="H8" s="8" t="n">
-        <v>47.859</v>
+        <v>29.807</v>
       </c>
       <c r="I8" s="8" t="n"/>
       <c r="J8" s="8" t="n"/>
@@ -5705,15 +5737,13 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n">
-        <v>2.927</v>
-      </c>
+      <c r="C9" s="9" t="n"/>
       <c r="D9" s="9" t="n"/>
       <c r="E9" s="9" t="n"/>
       <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="n"/>
       <c r="H9" s="9" t="n">
-        <v>42.582</v>
+        <v>46</v>
       </c>
       <c r="I9" s="9" t="n"/>
       <c r="J9" s="9" t="n"/>
@@ -5758,18 +5788,16 @@
           <t>B3</t>
         </is>
       </c>
-      <c r="C10" s="8" t="n">
-        <v>7.378</v>
-      </c>
+      <c r="C10" s="8" t="n"/>
       <c r="D10" s="8" t="n"/>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
       <c r="H10" s="8" t="n"/>
-      <c r="I10" s="8" t="n"/>
-      <c r="J10" s="8" t="n">
-        <v>32.622</v>
-      </c>
+      <c r="I10" s="8" t="n">
+        <v>40</v>
+      </c>
+      <c r="J10" s="8" t="n"/>
       <c r="K10" s="8" t="n"/>
       <c r="L10" s="8" t="n"/>
       <c r="M10" s="8" t="n"/>
@@ -5811,15 +5839,13 @@
           <t>B4</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n">
-        <v>1.516</v>
-      </c>
+      <c r="C11" s="9" t="n"/>
       <c r="D11" s="9" t="n"/>
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="9" t="n"/>
       <c r="H11" s="9" t="n">
-        <v>26.304</v>
+        <v>28</v>
       </c>
       <c r="I11" s="9" t="n"/>
       <c r="J11" s="9" t="n"/>
@@ -5864,19 +5890,19 @@
           <t>B5</t>
         </is>
       </c>
-      <c r="C12" s="8" t="n">
-        <v>1.798</v>
-      </c>
+      <c r="C12" s="8" t="n"/>
       <c r="D12" s="8" t="n"/>
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n"/>
       <c r="H12" s="8" t="n"/>
-      <c r="I12" s="8" t="n"/>
+      <c r="I12" s="8" t="n">
+        <v>1.428</v>
+      </c>
       <c r="J12" s="8" t="n"/>
       <c r="K12" s="8" t="n"/>
       <c r="L12" s="8" t="n">
-        <v>23.202</v>
+        <v>22.857</v>
       </c>
       <c r="M12" s="8" t="n"/>
       <c r="N12" s="8" t="n"/>
@@ -5922,11 +5948,11 @@
       <c r="E13" s="9" t="n"/>
       <c r="F13" s="9" t="n"/>
       <c r="G13" s="9" t="n"/>
-      <c r="H13" s="9" t="n">
+      <c r="H13" s="9" t="n"/>
+      <c r="I13" s="9" t="n"/>
+      <c r="J13" s="9" t="n">
         <v>86</v>
       </c>
-      <c r="I13" s="9" t="n"/>
-      <c r="J13" s="9" t="n"/>
       <c r="K13" s="9" t="n"/>
       <c r="L13" s="9" t="n"/>
       <c r="M13" s="9" t="n"/>
@@ -5972,7 +5998,7 @@
       <c r="D14" s="8" t="n"/>
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n">
-        <v>54.057</v>
+        <v>55</v>
       </c>
       <c r="G14" s="8" t="n"/>
       <c r="H14" s="8" t="n"/>
@@ -6021,14 +6047,18 @@
       </c>
       <c r="C15" s="9" t="n"/>
       <c r="D15" s="9" t="n">
-        <v>44</v>
+        <v>22.604</v>
       </c>
       <c r="E15" s="9" t="n"/>
       <c r="F15" s="9" t="n"/>
       <c r="G15" s="9" t="n"/>
       <c r="H15" s="9" t="n"/>
-      <c r="I15" s="9" t="n"/>
-      <c r="J15" s="9" t="n"/>
+      <c r="I15" s="9" t="n">
+        <v>1.171</v>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>20.225</v>
+      </c>
       <c r="K15" s="9" t="n"/>
       <c r="L15" s="9" t="n"/>
       <c r="M15" s="9" t="n"/>
@@ -6071,13 +6101,17 @@
         </is>
       </c>
       <c r="C16" s="8" t="n"/>
-      <c r="D16" s="8" t="n"/>
+      <c r="D16" s="8" t="n">
+        <v>17.009</v>
+      </c>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n">
-        <v>43.987</v>
+        <v>17.009</v>
       </c>
       <c r="G16" s="8" t="n"/>
-      <c r="H16" s="8" t="n"/>
+      <c r="H16" s="8" t="n">
+        <v>13.834</v>
+      </c>
       <c r="I16" s="8" t="n"/>
       <c r="J16" s="8" t="n"/>
       <c r="K16" s="8" t="n"/>
@@ -6085,7 +6119,7 @@
       <c r="M16" s="8" t="n"/>
       <c r="N16" s="8" t="n"/>
       <c r="O16" s="8" t="n">
-        <v>6.013</v>
+        <v>2.149</v>
       </c>
       <c r="P16" s="8" t="n"/>
       <c r="Q16" s="8" t="n"/>
@@ -6175,13 +6209,15 @@
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>37.359</v>
-      </c>
-      <c r="D18" s="8" t="n"/>
+        <v>27.286</v>
+      </c>
+      <c r="D18" s="8" t="n">
+        <v>4.299</v>
+      </c>
       <c r="E18" s="8" t="n"/>
       <c r="F18" s="8" t="n"/>
       <c r="G18" s="8" t="n">
-        <v>22.641</v>
+        <v>28.415</v>
       </c>
       <c r="H18" s="8" t="n"/>
       <c r="I18" s="8" t="n"/>
@@ -6284,17 +6320,19 @@
       <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
       <c r="H20" s="8" t="n"/>
-      <c r="I20" s="8" t="n"/>
-      <c r="J20" s="8" t="n">
-        <v>35</v>
-      </c>
+      <c r="I20" s="8" t="n">
+        <v>16.114</v>
+      </c>
+      <c r="J20" s="8" t="n"/>
       <c r="K20" s="8" t="n"/>
       <c r="L20" s="8" t="n"/>
       <c r="M20" s="8" t="n"/>
       <c r="N20" s="8" t="n"/>
       <c r="O20" s="8" t="n"/>
       <c r="P20" s="8" t="n"/>
-      <c r="Q20" s="8" t="n"/>
+      <c r="Q20" s="8" t="n">
+        <v>18.886</v>
+      </c>
       <c r="R20" s="8" t="n"/>
       <c r="S20" s="8" t="n"/>
       <c r="T20" s="8" t="n"/>
@@ -6334,11 +6372,11 @@
       <c r="E21" s="9" t="n"/>
       <c r="F21" s="9" t="n"/>
       <c r="G21" s="9" t="n"/>
-      <c r="H21" s="9" t="n"/>
+      <c r="H21" s="9" t="n">
+        <v>20</v>
+      </c>
       <c r="I21" s="9" t="n"/>
-      <c r="J21" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="J21" s="9" t="n"/>
       <c r="K21" s="9" t="n"/>
       <c r="L21" s="9" t="n"/>
       <c r="M21" s="9" t="n"/>
@@ -6380,19 +6418,25 @@
           <t>C1</t>
         </is>
       </c>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="n"/>
-      <c r="E22" s="8" t="n">
-        <v>15</v>
-      </c>
+      <c r="C22" s="8" t="n">
+        <v>4.514</v>
+      </c>
+      <c r="D22" s="8" t="n">
+        <v>4.514</v>
+      </c>
+      <c r="E22" s="8" t="n"/>
       <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
-      <c r="H22" s="8" t="n"/>
+      <c r="H22" s="8" t="n">
+        <v>2.706</v>
+      </c>
       <c r="I22" s="8" t="n"/>
       <c r="J22" s="8" t="n"/>
       <c r="K22" s="8" t="n"/>
       <c r="L22" s="8" t="n"/>
-      <c r="M22" s="8" t="n"/>
+      <c r="M22" s="8" t="n">
+        <v>3.265</v>
+      </c>
       <c r="N22" s="8" t="n"/>
       <c r="O22" s="8" t="n"/>
       <c r="P22" s="8" t="n"/>
@@ -6431,11 +6475,11 @@
           <t>C2</t>
         </is>
       </c>
-      <c r="C23" s="9" t="n">
-        <v>9.300000000000001</v>
-      </c>
+      <c r="C23" s="9" t="n"/>
       <c r="D23" s="9" t="n"/>
-      <c r="E23" s="9" t="n"/>
+      <c r="E23" s="9" t="n">
+        <v>13</v>
+      </c>
       <c r="F23" s="9" t="n"/>
       <c r="G23" s="9" t="n"/>
       <c r="H23" s="9" t="n"/>
@@ -6493,10 +6537,10 @@
       <c r="K24" s="8" t="n"/>
       <c r="L24" s="8" t="n"/>
       <c r="M24" s="8" t="n"/>
-      <c r="N24" s="8" t="n">
+      <c r="N24" s="8" t="n"/>
+      <c r="O24" s="8" t="n">
         <v>15</v>
       </c>
-      <c r="O24" s="8" t="n"/>
       <c r="P24" s="8" t="n"/>
       <c r="Q24" s="8" t="n"/>
       <c r="R24" s="8" t="n"/>
@@ -6534,21 +6578,21 @@
         </is>
       </c>
       <c r="C25" s="9" t="n"/>
-      <c r="D25" s="9" t="n">
-        <v>5.956</v>
-      </c>
+      <c r="D25" s="9" t="n"/>
       <c r="E25" s="9" t="n"/>
       <c r="F25" s="9" t="n"/>
       <c r="G25" s="9" t="n"/>
       <c r="H25" s="9" t="n"/>
       <c r="I25" s="9" t="n">
-        <v>4.363</v>
+        <v>2.3</v>
       </c>
       <c r="J25" s="9" t="n"/>
       <c r="K25" s="9" t="n"/>
       <c r="L25" s="9" t="n"/>
       <c r="M25" s="9" t="n"/>
-      <c r="N25" s="9" t="n"/>
+      <c r="N25" s="9" t="n">
+        <v>10.561</v>
+      </c>
       <c r="O25" s="9" t="n"/>
       <c r="P25" s="9" t="n"/>
       <c r="Q25" s="9" t="n"/>
@@ -6642,17 +6686,19 @@
       <c r="E27" s="9" t="n"/>
       <c r="F27" s="9" t="n"/>
       <c r="G27" s="9" t="n"/>
-      <c r="H27" s="9" t="n"/>
+      <c r="H27" s="9" t="n">
+        <v>5.458</v>
+      </c>
       <c r="I27" s="9" t="n"/>
-      <c r="J27" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="J27" s="9" t="n"/>
       <c r="K27" s="9" t="n"/>
       <c r="L27" s="9" t="n"/>
       <c r="M27" s="9" t="n"/>
       <c r="N27" s="9" t="n"/>
       <c r="O27" s="9" t="n"/>
-      <c r="P27" s="9" t="n"/>
+      <c r="P27" s="9" t="n">
+        <v>14.542</v>
+      </c>
       <c r="Q27" s="9" t="n"/>
       <c r="R27" s="9" t="n"/>
       <c r="S27" s="9" t="n"/>
@@ -6705,7 +6751,7 @@
       <c r="Q28" s="8" t="n"/>
       <c r="R28" s="8" t="n"/>
       <c r="S28" s="8" t="n">
-        <v>5.445</v>
+        <v>7.608</v>
       </c>
       <c r="T28" s="8" t="n"/>
       <c r="U28" s="8" t="n"/>
@@ -6718,7 +6764,7 @@
       <c r="AB28" s="8" t="n"/>
       <c r="AC28" s="8" t="n"/>
       <c r="AD28" s="8" t="n">
-        <v>9.555</v>
+        <v>7.392</v>
       </c>
       <c r="AE28" s="8" t="n"/>
       <c r="AF28" s="8" t="n"/>
@@ -6762,7 +6808,7 @@
       <c r="U29" s="9" t="n"/>
       <c r="V29" s="9" t="n"/>
       <c r="W29" s="9" t="n">
-        <v>10</v>
+        <v>8.795999999999999</v>
       </c>
       <c r="X29" s="9" t="n"/>
       <c r="Y29" s="9" t="n"/>
@@ -6810,18 +6856,20 @@
       <c r="R30" s="8" t="n"/>
       <c r="S30" s="8" t="n"/>
       <c r="T30" s="8" t="n">
-        <v>7.317</v>
+        <v>11.333</v>
       </c>
       <c r="U30" s="8" t="n"/>
       <c r="V30" s="8" t="n"/>
       <c r="W30" s="8" t="n"/>
       <c r="X30" s="8" t="n">
-        <v>6.683</v>
+        <v>2.047</v>
       </c>
       <c r="Y30" s="8" t="n"/>
       <c r="Z30" s="8" t="n"/>
       <c r="AA30" s="8" t="n"/>
-      <c r="AB30" s="8" t="n"/>
+      <c r="AB30" s="8" t="n">
+        <v>0.62</v>
+      </c>
       <c r="AC30" s="8" t="n"/>
       <c r="AD30" s="8" t="n"/>
       <c r="AE30" s="8" t="n"/>
@@ -6860,14 +6908,16 @@
       <c r="O31" s="9" t="n"/>
       <c r="P31" s="9" t="n"/>
       <c r="Q31" s="9" t="n"/>
-      <c r="R31" s="9" t="n">
-        <v>6</v>
-      </c>
+      <c r="R31" s="9" t="n"/>
       <c r="S31" s="9" t="n"/>
       <c r="T31" s="9" t="n"/>
-      <c r="U31" s="9" t="n"/>
+      <c r="U31" s="9" t="n">
+        <v>0.415</v>
+      </c>
       <c r="V31" s="9" t="n"/>
-      <c r="W31" s="9" t="n"/>
+      <c r="W31" s="9" t="n">
+        <v>5.187</v>
+      </c>
       <c r="X31" s="9" t="n"/>
       <c r="Y31" s="9" t="n"/>
       <c r="Z31" s="9" t="n"/>
@@ -6912,19 +6962,21 @@
       <c r="P32" s="8" t="n"/>
       <c r="Q32" s="8" t="n"/>
       <c r="R32" s="8" t="n"/>
-      <c r="S32" s="8" t="n">
-        <v>5.936</v>
-      </c>
+      <c r="S32" s="8" t="n"/>
       <c r="T32" s="8" t="n"/>
       <c r="U32" s="8" t="n">
-        <v>1.898</v>
+        <v>3.239</v>
       </c>
       <c r="V32" s="8" t="n"/>
       <c r="W32" s="8" t="n"/>
       <c r="X32" s="8" t="n"/>
       <c r="Y32" s="8" t="n"/>
-      <c r="Z32" s="8" t="n"/>
-      <c r="AA32" s="8" t="n"/>
+      <c r="Z32" s="8" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="AA32" s="8" t="n">
+        <v>2.791</v>
+      </c>
       <c r="AB32" s="8" t="n"/>
       <c r="AC32" s="8" t="n"/>
       <c r="AD32" s="8" t="n"/>
@@ -6976,17 +7028,21 @@
       <c r="AA33" s="9" t="n"/>
       <c r="AB33" s="9" t="n"/>
       <c r="AC33" s="9" t="n">
-        <v>3.781</v>
+        <v>0.304</v>
       </c>
       <c r="AD33" s="9" t="n"/>
       <c r="AE33" s="9" t="n"/>
       <c r="AF33" s="9" t="n"/>
       <c r="AG33" s="9" t="n">
-        <v>0.983</v>
+        <v>4.08</v>
       </c>
       <c r="AH33" s="9" t="n"/>
-      <c r="AI33" s="9" t="n"/>
-      <c r="AJ33" s="9" t="n"/>
+      <c r="AI33" s="9" t="n">
+        <v>2.336</v>
+      </c>
+      <c r="AJ33" s="9" t="n">
+        <v>2.636</v>
+      </c>
       <c r="AK33" s="9" t="n"/>
       <c r="AL33" s="9" t="n"/>
       <c r="AM33" s="9" t="n"/>
@@ -7019,21 +7075,27 @@
       <c r="Q34" s="8" t="n"/>
       <c r="R34" s="8" t="n"/>
       <c r="S34" s="8" t="n">
-        <v>22</v>
+        <v>11.031</v>
       </c>
       <c r="T34" s="8" t="n"/>
       <c r="U34" s="8" t="n"/>
-      <c r="V34" s="8" t="n"/>
+      <c r="V34" s="8" t="n">
+        <v>8.614000000000001</v>
+      </c>
       <c r="W34" s="8" t="n"/>
       <c r="X34" s="8" t="n"/>
-      <c r="Y34" s="8" t="n"/>
+      <c r="Y34" s="8" t="n">
+        <v>1.249</v>
+      </c>
       <c r="Z34" s="8" t="n"/>
       <c r="AA34" s="8" t="n"/>
       <c r="AB34" s="8" t="n"/>
       <c r="AC34" s="8" t="n"/>
       <c r="AD34" s="8" t="n"/>
       <c r="AE34" s="8" t="n"/>
-      <c r="AF34" s="8" t="n"/>
+      <c r="AF34" s="8" t="n">
+        <v>1.106</v>
+      </c>
       <c r="AG34" s="8" t="n"/>
       <c r="AH34" s="8" t="n"/>
       <c r="AI34" s="8" t="n"/>
@@ -7070,7 +7132,7 @@
       <c r="Q35" s="9" t="n"/>
       <c r="R35" s="9" t="n"/>
       <c r="S35" s="9" t="n">
-        <v>20</v>
+        <v>13.181</v>
       </c>
       <c r="T35" s="9" t="n"/>
       <c r="U35" s="9" t="n"/>
@@ -7082,7 +7144,9 @@
       <c r="AA35" s="9" t="n"/>
       <c r="AB35" s="9" t="n"/>
       <c r="AC35" s="9" t="n"/>
-      <c r="AD35" s="9" t="n"/>
+      <c r="AD35" s="9" t="n">
+        <v>6.819</v>
+      </c>
       <c r="AE35" s="9" t="n"/>
       <c r="AF35" s="9" t="n"/>
       <c r="AG35" s="9" t="n"/>
@@ -7121,7 +7185,7 @@
       <c r="Q36" s="8" t="n"/>
       <c r="R36" s="8" t="n"/>
       <c r="S36" s="8" t="n">
-        <v>0.184</v>
+        <v>0.6</v>
       </c>
       <c r="T36" s="8" t="n"/>
       <c r="U36" s="8" t="n"/>
@@ -7133,9 +7197,7 @@
       <c r="AA36" s="8" t="n"/>
       <c r="AB36" s="8" t="n"/>
       <c r="AC36" s="8" t="n"/>
-      <c r="AD36" s="8" t="n">
-        <v>0.416</v>
-      </c>
+      <c r="AD36" s="8" t="n"/>
       <c r="AE36" s="8" t="n"/>
       <c r="AF36" s="8" t="n"/>
       <c r="AG36" s="8" t="n"/>
@@ -7174,23 +7236,29 @@
       <c r="Q37" s="9" t="n"/>
       <c r="R37" s="9" t="n"/>
       <c r="S37" s="9" t="n">
-        <v>0.6</v>
+        <v>0.207</v>
       </c>
       <c r="T37" s="9" t="n"/>
       <c r="U37" s="9" t="n"/>
       <c r="V37" s="9" t="n"/>
       <c r="W37" s="9" t="n"/>
-      <c r="X37" s="9" t="n"/>
+      <c r="X37" s="9" t="n">
+        <v>0.03</v>
+      </c>
       <c r="Y37" s="9" t="n"/>
       <c r="Z37" s="9" t="n"/>
       <c r="AA37" s="9" t="n"/>
       <c r="AB37" s="9" t="n"/>
       <c r="AC37" s="9" t="n"/>
       <c r="AD37" s="9" t="n"/>
-      <c r="AE37" s="9" t="n"/>
+      <c r="AE37" s="9" t="n">
+        <v>0.207</v>
+      </c>
       <c r="AF37" s="9" t="n"/>
       <c r="AG37" s="9" t="n"/>
-      <c r="AH37" s="9" t="n"/>
+      <c r="AH37" s="9" t="n">
+        <v>0.156</v>
+      </c>
       <c r="AI37" s="9" t="n"/>
       <c r="AJ37" s="9" t="n"/>
       <c r="AK37" s="9" t="n"/>
@@ -7225,13 +7293,15 @@
       <c r="Q38" s="8" t="n"/>
       <c r="R38" s="8" t="n"/>
       <c r="S38" s="8" t="n">
-        <v>0.6</v>
+        <v>0.314</v>
       </c>
       <c r="T38" s="8" t="n"/>
       <c r="U38" s="8" t="n"/>
       <c r="V38" s="8" t="n"/>
       <c r="W38" s="8" t="n"/>
-      <c r="X38" s="8" t="n"/>
+      <c r="X38" s="8" t="n">
+        <v>0.286</v>
+      </c>
       <c r="Y38" s="8" t="n"/>
       <c r="Z38" s="8" t="n"/>
       <c r="AA38" s="8" t="n"/>
@@ -7327,14 +7397,12 @@
       <c r="Q40" s="8" t="n"/>
       <c r="R40" s="8" t="n"/>
       <c r="S40" s="8" t="n">
-        <v>0.028</v>
+        <v>0.6</v>
       </c>
       <c r="T40" s="8" t="n"/>
       <c r="U40" s="8" t="n"/>
       <c r="V40" s="8" t="n"/>
-      <c r="W40" s="8" t="n">
-        <v>0.572</v>
-      </c>
+      <c r="W40" s="8" t="n"/>
       <c r="X40" s="8" t="n"/>
       <c r="Y40" s="8" t="n"/>
       <c r="Z40" s="8" t="n"/>
@@ -7380,21 +7448,23 @@
       <c r="Q41" s="9" t="n"/>
       <c r="R41" s="9" t="n"/>
       <c r="S41" s="9" t="n">
-        <v>0.142</v>
+        <v>0.296</v>
       </c>
       <c r="T41" s="9" t="n"/>
       <c r="U41" s="9" t="n"/>
       <c r="V41" s="9" t="n"/>
-      <c r="W41" s="9" t="n">
-        <v>0.458</v>
-      </c>
-      <c r="X41" s="9" t="n"/>
+      <c r="W41" s="9" t="n"/>
+      <c r="X41" s="9" t="n">
+        <v>0.28</v>
+      </c>
       <c r="Y41" s="9" t="n"/>
       <c r="Z41" s="9" t="n"/>
       <c r="AA41" s="9" t="n"/>
       <c r="AB41" s="9" t="n"/>
       <c r="AC41" s="9" t="n"/>
-      <c r="AD41" s="9" t="n"/>
+      <c r="AD41" s="9" t="n">
+        <v>0.024</v>
+      </c>
       <c r="AE41" s="9" t="n"/>
       <c r="AF41" s="9" t="n"/>
       <c r="AG41" s="9" t="n"/>
@@ -7432,14 +7502,14 @@
       <c r="P42" s="8" t="n"/>
       <c r="Q42" s="8" t="n"/>
       <c r="R42" s="8" t="n"/>
-      <c r="S42" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S42" s="8" t="n"/>
       <c r="T42" s="8" t="n"/>
       <c r="U42" s="8" t="n"/>
       <c r="V42" s="8" t="n"/>
       <c r="W42" s="8" t="n"/>
-      <c r="X42" s="8" t="n"/>
+      <c r="X42" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y42" s="8" t="n"/>
       <c r="Z42" s="8" t="n"/>
       <c r="AA42" s="8" t="n"/>
@@ -7483,16 +7553,14 @@
       <c r="P43" s="9" t="n"/>
       <c r="Q43" s="9" t="n"/>
       <c r="R43" s="9" t="n"/>
-      <c r="S43" s="9" t="n">
-        <v>0.03</v>
-      </c>
+      <c r="S43" s="9" t="n"/>
       <c r="T43" s="9" t="n"/>
       <c r="U43" s="9" t="n"/>
       <c r="V43" s="9" t="n"/>
-      <c r="W43" s="9" t="n">
-        <v>0.515</v>
-      </c>
-      <c r="X43" s="9" t="n"/>
+      <c r="W43" s="9" t="n"/>
+      <c r="X43" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y43" s="9" t="n"/>
       <c r="Z43" s="9" t="n"/>
       <c r="AA43" s="9" t="n"/>
@@ -7536,16 +7604,14 @@
       <c r="P44" s="8" t="n"/>
       <c r="Q44" s="8" t="n"/>
       <c r="R44" s="8" t="n"/>
-      <c r="S44" s="8" t="n">
-        <v>0.05</v>
-      </c>
+      <c r="S44" s="8" t="n"/>
       <c r="T44" s="8" t="n"/>
       <c r="U44" s="8" t="n"/>
       <c r="V44" s="8" t="n"/>
-      <c r="W44" s="8" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="X44" s="8" t="n"/>
+      <c r="W44" s="8" t="n"/>
+      <c r="X44" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y44" s="8" t="n"/>
       <c r="Z44" s="8" t="n"/>
       <c r="AA44" s="8" t="n"/>
@@ -7589,16 +7655,14 @@
       <c r="P45" s="9" t="n"/>
       <c r="Q45" s="9" t="n"/>
       <c r="R45" s="9" t="n"/>
-      <c r="S45" s="9" t="n">
-        <v>0.11</v>
-      </c>
+      <c r="S45" s="9" t="n"/>
       <c r="T45" s="9" t="n"/>
       <c r="U45" s="9" t="n"/>
       <c r="V45" s="9" t="n"/>
-      <c r="W45" s="9" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="X45" s="9" t="n"/>
+      <c r="W45" s="9" t="n"/>
+      <c r="X45" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y45" s="9" t="n"/>
       <c r="Z45" s="9" t="n"/>
       <c r="AA45" s="9" t="n"/>
@@ -7642,14 +7706,14 @@
       <c r="P46" s="8" t="n"/>
       <c r="Q46" s="8" t="n"/>
       <c r="R46" s="8" t="n"/>
-      <c r="S46" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S46" s="8" t="n"/>
       <c r="T46" s="8" t="n"/>
       <c r="U46" s="8" t="n"/>
       <c r="V46" s="8" t="n"/>
       <c r="W46" s="8" t="n"/>
-      <c r="X46" s="8" t="n"/>
+      <c r="X46" s="8" t="n">
+        <v>0.589</v>
+      </c>
       <c r="Y46" s="8" t="n"/>
       <c r="Z46" s="8" t="n"/>
       <c r="AA46" s="8" t="n"/>
@@ -7744,7 +7808,9 @@
       <c r="P48" s="8" t="n"/>
       <c r="Q48" s="8" t="n"/>
       <c r="R48" s="8" t="n"/>
-      <c r="S48" s="8" t="n"/>
+      <c r="S48" s="8" t="n">
+        <v>0.59</v>
+      </c>
       <c r="T48" s="8" t="n"/>
       <c r="U48" s="8" t="n"/>
       <c r="V48" s="8" t="n"/>
@@ -7753,9 +7819,7 @@
       <c r="Y48" s="8" t="n"/>
       <c r="Z48" s="8" t="n"/>
       <c r="AA48" s="8" t="n"/>
-      <c r="AB48" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AB48" s="8" t="n"/>
       <c r="AC48" s="8" t="n"/>
       <c r="AD48" s="8" t="n"/>
       <c r="AE48" s="8" t="n"/>
@@ -7795,10 +7859,10 @@
       <c r="P49" s="9" t="n"/>
       <c r="Q49" s="9" t="n"/>
       <c r="R49" s="9" t="n"/>
-      <c r="S49" s="9" t="n"/>
-      <c r="T49" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S49" s="9" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="T49" s="9" t="n"/>
       <c r="U49" s="9" t="n"/>
       <c r="V49" s="9" t="n"/>
       <c r="W49" s="9" t="n"/>
@@ -7846,10 +7910,10 @@
       <c r="P50" s="8" t="n"/>
       <c r="Q50" s="8" t="n"/>
       <c r="R50" s="8" t="n"/>
-      <c r="S50" s="8" t="n"/>
-      <c r="T50" s="8" t="n">
-        <v>0.592</v>
-      </c>
+      <c r="S50" s="8" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="T50" s="8" t="n"/>
       <c r="U50" s="8" t="n"/>
       <c r="V50" s="8" t="n"/>
       <c r="W50" s="8" t="n"/>
@@ -7897,10 +7961,10 @@
       <c r="P51" s="9" t="n"/>
       <c r="Q51" s="9" t="n"/>
       <c r="R51" s="9" t="n"/>
-      <c r="S51" s="9" t="n"/>
-      <c r="T51" s="9" t="n">
-        <v>0.428</v>
-      </c>
+      <c r="S51" s="9" t="n">
+        <v>0.536</v>
+      </c>
+      <c r="T51" s="9" t="n"/>
       <c r="U51" s="9" t="n"/>
       <c r="V51" s="9" t="n"/>
       <c r="W51" s="9" t="n"/>
@@ -7912,7 +7976,9 @@
       <c r="AC51" s="9" t="n"/>
       <c r="AD51" s="9" t="n"/>
       <c r="AE51" s="9" t="n"/>
-      <c r="AF51" s="9" t="n"/>
+      <c r="AF51" s="9" t="n">
+        <v>0.055</v>
+      </c>
       <c r="AG51" s="9" t="n"/>
       <c r="AH51" s="9" t="n"/>
       <c r="AI51" s="9" t="n"/>
@@ -7948,14 +8014,14 @@
       <c r="P52" s="8" t="n"/>
       <c r="Q52" s="8" t="n"/>
       <c r="R52" s="8" t="n"/>
-      <c r="S52" s="8" t="n"/>
+      <c r="S52" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T52" s="8" t="n"/>
       <c r="U52" s="8" t="n"/>
       <c r="V52" s="8" t="n"/>
       <c r="W52" s="8" t="n"/>
-      <c r="X52" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="X52" s="8" t="n"/>
       <c r="Y52" s="8" t="n"/>
       <c r="Z52" s="8" t="n"/>
       <c r="AA52" s="8" t="n"/>
@@ -7999,10 +8065,10 @@
       <c r="P53" s="9" t="n"/>
       <c r="Q53" s="9" t="n"/>
       <c r="R53" s="9" t="n"/>
-      <c r="S53" s="9" t="n"/>
-      <c r="T53" s="9" t="n">
-        <v>0.578</v>
-      </c>
+      <c r="S53" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T53" s="9" t="n"/>
       <c r="U53" s="9" t="n"/>
       <c r="V53" s="9" t="n"/>
       <c r="W53" s="9" t="n"/>
@@ -8050,7 +8116,9 @@
       <c r="P54" s="8" t="n"/>
       <c r="Q54" s="8" t="n"/>
       <c r="R54" s="8" t="n"/>
-      <c r="S54" s="8" t="n"/>
+      <c r="S54" s="8" t="n">
+        <v>0.519</v>
+      </c>
       <c r="T54" s="8" t="n"/>
       <c r="U54" s="8" t="n"/>
       <c r="V54" s="8" t="n"/>
@@ -8059,9 +8127,7 @@
       <c r="Y54" s="8" t="n"/>
       <c r="Z54" s="8" t="n"/>
       <c r="AA54" s="8" t="n"/>
-      <c r="AB54" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AB54" s="8" t="n"/>
       <c r="AC54" s="8" t="n"/>
       <c r="AD54" s="8" t="n"/>
       <c r="AE54" s="8" t="n"/>
@@ -8101,10 +8167,10 @@
       <c r="P55" s="9" t="n"/>
       <c r="Q55" s="9" t="n"/>
       <c r="R55" s="9" t="n"/>
-      <c r="S55" s="9" t="n"/>
-      <c r="T55" s="9" t="n">
+      <c r="S55" s="9" t="n">
         <v>0.6</v>
       </c>
+      <c r="T55" s="9" t="n"/>
       <c r="U55" s="9" t="n"/>
       <c r="V55" s="9" t="n"/>
       <c r="W55" s="9" t="n"/>
@@ -8179,7 +8245,7 @@
       <c r="AJ56" s="8" t="n"/>
       <c r="AK56" s="8" t="n"/>
       <c r="AL56" s="8" t="n">
-        <v>13.303</v>
+        <v>14.791</v>
       </c>
       <c r="AM56" s="8" t="n"/>
       <c r="AN56" s="8" t="n"/>
@@ -8227,10 +8293,10 @@
       <c r="AH57" s="9" t="n"/>
       <c r="AI57" s="9" t="n"/>
       <c r="AJ57" s="9" t="n"/>
-      <c r="AK57" s="9" t="n"/>
-      <c r="AL57" s="9" t="n">
-        <v>10</v>
-      </c>
+      <c r="AK57" s="9" t="n">
+        <v>2.882</v>
+      </c>
+      <c r="AL57" s="9" t="n"/>
       <c r="AM57" s="9" t="n"/>
       <c r="AN57" s="9" t="n"/>
       <c r="AO57" s="9" t="n"/>
@@ -8278,7 +8344,7 @@
       <c r="AI58" s="8" t="n"/>
       <c r="AJ58" s="8" t="n"/>
       <c r="AK58" s="8" t="n">
-        <v>14</v>
+        <v>6.011</v>
       </c>
       <c r="AL58" s="8" t="n"/>
       <c r="AM58" s="8" t="n"/>
@@ -8327,7 +8393,9 @@
       <c r="AH59" s="9" t="n"/>
       <c r="AI59" s="9" t="n"/>
       <c r="AJ59" s="9" t="n"/>
-      <c r="AK59" s="9" t="n"/>
+      <c r="AK59" s="9" t="n">
+        <v>5.178</v>
+      </c>
       <c r="AL59" s="9" t="n"/>
       <c r="AM59" s="9" t="n"/>
       <c r="AN59" s="9" t="n"/>
@@ -8377,7 +8445,7 @@
       <c r="AJ60" s="8" t="n"/>
       <c r="AK60" s="8" t="n"/>
       <c r="AL60" s="8" t="n">
-        <v>7.945</v>
+        <v>10</v>
       </c>
       <c r="AM60" s="8" t="n"/>
       <c r="AN60" s="8" t="n"/>
@@ -8428,7 +8496,7 @@
       <c r="AK61" s="9" t="n"/>
       <c r="AL61" s="9" t="n"/>
       <c r="AM61" s="9" t="n">
-        <v>12</v>
+        <v>11.618</v>
       </c>
       <c r="AN61" s="9" t="n"/>
       <c r="AO61" s="9" t="n"/>
@@ -8476,7 +8544,7 @@
       <c r="AI62" s="8" t="n"/>
       <c r="AJ62" s="8" t="n"/>
       <c r="AK62" s="8" t="n">
-        <v>1.802</v>
+        <v>22</v>
       </c>
       <c r="AL62" s="8" t="n"/>
       <c r="AM62" s="8" t="n"/>
@@ -8526,7 +8594,7 @@
       <c r="AI63" s="9" t="n"/>
       <c r="AJ63" s="9" t="n"/>
       <c r="AK63" s="9" t="n">
-        <v>20</v>
+        <v>2.864</v>
       </c>
       <c r="AL63" s="9" t="n"/>
       <c r="AM63" s="9" t="n"/>
@@ -8579,7 +8647,7 @@
       <c r="AL64" s="8" t="n"/>
       <c r="AM64" s="8" t="n"/>
       <c r="AN64" s="8" t="n">
-        <v>0.544</v>
+        <v>0.6</v>
       </c>
       <c r="AO64" s="8" t="n"/>
       <c r="AP64" s="8" t="n"/>
@@ -8629,9 +8697,11 @@
       <c r="AL65" s="9" t="n"/>
       <c r="AM65" s="9" t="n"/>
       <c r="AN65" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AO65" s="9" t="n"/>
+        <v>0.58</v>
+      </c>
+      <c r="AO65" s="9" t="n">
+        <v>0.02</v>
+      </c>
       <c r="AP65" s="9" t="n"/>
       <c r="AQ65" s="9" t="n"/>
     </row>
@@ -8679,10 +8749,12 @@
       <c r="AL66" s="8" t="n"/>
       <c r="AM66" s="8" t="n"/>
       <c r="AN66" s="8" t="n">
-        <v>0.536</v>
+        <v>0.57</v>
       </c>
       <c r="AO66" s="8" t="n"/>
-      <c r="AP66" s="8" t="n"/>
+      <c r="AP66" s="8" t="n">
+        <v>0.012</v>
+      </c>
       <c r="AQ66" s="8" t="n"/>
     </row>
     <row r="67" ht="12" customHeight="1" s="19">
@@ -8928,13 +9000,11 @@
       <c r="AK71" s="9" t="n"/>
       <c r="AL71" s="9" t="n"/>
       <c r="AM71" s="9" t="n"/>
-      <c r="AN71" s="9" t="n">
-        <v>0.048</v>
-      </c>
+      <c r="AN71" s="9" t="n"/>
       <c r="AO71" s="9" t="n"/>
       <c r="AP71" s="9" t="n"/>
       <c r="AQ71" s="9" t="n">
-        <v>0.552</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="72" ht="12" customHeight="1" s="19">
@@ -8984,7 +9054,7 @@
       <c r="AO72" s="8" t="n"/>
       <c r="AP72" s="8" t="n"/>
       <c r="AQ72" s="8" t="n">
-        <v>0.571</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="73" ht="12" customHeight="1" s="19">
@@ -9230,9 +9300,11 @@
       <c r="AK77" s="9" t="n"/>
       <c r="AL77" s="9" t="n"/>
       <c r="AM77" s="9" t="n"/>
-      <c r="AN77" s="9" t="n"/>
+      <c r="AN77" s="9" t="n">
+        <v>0.196</v>
+      </c>
       <c r="AO77" s="9" t="n">
-        <v>0.5639999999999999</v>
+        <v>0.404</v>
       </c>
       <c r="AP77" s="9" t="n"/>
       <c r="AQ77" s="9" t="n"/>
@@ -9281,10 +9353,10 @@
       <c r="AL78" s="8" t="n"/>
       <c r="AM78" s="8" t="n"/>
       <c r="AN78" s="8" t="n">
-        <v>0.048</v>
+        <v>0.029</v>
       </c>
       <c r="AO78" s="8" t="n">
-        <v>0.509</v>
+        <v>0.571</v>
       </c>
       <c r="AP78" s="8" t="n"/>
       <c r="AQ78" s="8" t="n"/>
@@ -9332,11 +9404,9 @@
       <c r="AK79" s="9" t="n"/>
       <c r="AL79" s="9" t="n"/>
       <c r="AM79" s="9" t="n"/>
-      <c r="AN79" s="9" t="n">
-        <v>0.038</v>
-      </c>
+      <c r="AN79" s="9" t="n"/>
       <c r="AO79" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>0.516</v>
       </c>
       <c r="AP79" s="9" t="n"/>
       <c r="AQ79" s="9" t="n"/>
@@ -9364,7 +9434,9 @@
       <c r="Q80" s="8" t="n"/>
       <c r="R80" s="8" t="n"/>
       <c r="S80" s="8" t="n"/>
-      <c r="T80" s="8" t="n"/>
+      <c r="T80" s="8" t="n">
+        <v>0.044</v>
+      </c>
       <c r="U80" s="8" t="n"/>
       <c r="V80" s="8" t="n"/>
       <c r="W80" s="8" t="n"/>
@@ -9372,15 +9444,15 @@
       <c r="Y80" s="8" t="n"/>
       <c r="Z80" s="8" t="n"/>
       <c r="AA80" s="8" t="n"/>
-      <c r="AB80" s="8" t="n"/>
+      <c r="AB80" s="8" t="n">
+        <v>0.524</v>
+      </c>
       <c r="AC80" s="8" t="n"/>
       <c r="AD80" s="8" t="n"/>
       <c r="AE80" s="8" t="n"/>
       <c r="AF80" s="8" t="n"/>
       <c r="AG80" s="8" t="n"/>
-      <c r="AH80" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AH80" s="8" t="n"/>
       <c r="AI80" s="8" t="n"/>
       <c r="AJ80" s="8" t="n"/>
       <c r="AK80" s="8" t="n"/>
@@ -9415,12 +9487,12 @@
       <c r="R81" s="9" t="n"/>
       <c r="S81" s="9" t="n"/>
       <c r="T81" s="9" t="n"/>
-      <c r="U81" s="9" t="n">
-        <v>0.055</v>
-      </c>
+      <c r="U81" s="9" t="n"/>
       <c r="V81" s="9" t="n"/>
       <c r="W81" s="9" t="n"/>
-      <c r="X81" s="9" t="n"/>
+      <c r="X81" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y81" s="9" t="n"/>
       <c r="Z81" s="9" t="n"/>
       <c r="AA81" s="9" t="n"/>
@@ -9428,9 +9500,7 @@
       <c r="AC81" s="9" t="n"/>
       <c r="AD81" s="9" t="n"/>
       <c r="AE81" s="9" t="n"/>
-      <c r="AF81" s="9" t="n">
-        <v>0.545</v>
-      </c>
+      <c r="AF81" s="9" t="n"/>
       <c r="AG81" s="9" t="n"/>
       <c r="AH81" s="9" t="n"/>
       <c r="AI81" s="9" t="n"/>
@@ -9475,11 +9545,11 @@
       <c r="Z82" s="8" t="n"/>
       <c r="AA82" s="8" t="n"/>
       <c r="AB82" s="8" t="n"/>
-      <c r="AC82" s="8" t="n"/>
+      <c r="AC82" s="8" t="n">
+        <v>0.446</v>
+      </c>
       <c r="AD82" s="8" t="n"/>
-      <c r="AE82" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AE82" s="8" t="n"/>
       <c r="AF82" s="8" t="n"/>
       <c r="AG82" s="8" t="n"/>
       <c r="AH82" s="8" t="n"/>
@@ -9515,9 +9585,7 @@
       <c r="P83" s="9" t="n"/>
       <c r="Q83" s="9" t="n"/>
       <c r="R83" s="9" t="n"/>
-      <c r="S83" s="9" t="n">
-        <v>0.027</v>
-      </c>
+      <c r="S83" s="9" t="n"/>
       <c r="T83" s="9" t="n"/>
       <c r="U83" s="9" t="n"/>
       <c r="V83" s="9" t="n"/>
@@ -9528,10 +9596,10 @@
       <c r="AA83" s="9" t="n"/>
       <c r="AB83" s="9" t="n"/>
       <c r="AC83" s="9" t="n"/>
-      <c r="AD83" s="9" t="n">
-        <v>0.573</v>
-      </c>
-      <c r="AE83" s="9" t="n"/>
+      <c r="AD83" s="9" t="n"/>
+      <c r="AE83" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AF83" s="9" t="n"/>
       <c r="AG83" s="9" t="n"/>
       <c r="AH83" s="9" t="n"/>
@@ -9970,7 +10038,7 @@
       <c r="C3" s="9" t="n"/>
       <c r="D3" s="9" t="n"/>
       <c r="E3" s="9" t="n">
-        <v>55</v>
+        <v>51.825</v>
       </c>
       <c r="F3" s="9" t="n"/>
       <c r="G3" s="9" t="n"/>
@@ -10027,7 +10095,7 @@
       <c r="I4" s="8" t="n"/>
       <c r="J4" s="8" t="n"/>
       <c r="K4" s="8" t="n">
-        <v>35</v>
+        <v>34.206</v>
       </c>
       <c r="L4" s="8" t="n"/>
       <c r="M4" s="8" t="n"/>
@@ -10071,12 +10139,14 @@
       </c>
       <c r="C5" s="9" t="n"/>
       <c r="D5" s="9" t="n">
-        <v>72</v>
+        <v>30.713</v>
       </c>
       <c r="E5" s="9" t="n"/>
       <c r="F5" s="9" t="n"/>
       <c r="G5" s="9" t="n"/>
-      <c r="H5" s="9" t="n"/>
+      <c r="H5" s="9" t="n">
+        <v>28.367</v>
+      </c>
       <c r="I5" s="9" t="n"/>
       <c r="J5" s="9" t="n"/>
       <c r="K5" s="9" t="n"/>
@@ -10084,7 +10154,9 @@
       <c r="M5" s="9" t="n"/>
       <c r="N5" s="9" t="n"/>
       <c r="O5" s="9" t="n"/>
-      <c r="P5" s="9" t="n"/>
+      <c r="P5" s="9" t="n">
+        <v>12.92</v>
+      </c>
       <c r="Q5" s="9" t="n"/>
       <c r="R5" s="9" t="n"/>
       <c r="S5" s="9" t="n"/>
@@ -10172,20 +10244,24 @@
         </is>
       </c>
       <c r="C7" s="9" t="n"/>
-      <c r="D7" s="9" t="n"/>
+      <c r="D7" s="9" t="n">
+        <v>31.743</v>
+      </c>
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="9" t="n"/>
-      <c r="G7" s="9" t="n"/>
-      <c r="H7" s="9" t="n">
-        <v>55</v>
-      </c>
+      <c r="G7" s="9" t="n">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="H7" s="9" t="n"/>
       <c r="I7" s="9" t="n"/>
       <c r="J7" s="9" t="n"/>
       <c r="K7" s="9" t="n"/>
       <c r="L7" s="9" t="n"/>
       <c r="M7" s="9" t="n"/>
       <c r="N7" s="9" t="n"/>
-      <c r="O7" s="9" t="n"/>
+      <c r="O7" s="9" t="n">
+        <v>14.797</v>
+      </c>
       <c r="P7" s="9" t="n"/>
       <c r="Q7" s="9" t="n"/>
       <c r="R7" s="9" t="n"/>
@@ -10274,13 +10350,15 @@
         </is>
       </c>
       <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
+      <c r="D9" s="9" t="n">
+        <v>23.518</v>
+      </c>
       <c r="E9" s="9" t="n"/>
       <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="n"/>
       <c r="H9" s="9" t="n"/>
       <c r="I9" s="9" t="n">
-        <v>46</v>
+        <v>22.482</v>
       </c>
       <c r="J9" s="9" t="n"/>
       <c r="K9" s="9" t="n"/>
@@ -10325,12 +10403,14 @@
         </is>
       </c>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n"/>
+      <c r="D10" s="8" t="n">
+        <v>20</v>
+      </c>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
       <c r="H10" s="8" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="I10" s="8" t="n"/>
       <c r="J10" s="8" t="n"/>
@@ -10375,22 +10455,28 @@
           <t>B4</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
+      <c r="C11" s="9" t="n">
+        <v>1.855</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>9.509</v>
+      </c>
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="9" t="n"/>
       <c r="H11" s="9" t="n"/>
       <c r="I11" s="9" t="n"/>
       <c r="J11" s="9" t="n"/>
-      <c r="K11" s="9" t="n"/>
+      <c r="K11" s="9" t="n">
+        <v>6.516</v>
+      </c>
       <c r="L11" s="9" t="n">
-        <v>25</v>
+        <v>8.708</v>
       </c>
       <c r="M11" s="9" t="n"/>
       <c r="N11" s="9" t="n"/>
       <c r="O11" s="9" t="n">
-        <v>3</v>
+        <v>1.412</v>
       </c>
       <c r="P11" s="9" t="n"/>
       <c r="Q11" s="9" t="n"/>
@@ -10429,11 +10515,13 @@
         </is>
       </c>
       <c r="C12" s="8" t="n"/>
-      <c r="D12" s="8" t="n"/>
+      <c r="D12" s="8" t="n">
+        <v>12.5</v>
+      </c>
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="H12" s="8" t="n"/>
       <c r="I12" s="8" t="n"/>
@@ -10483,7 +10571,7 @@
       <c r="D13" s="9" t="n"/>
       <c r="E13" s="9" t="n"/>
       <c r="F13" s="9" t="n">
-        <v>86</v>
+        <v>84.64</v>
       </c>
       <c r="G13" s="9" t="n"/>
       <c r="H13" s="9" t="n"/>
@@ -10535,11 +10623,11 @@
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n"/>
       <c r="G14" s="8" t="n"/>
-      <c r="H14" s="8" t="n"/>
+      <c r="H14" s="8" t="n">
+        <v>55</v>
+      </c>
       <c r="I14" s="8" t="n"/>
-      <c r="J14" s="8" t="n">
-        <v>55</v>
-      </c>
+      <c r="J14" s="8" t="n"/>
       <c r="K14" s="8" t="n"/>
       <c r="L14" s="8" t="n"/>
       <c r="M14" s="8" t="n"/>
@@ -10587,15 +10675,13 @@
       <c r="F15" s="9" t="n"/>
       <c r="G15" s="9" t="n"/>
       <c r="H15" s="9" t="n">
-        <v>37.421</v>
+        <v>44</v>
       </c>
       <c r="I15" s="9" t="n"/>
       <c r="J15" s="9" t="n"/>
       <c r="K15" s="9" t="n"/>
       <c r="L15" s="9" t="n"/>
-      <c r="M15" s="9" t="n">
-        <v>6.579</v>
-      </c>
+      <c r="M15" s="9" t="n"/>
       <c r="N15" s="9" t="n"/>
       <c r="O15" s="9" t="n"/>
       <c r="P15" s="9" t="n"/>
@@ -10693,15 +10779,13 @@
       <c r="H17" s="9" t="n"/>
       <c r="I17" s="9" t="n"/>
       <c r="J17" s="9" t="n">
-        <v>22.895</v>
+        <v>25</v>
       </c>
       <c r="K17" s="9" t="n"/>
       <c r="L17" s="9" t="n"/>
       <c r="M17" s="9" t="n"/>
       <c r="N17" s="9" t="n"/>
-      <c r="O17" s="9" t="n">
-        <v>2.105</v>
-      </c>
+      <c r="O17" s="9" t="n"/>
       <c r="P17" s="9" t="n"/>
       <c r="Q17" s="9" t="n"/>
       <c r="R17" s="9" t="n"/>
@@ -10747,14 +10831,18 @@
       <c r="I18" s="8" t="n"/>
       <c r="J18" s="8" t="n"/>
       <c r="K18" s="8" t="n">
-        <v>13.25</v>
-      </c>
-      <c r="L18" s="8" t="n"/>
+        <v>8.997</v>
+      </c>
+      <c r="L18" s="8" t="n">
+        <v>14.608</v>
+      </c>
       <c r="M18" s="8" t="n"/>
-      <c r="N18" s="8" t="n"/>
+      <c r="N18" s="8" t="n">
+        <v>15.942</v>
+      </c>
       <c r="O18" s="8" t="n"/>
       <c r="P18" s="8" t="n">
-        <v>35</v>
+        <v>20.453</v>
       </c>
       <c r="Q18" s="8" t="n"/>
       <c r="R18" s="8" t="n"/>
@@ -10792,14 +10880,16 @@
         </is>
       </c>
       <c r="C19" s="9" t="n">
-        <v>45</v>
+        <v>26.741</v>
       </c>
       <c r="D19" s="9" t="n"/>
       <c r="E19" s="9" t="n"/>
       <c r="F19" s="9" t="n"/>
       <c r="G19" s="9" t="n"/>
       <c r="H19" s="9" t="n"/>
-      <c r="I19" s="9" t="n"/>
+      <c r="I19" s="9" t="n">
+        <v>18.259</v>
+      </c>
       <c r="J19" s="9" t="n"/>
       <c r="K19" s="9" t="n"/>
       <c r="L19" s="9" t="n"/>
@@ -10842,11 +10932,13 @@
           <t>B13</t>
         </is>
       </c>
-      <c r="C20" s="8" t="n"/>
+      <c r="C20" s="8" t="n">
+        <v>11.036</v>
+      </c>
       <c r="D20" s="8" t="n"/>
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="8" t="n">
-        <v>14.121</v>
+        <v>15.871</v>
       </c>
       <c r="G20" s="8" t="n"/>
       <c r="H20" s="8" t="n"/>
@@ -10855,7 +10947,7 @@
       <c r="K20" s="8" t="n"/>
       <c r="L20" s="8" t="n"/>
       <c r="M20" s="8" t="n">
-        <v>7.707</v>
+        <v>8.093</v>
       </c>
       <c r="N20" s="8" t="n"/>
       <c r="O20" s="8" t="n"/>
@@ -10902,14 +10994,14 @@
       <c r="G21" s="9" t="n"/>
       <c r="H21" s="9" t="n"/>
       <c r="I21" s="9" t="n"/>
-      <c r="J21" s="9" t="n"/>
+      <c r="J21" s="9" t="n">
+        <v>20</v>
+      </c>
       <c r="K21" s="9" t="n"/>
       <c r="L21" s="9" t="n"/>
       <c r="M21" s="9" t="n"/>
       <c r="N21" s="9" t="n"/>
-      <c r="O21" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="O21" s="9" t="n"/>
       <c r="P21" s="9" t="n"/>
       <c r="Q21" s="9" t="n"/>
       <c r="R21" s="9" t="n"/>
@@ -10952,14 +11044,14 @@
       <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
-      <c r="I22" s="8" t="n"/>
+      <c r="I22" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="J22" s="8" t="n"/>
       <c r="K22" s="8" t="n"/>
       <c r="L22" s="8" t="n"/>
       <c r="M22" s="8" t="n"/>
-      <c r="N22" s="8" t="n">
-        <v>15</v>
-      </c>
+      <c r="N22" s="8" t="n"/>
       <c r="O22" s="8" t="n"/>
       <c r="P22" s="8" t="n"/>
       <c r="Q22" s="8" t="n"/>
@@ -11003,13 +11095,13 @@
       <c r="F23" s="9" t="n"/>
       <c r="G23" s="9" t="n"/>
       <c r="H23" s="9" t="n"/>
-      <c r="I23" s="9" t="n">
-        <v>13</v>
-      </c>
+      <c r="I23" s="9" t="n"/>
       <c r="J23" s="9" t="n"/>
       <c r="K23" s="9" t="n"/>
       <c r="L23" s="9" t="n"/>
-      <c r="M23" s="9" t="n"/>
+      <c r="M23" s="9" t="n">
+        <v>6.683</v>
+      </c>
       <c r="N23" s="9" t="n"/>
       <c r="O23" s="9" t="n"/>
       <c r="P23" s="9" t="n"/>
@@ -11055,7 +11147,9 @@
       <c r="G24" s="8" t="n"/>
       <c r="H24" s="8" t="n"/>
       <c r="I24" s="8" t="n"/>
-      <c r="J24" s="8" t="n"/>
+      <c r="J24" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="K24" s="8" t="n"/>
       <c r="L24" s="8" t="n"/>
       <c r="M24" s="8" t="n"/>
@@ -11098,7 +11192,7 @@
         </is>
       </c>
       <c r="C25" s="9" t="n">
-        <v>18</v>
+        <v>14.529</v>
       </c>
       <c r="D25" s="9" t="n"/>
       <c r="E25" s="9" t="n"/>
@@ -11200,7 +11294,7 @@
         </is>
       </c>
       <c r="C27" s="9" t="n">
-        <v>20</v>
+        <v>19.605</v>
       </c>
       <c r="D27" s="9" t="n"/>
       <c r="E27" s="9" t="n"/>
@@ -11271,7 +11365,7 @@
       <c r="U28" s="8" t="n"/>
       <c r="V28" s="8" t="n"/>
       <c r="W28" s="8" t="n">
-        <v>15</v>
+        <v>14.438</v>
       </c>
       <c r="X28" s="8" t="n"/>
       <c r="Y28" s="8" t="n"/>
@@ -11280,7 +11374,9 @@
       <c r="AB28" s="8" t="n"/>
       <c r="AC28" s="8" t="n"/>
       <c r="AD28" s="8" t="n"/>
-      <c r="AE28" s="8" t="n"/>
+      <c r="AE28" s="8" t="n">
+        <v>0.5620000000000001</v>
+      </c>
       <c r="AF28" s="8" t="n"/>
       <c r="AG28" s="8" t="n"/>
       <c r="AH28" s="8" t="n"/>
@@ -11329,7 +11425,7 @@
       <c r="AB29" s="9" t="n"/>
       <c r="AC29" s="9" t="n"/>
       <c r="AD29" s="9" t="n">
-        <v>10</v>
+        <v>9.590999999999999</v>
       </c>
       <c r="AE29" s="9" t="n"/>
       <c r="AF29" s="9" t="n"/>
@@ -11369,12 +11465,12 @@
       <c r="Q30" s="8" t="n"/>
       <c r="R30" s="8" t="n"/>
       <c r="S30" s="8" t="n">
-        <v>5.68</v>
+        <v>5.23</v>
       </c>
       <c r="T30" s="8" t="n"/>
       <c r="U30" s="8" t="n"/>
       <c r="V30" s="8" t="n">
-        <v>8.32</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="W30" s="8" t="n"/>
       <c r="X30" s="8" t="n"/>
@@ -11382,7 +11478,9 @@
       <c r="Z30" s="8" t="n"/>
       <c r="AA30" s="8" t="n"/>
       <c r="AB30" s="8" t="n"/>
-      <c r="AC30" s="8" t="n"/>
+      <c r="AC30" s="8" t="n">
+        <v>0.489</v>
+      </c>
       <c r="AD30" s="8" t="n"/>
       <c r="AE30" s="8" t="n"/>
       <c r="AF30" s="8" t="n"/>
@@ -11474,11 +11572,11 @@
       <c r="R32" s="8" t="n"/>
       <c r="S32" s="8" t="n"/>
       <c r="T32" s="8" t="n">
-        <v>7.44</v>
+        <v>6.58</v>
       </c>
       <c r="U32" s="8" t="n"/>
       <c r="V32" s="8" t="n">
-        <v>2.56</v>
+        <v>3.42</v>
       </c>
       <c r="W32" s="8" t="n"/>
       <c r="X32" s="8" t="n"/>
@@ -11528,16 +11626,20 @@
       <c r="S33" s="9" t="n"/>
       <c r="T33" s="9" t="n"/>
       <c r="U33" s="9" t="n">
-        <v>2.16</v>
+        <v>6.085</v>
       </c>
       <c r="V33" s="9" t="n">
-        <v>4.12</v>
+        <v>1.943</v>
       </c>
       <c r="W33" s="9" t="n"/>
       <c r="X33" s="9" t="n"/>
       <c r="Y33" s="9" t="n"/>
-      <c r="Z33" s="9" t="n"/>
-      <c r="AA33" s="9" t="n"/>
+      <c r="Z33" s="9" t="n">
+        <v>2.599</v>
+      </c>
+      <c r="AA33" s="9" t="n">
+        <v>1.373</v>
+      </c>
       <c r="AB33" s="9" t="n"/>
       <c r="AC33" s="9" t="n"/>
       <c r="AD33" s="9" t="n"/>
@@ -11577,26 +11679,30 @@
       <c r="O34" s="8" t="n"/>
       <c r="P34" s="8" t="n"/>
       <c r="Q34" s="8" t="n"/>
-      <c r="R34" s="8" t="n">
-        <v>22</v>
-      </c>
+      <c r="R34" s="8" t="n"/>
       <c r="S34" s="8" t="n"/>
       <c r="T34" s="8" t="n"/>
       <c r="U34" s="8" t="n"/>
       <c r="V34" s="8" t="n"/>
       <c r="W34" s="8" t="n"/>
-      <c r="X34" s="8" t="n"/>
+      <c r="X34" s="8" t="n">
+        <v>4.824</v>
+      </c>
       <c r="Y34" s="8" t="n"/>
       <c r="Z34" s="8" t="n"/>
       <c r="AA34" s="8" t="n"/>
       <c r="AB34" s="8" t="n"/>
-      <c r="AC34" s="8" t="n"/>
+      <c r="AC34" s="8" t="n">
+        <v>7.116</v>
+      </c>
       <c r="AD34" s="8" t="n"/>
       <c r="AE34" s="8" t="n"/>
       <c r="AF34" s="8" t="n"/>
       <c r="AG34" s="8" t="n"/>
       <c r="AH34" s="8" t="n"/>
-      <c r="AI34" s="8" t="n"/>
+      <c r="AI34" s="8" t="n">
+        <v>1.176</v>
+      </c>
       <c r="AJ34" s="8" t="n"/>
       <c r="AK34" s="8" t="n"/>
       <c r="AL34" s="8" t="n"/>
@@ -11628,9 +11734,7 @@
       <c r="O35" s="9" t="n"/>
       <c r="P35" s="9" t="n"/>
       <c r="Q35" s="9" t="n"/>
-      <c r="R35" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="R35" s="9" t="n"/>
       <c r="S35" s="9" t="n"/>
       <c r="T35" s="9" t="n"/>
       <c r="U35" s="9" t="n"/>
@@ -11640,15 +11744,23 @@
       <c r="Y35" s="9" t="n"/>
       <c r="Z35" s="9" t="n"/>
       <c r="AA35" s="9" t="n"/>
-      <c r="AB35" s="9" t="n"/>
+      <c r="AB35" s="9" t="n">
+        <v>2.3</v>
+      </c>
       <c r="AC35" s="9" t="n"/>
-      <c r="AD35" s="9" t="n"/>
+      <c r="AD35" s="9" t="n">
+        <v>5.925</v>
+      </c>
       <c r="AE35" s="9" t="n"/>
       <c r="AF35" s="9" t="n"/>
-      <c r="AG35" s="9" t="n"/>
+      <c r="AG35" s="9" t="n">
+        <v>0.504</v>
+      </c>
       <c r="AH35" s="9" t="n"/>
       <c r="AI35" s="9" t="n"/>
-      <c r="AJ35" s="9" t="n"/>
+      <c r="AJ35" s="9" t="n">
+        <v>1.409</v>
+      </c>
       <c r="AK35" s="9" t="n"/>
       <c r="AL35" s="9" t="n"/>
       <c r="AM35" s="9" t="n"/>
@@ -11744,12 +11856,12 @@
       <c r="AC37" s="9" t="n"/>
       <c r="AD37" s="9" t="n"/>
       <c r="AE37" s="9" t="n">
-        <v>0.27</v>
+        <v>0.197</v>
       </c>
       <c r="AF37" s="9" t="n"/>
       <c r="AG37" s="9" t="n"/>
       <c r="AH37" s="9" t="n">
-        <v>0.3</v>
+        <v>0.224</v>
       </c>
       <c r="AI37" s="9" t="n"/>
       <c r="AJ37" s="9" t="n"/>
@@ -11784,14 +11896,14 @@
       <c r="P38" s="8" t="n"/>
       <c r="Q38" s="8" t="n"/>
       <c r="R38" s="8" t="n"/>
-      <c r="S38" s="8" t="n"/>
+      <c r="S38" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T38" s="8" t="n"/>
       <c r="U38" s="8" t="n"/>
       <c r="V38" s="8" t="n"/>
       <c r="W38" s="8" t="n"/>
-      <c r="X38" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="X38" s="8" t="n"/>
       <c r="Y38" s="8" t="n"/>
       <c r="Z38" s="8" t="n"/>
       <c r="AA38" s="8" t="n"/>
@@ -11837,11 +11949,13 @@
       <c r="R39" s="9" t="n"/>
       <c r="S39" s="9" t="n"/>
       <c r="T39" s="9" t="n"/>
-      <c r="U39" s="9" t="n"/>
+      <c r="U39" s="9" t="n">
+        <v>0.28</v>
+      </c>
       <c r="V39" s="9" t="n"/>
       <c r="W39" s="9" t="n"/>
       <c r="X39" s="9" t="n">
-        <v>0.6</v>
+        <v>0.32</v>
       </c>
       <c r="Y39" s="9" t="n"/>
       <c r="Z39" s="9" t="n"/>
@@ -11886,14 +12000,14 @@
       <c r="P40" s="8" t="n"/>
       <c r="Q40" s="8" t="n"/>
       <c r="R40" s="8" t="n"/>
-      <c r="S40" s="8" t="n"/>
+      <c r="S40" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T40" s="8" t="n"/>
       <c r="U40" s="8" t="n"/>
       <c r="V40" s="8" t="n"/>
       <c r="W40" s="8" t="n"/>
-      <c r="X40" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="X40" s="8" t="n"/>
       <c r="Y40" s="8" t="n"/>
       <c r="Z40" s="8" t="n"/>
       <c r="AA40" s="8" t="n"/>
@@ -11943,16 +12057,20 @@
       <c r="V41" s="9" t="n"/>
       <c r="W41" s="9" t="n"/>
       <c r="X41" s="9" t="n">
-        <v>0.6</v>
+        <v>0.501</v>
       </c>
       <c r="Y41" s="9" t="n"/>
-      <c r="Z41" s="9" t="n"/>
+      <c r="Z41" s="9" t="n">
+        <v>0.055</v>
+      </c>
       <c r="AA41" s="9" t="n"/>
       <c r="AB41" s="9" t="n"/>
       <c r="AC41" s="9" t="n"/>
       <c r="AD41" s="9" t="n"/>
       <c r="AE41" s="9" t="n"/>
-      <c r="AF41" s="9" t="n"/>
+      <c r="AF41" s="9" t="n">
+        <v>0.043</v>
+      </c>
       <c r="AG41" s="9" t="n"/>
       <c r="AH41" s="9" t="n"/>
       <c r="AI41" s="9" t="n"/>
@@ -11988,13 +12106,15 @@
       <c r="P42" s="8" t="n"/>
       <c r="Q42" s="8" t="n"/>
       <c r="R42" s="8" t="n"/>
-      <c r="S42" s="8" t="n"/>
+      <c r="S42" s="8" t="n">
+        <v>0.318</v>
+      </c>
       <c r="T42" s="8" t="n"/>
       <c r="U42" s="8" t="n"/>
       <c r="V42" s="8" t="n"/>
       <c r="W42" s="8" t="n"/>
       <c r="X42" s="8" t="n">
-        <v>0.6</v>
+        <v>0.282</v>
       </c>
       <c r="Y42" s="8" t="n"/>
       <c r="Z42" s="8" t="n"/>
@@ -12039,14 +12159,14 @@
       <c r="P43" s="9" t="n"/>
       <c r="Q43" s="9" t="n"/>
       <c r="R43" s="9" t="n"/>
-      <c r="S43" s="9" t="n"/>
+      <c r="S43" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T43" s="9" t="n"/>
       <c r="U43" s="9" t="n"/>
       <c r="V43" s="9" t="n"/>
       <c r="W43" s="9" t="n"/>
-      <c r="X43" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="X43" s="9" t="n"/>
       <c r="Y43" s="9" t="n"/>
       <c r="Z43" s="9" t="n"/>
       <c r="AA43" s="9" t="n"/>
@@ -12090,14 +12210,14 @@
       <c r="P44" s="8" t="n"/>
       <c r="Q44" s="8" t="n"/>
       <c r="R44" s="8" t="n"/>
-      <c r="S44" s="8" t="n"/>
+      <c r="S44" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T44" s="8" t="n"/>
       <c r="U44" s="8" t="n"/>
       <c r="V44" s="8" t="n"/>
       <c r="W44" s="8" t="n"/>
-      <c r="X44" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="X44" s="8" t="n"/>
       <c r="Y44" s="8" t="n"/>
       <c r="Z44" s="8" t="n"/>
       <c r="AA44" s="8" t="n"/>
@@ -12141,14 +12261,14 @@
       <c r="P45" s="9" t="n"/>
       <c r="Q45" s="9" t="n"/>
       <c r="R45" s="9" t="n"/>
-      <c r="S45" s="9" t="n"/>
+      <c r="S45" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T45" s="9" t="n"/>
       <c r="U45" s="9" t="n"/>
       <c r="V45" s="9" t="n"/>
       <c r="W45" s="9" t="n"/>
-      <c r="X45" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="X45" s="9" t="n"/>
       <c r="Y45" s="9" t="n"/>
       <c r="Z45" s="9" t="n"/>
       <c r="AA45" s="9" t="n"/>
@@ -12192,14 +12312,14 @@
       <c r="P46" s="8" t="n"/>
       <c r="Q46" s="8" t="n"/>
       <c r="R46" s="8" t="n"/>
-      <c r="S46" s="8" t="n"/>
+      <c r="S46" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T46" s="8" t="n"/>
       <c r="U46" s="8" t="n"/>
       <c r="V46" s="8" t="n"/>
       <c r="W46" s="8" t="n"/>
-      <c r="X46" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="X46" s="8" t="n"/>
       <c r="Y46" s="8" t="n"/>
       <c r="Z46" s="8" t="n"/>
       <c r="AA46" s="8" t="n"/>
@@ -12295,9 +12415,11 @@
       <c r="Q48" s="8" t="n"/>
       <c r="R48" s="8" t="n"/>
       <c r="S48" s="8" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="T48" s="8" t="n"/>
+        <v>0.313</v>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v>0.22</v>
+      </c>
       <c r="U48" s="8" t="n"/>
       <c r="V48" s="8" t="n"/>
       <c r="W48" s="8" t="n"/>
@@ -12313,7 +12435,9 @@
       <c r="AG48" s="8" t="n"/>
       <c r="AH48" s="8" t="n"/>
       <c r="AI48" s="8" t="n"/>
-      <c r="AJ48" s="8" t="n"/>
+      <c r="AJ48" s="8" t="n">
+        <v>0.066</v>
+      </c>
       <c r="AK48" s="8" t="n"/>
       <c r="AL48" s="8" t="n"/>
       <c r="AM48" s="8" t="n"/>
@@ -12346,14 +12470,16 @@
       <c r="Q49" s="9" t="n"/>
       <c r="R49" s="9" t="n"/>
       <c r="S49" s="9" t="n">
-        <v>0.6</v>
+        <v>0.473</v>
       </c>
       <c r="T49" s="9" t="n"/>
       <c r="U49" s="9" t="n"/>
       <c r="V49" s="9" t="n"/>
       <c r="W49" s="9" t="n"/>
       <c r="X49" s="9" t="n"/>
-      <c r="Y49" s="9" t="n"/>
+      <c r="Y49" s="9" t="n">
+        <v>0.127</v>
+      </c>
       <c r="Z49" s="9" t="n"/>
       <c r="AA49" s="9" t="n"/>
       <c r="AB49" s="9" t="n"/>
@@ -12397,7 +12523,7 @@
       <c r="Q50" s="8" t="n"/>
       <c r="R50" s="8" t="n"/>
       <c r="S50" s="8" t="n">
-        <v>0.6</v>
+        <v>0.553</v>
       </c>
       <c r="T50" s="8" t="n"/>
       <c r="U50" s="8" t="n"/>
@@ -12448,7 +12574,7 @@
       <c r="Q51" s="9" t="n"/>
       <c r="R51" s="9" t="n"/>
       <c r="S51" s="9" t="n">
-        <v>0.6</v>
+        <v>0.554</v>
       </c>
       <c r="T51" s="9" t="n"/>
       <c r="U51" s="9" t="n"/>
@@ -12550,7 +12676,7 @@
       <c r="Q53" s="9" t="n"/>
       <c r="R53" s="9" t="n"/>
       <c r="S53" s="9" t="n">
-        <v>0.6</v>
+        <v>0.493</v>
       </c>
       <c r="T53" s="9" t="n"/>
       <c r="U53" s="9" t="n"/>
@@ -12561,9 +12687,13 @@
       <c r="Z53" s="9" t="n"/>
       <c r="AA53" s="9" t="n"/>
       <c r="AB53" s="9" t="n"/>
-      <c r="AC53" s="9" t="n"/>
+      <c r="AC53" s="9" t="n">
+        <v>0.008</v>
+      </c>
       <c r="AD53" s="9" t="n"/>
-      <c r="AE53" s="9" t="n"/>
+      <c r="AE53" s="9" t="n">
+        <v>0.099</v>
+      </c>
       <c r="AF53" s="9" t="n"/>
       <c r="AG53" s="9" t="n"/>
       <c r="AH53" s="9" t="n"/>
@@ -12659,12 +12789,12 @@
       <c r="X55" s="9" t="n"/>
       <c r="Y55" s="9" t="n"/>
       <c r="Z55" s="9" t="n"/>
-      <c r="AA55" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AA55" s="9" t="n"/>
       <c r="AB55" s="9" t="n"/>
       <c r="AC55" s="9" t="n"/>
-      <c r="AD55" s="9" t="n"/>
+      <c r="AD55" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AE55" s="9" t="n"/>
       <c r="AF55" s="9" t="n"/>
       <c r="AG55" s="9" t="n"/>
@@ -12728,7 +12858,7 @@
       <c r="AI56" s="8" t="n"/>
       <c r="AJ56" s="8" t="n"/>
       <c r="AK56" s="8" t="n">
-        <v>15</v>
+        <v>14.713</v>
       </c>
       <c r="AL56" s="8" t="n"/>
       <c r="AM56" s="8" t="n"/>
@@ -12779,7 +12909,7 @@
       <c r="AJ57" s="9" t="n"/>
       <c r="AK57" s="9" t="n"/>
       <c r="AL57" s="9" t="n">
-        <v>10</v>
+        <v>9.702</v>
       </c>
       <c r="AM57" s="9" t="n"/>
       <c r="AN57" s="9" t="n"/>
@@ -12829,7 +12959,7 @@
       <c r="AJ58" s="8" t="n"/>
       <c r="AK58" s="8" t="n"/>
       <c r="AL58" s="8" t="n">
-        <v>14</v>
+        <v>11.167</v>
       </c>
       <c r="AM58" s="8" t="n"/>
       <c r="AN58" s="8" t="n"/>
@@ -12880,7 +13010,7 @@
       <c r="AK59" s="9" t="n"/>
       <c r="AL59" s="9" t="n"/>
       <c r="AM59" s="9" t="n">
-        <v>6</v>
+        <v>5.787</v>
       </c>
       <c r="AN59" s="9" t="n"/>
       <c r="AO59" s="9" t="n"/>
@@ -12928,7 +13058,7 @@
       <c r="AI60" s="8" t="n"/>
       <c r="AJ60" s="8" t="n"/>
       <c r="AK60" s="8" t="n">
-        <v>10</v>
+        <v>8.634</v>
       </c>
       <c r="AL60" s="8" t="n"/>
       <c r="AM60" s="8" t="n"/>
@@ -12978,7 +13108,7 @@
       <c r="AI61" s="9" t="n"/>
       <c r="AJ61" s="9" t="n"/>
       <c r="AK61" s="9" t="n">
-        <v>5</v>
+        <v>6.806</v>
       </c>
       <c r="AL61" s="9" t="n"/>
       <c r="AM61" s="9" t="n"/>
@@ -13029,7 +13159,9 @@
       <c r="AJ62" s="8" t="n"/>
       <c r="AK62" s="8" t="n"/>
       <c r="AL62" s="8" t="n"/>
-      <c r="AM62" s="8" t="n"/>
+      <c r="AM62" s="8" t="n">
+        <v>21.756</v>
+      </c>
       <c r="AN62" s="8" t="n"/>
       <c r="AO62" s="8" t="n"/>
       <c r="AP62" s="8" t="n"/>
@@ -13076,7 +13208,9 @@
       <c r="AI63" s="9" t="n"/>
       <c r="AJ63" s="9" t="n"/>
       <c r="AK63" s="9" t="n"/>
-      <c r="AL63" s="9" t="n"/>
+      <c r="AL63" s="9" t="n">
+        <v>5.867</v>
+      </c>
       <c r="AM63" s="9" t="n"/>
       <c r="AN63" s="9" t="n"/>
       <c r="AO63" s="9" t="n"/>
@@ -13177,7 +13311,7 @@
       <c r="AL65" s="9" t="n"/>
       <c r="AM65" s="9" t="n"/>
       <c r="AN65" s="9" t="n">
-        <v>0.6</v>
+        <v>0.479</v>
       </c>
       <c r="AO65" s="9" t="n"/>
       <c r="AP65" s="9" t="n"/>
@@ -13276,12 +13410,16 @@
       <c r="AK67" s="9" t="n"/>
       <c r="AL67" s="9" t="n"/>
       <c r="AM67" s="9" t="n"/>
-      <c r="AN67" s="9" t="n"/>
+      <c r="AN67" s="9" t="n">
+        <v>0.006</v>
+      </c>
       <c r="AO67" s="9" t="n"/>
       <c r="AP67" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AQ67" s="9" t="n"/>
+        <v>0.443</v>
+      </c>
+      <c r="AQ67" s="9" t="n">
+        <v>0.152</v>
+      </c>
     </row>
     <row r="68" ht="12" customHeight="1" s="19">
       <c r="B68" s="10" t="inlineStr">
@@ -13379,9 +13517,11 @@
       <c r="AN69" s="9" t="n"/>
       <c r="AO69" s="9" t="n"/>
       <c r="AP69" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AQ69" s="9" t="n"/>
+        <v>0.459</v>
+      </c>
+      <c r="AQ69" s="9" t="n">
+        <v>0.141</v>
+      </c>
     </row>
     <row r="70" ht="12" customHeight="1" s="19">
       <c r="B70" s="10" t="inlineStr">
@@ -13426,11 +13566,13 @@
       <c r="AK70" s="8" t="n"/>
       <c r="AL70" s="8" t="n"/>
       <c r="AM70" s="8" t="n"/>
-      <c r="AN70" s="8" t="n"/>
+      <c r="AN70" s="8" t="n">
+        <v>0.104</v>
+      </c>
       <c r="AO70" s="8" t="n"/>
       <c r="AP70" s="8" t="n"/>
       <c r="AQ70" s="8" t="n">
-        <v>0.6</v>
+        <v>0.496</v>
       </c>
     </row>
     <row r="71" ht="12" customHeight="1" s="19">
@@ -13677,10 +13819,12 @@
       <c r="AL75" s="9" t="n"/>
       <c r="AM75" s="9" t="n"/>
       <c r="AN75" s="9" t="n"/>
-      <c r="AO75" s="9" t="n"/>
+      <c r="AO75" s="9" t="n">
+        <v>0.008999999999999999</v>
+      </c>
       <c r="AP75" s="9" t="n"/>
       <c r="AQ75" s="9" t="n">
-        <v>0.6</v>
+        <v>0.5659999999999999</v>
       </c>
     </row>
     <row r="76" ht="12" customHeight="1" s="19">
@@ -13730,7 +13874,7 @@
       <c r="AO76" s="8" t="n"/>
       <c r="AP76" s="8" t="n"/>
       <c r="AQ76" s="8" t="n">
-        <v>0.6</v>
+        <v>0.571</v>
       </c>
     </row>
     <row r="77" ht="12" customHeight="1" s="19">
@@ -13778,9 +13922,11 @@
       <c r="AM77" s="9" t="n"/>
       <c r="AN77" s="9" t="n"/>
       <c r="AO77" s="9" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AP77" s="9" t="n"/>
+        <v>0.233</v>
+      </c>
+      <c r="AP77" s="9" t="n">
+        <v>0.367</v>
+      </c>
       <c r="AQ77" s="9" t="n"/>
     </row>
     <row r="78" ht="12" customHeight="1" s="19">
@@ -13828,7 +13974,7 @@
       <c r="AM78" s="8" t="n"/>
       <c r="AN78" s="8" t="n"/>
       <c r="AO78" s="8" t="n">
-        <v>0.6</v>
+        <v>0.588</v>
       </c>
       <c r="AP78" s="8" t="n"/>
       <c r="AQ78" s="8" t="n"/>
@@ -13876,9 +14022,11 @@
       <c r="AK79" s="9" t="n"/>
       <c r="AL79" s="9" t="n"/>
       <c r="AM79" s="9" t="n"/>
-      <c r="AN79" s="9" t="n"/>
+      <c r="AN79" s="9" t="n">
+        <v>0.06900000000000001</v>
+      </c>
       <c r="AO79" s="9" t="n">
-        <v>0.6</v>
+        <v>0.531</v>
       </c>
       <c r="AP79" s="9" t="n"/>
       <c r="AQ79" s="9" t="n"/>
@@ -13917,10 +14065,10 @@
       <c r="AB80" s="8" t="n"/>
       <c r="AC80" s="8" t="n"/>
       <c r="AD80" s="8" t="n"/>
-      <c r="AE80" s="8" t="n"/>
-      <c r="AF80" s="8" t="n">
+      <c r="AE80" s="8" t="n">
         <v>0.6</v>
       </c>
+      <c r="AF80" s="8" t="n"/>
       <c r="AG80" s="8" t="n"/>
       <c r="AH80" s="8" t="n"/>
       <c r="AI80" s="8" t="n"/>
@@ -13964,13 +14112,13 @@
       <c r="Y81" s="9" t="n"/>
       <c r="Z81" s="9" t="n"/>
       <c r="AA81" s="9" t="n"/>
-      <c r="AB81" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AB81" s="9" t="n"/>
       <c r="AC81" s="9" t="n"/>
       <c r="AD81" s="9" t="n"/>
       <c r="AE81" s="9" t="n"/>
-      <c r="AF81" s="9" t="n"/>
+      <c r="AF81" s="9" t="n">
+        <v>0.585</v>
+      </c>
       <c r="AG81" s="9" t="n"/>
       <c r="AH81" s="9" t="n"/>
       <c r="AI81" s="9" t="n"/>
@@ -14010,14 +14158,14 @@
       <c r="U82" s="8" t="n"/>
       <c r="V82" s="8" t="n"/>
       <c r="W82" s="8" t="n"/>
-      <c r="X82" s="8" t="n"/>
+      <c r="X82" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y82" s="8" t="n"/>
       <c r="Z82" s="8" t="n"/>
       <c r="AA82" s="8" t="n"/>
       <c r="AB82" s="8" t="n"/>
-      <c r="AC82" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AC82" s="8" t="n"/>
       <c r="AD82" s="8" t="n"/>
       <c r="AE82" s="8" t="n"/>
       <c r="AF82" s="8" t="n"/>
@@ -14060,16 +14208,16 @@
       <c r="U83" s="9" t="n"/>
       <c r="V83" s="9" t="n"/>
       <c r="W83" s="9" t="n"/>
-      <c r="X83" s="9" t="n"/>
+      <c r="X83" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y83" s="9" t="n"/>
       <c r="Z83" s="9" t="n"/>
       <c r="AA83" s="9" t="n"/>
       <c r="AB83" s="9" t="n"/>
       <c r="AC83" s="9" t="n"/>
       <c r="AD83" s="9" t="n"/>
-      <c r="AE83" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AE83" s="9" t="n"/>
       <c r="AF83" s="9" t="n"/>
       <c r="AG83" s="9" t="n"/>
       <c r="AH83" s="9" t="n"/>
@@ -14454,15 +14602,13 @@
           <t>A1</t>
         </is>
       </c>
-      <c r="C2" s="8" t="n">
-        <v>6.256</v>
-      </c>
+      <c r="C2" s="8" t="n"/>
       <c r="D2" s="8" t="n"/>
       <c r="E2" s="8" t="n"/>
       <c r="F2" s="8" t="n"/>
       <c r="G2" s="8" t="n"/>
       <c r="H2" s="8" t="n">
-        <v>73.744</v>
+        <v>80</v>
       </c>
       <c r="I2" s="8" t="n"/>
       <c r="J2" s="8" t="n"/>
@@ -14516,16 +14662,16 @@
       <c r="I3" s="9" t="n"/>
       <c r="J3" s="9" t="n"/>
       <c r="K3" s="9" t="n">
-        <v>48.173</v>
+        <v>47.619</v>
       </c>
       <c r="L3" s="9" t="n"/>
       <c r="M3" s="9" t="n"/>
       <c r="N3" s="9" t="n"/>
-      <c r="O3" s="9" t="n"/>
+      <c r="O3" s="9" t="n">
+        <v>7.381</v>
+      </c>
       <c r="P3" s="9" t="n"/>
-      <c r="Q3" s="9" t="n">
-        <v>6.203</v>
-      </c>
+      <c r="Q3" s="9" t="n"/>
       <c r="R3" s="9" t="n"/>
       <c r="S3" s="9" t="n"/>
       <c r="T3" s="9" t="n"/>
@@ -14562,14 +14708,12 @@
       </c>
       <c r="C4" s="8" t="n"/>
       <c r="D4" s="8" t="n">
-        <v>24.158</v>
+        <v>35</v>
       </c>
       <c r="E4" s="8" t="n"/>
       <c r="F4" s="8" t="n"/>
       <c r="G4" s="8" t="n"/>
-      <c r="H4" s="8" t="n">
-        <v>10.842</v>
-      </c>
+      <c r="H4" s="8" t="n"/>
       <c r="I4" s="8" t="n"/>
       <c r="J4" s="8" t="n"/>
       <c r="K4" s="8" t="n"/>
@@ -14667,7 +14811,7 @@
       <c r="C6" s="8" t="n"/>
       <c r="D6" s="8" t="n"/>
       <c r="E6" s="8" t="n">
-        <v>56.505</v>
+        <v>56</v>
       </c>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="n"/>
@@ -14677,7 +14821,7 @@
       <c r="K6" s="8" t="n"/>
       <c r="L6" s="8" t="n"/>
       <c r="M6" s="8" t="n">
-        <v>11.495</v>
+        <v>12</v>
       </c>
       <c r="N6" s="8" t="n"/>
       <c r="O6" s="8" t="n"/>
@@ -14717,16 +14861,14 @@
           <t>A6</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n">
-        <v>14.746</v>
-      </c>
+      <c r="C7" s="9" t="n"/>
       <c r="D7" s="9" t="n"/>
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="9" t="n"/>
       <c r="G7" s="9" t="n"/>
       <c r="H7" s="9" t="n"/>
       <c r="I7" s="9" t="n">
-        <v>40.254</v>
+        <v>55</v>
       </c>
       <c r="J7" s="9" t="n"/>
       <c r="K7" s="9" t="n"/>
@@ -14821,15 +14963,13 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n">
-        <v>1.243</v>
-      </c>
+      <c r="C9" s="9" t="n"/>
       <c r="D9" s="9" t="n"/>
       <c r="E9" s="9" t="n"/>
       <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="n"/>
       <c r="H9" s="9" t="n">
-        <v>44.757</v>
+        <v>46</v>
       </c>
       <c r="I9" s="9" t="n"/>
       <c r="J9" s="9" t="n"/>
@@ -14875,15 +15015,15 @@
         </is>
       </c>
       <c r="C10" s="8" t="n"/>
-      <c r="D10" s="8" t="n">
-        <v>40</v>
-      </c>
+      <c r="D10" s="8" t="n"/>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
       <c r="H10" s="8" t="n"/>
       <c r="I10" s="8" t="n"/>
-      <c r="J10" s="8" t="n"/>
+      <c r="J10" s="8" t="n">
+        <v>40</v>
+      </c>
       <c r="K10" s="8" t="n"/>
       <c r="L10" s="8" t="n"/>
       <c r="M10" s="8" t="n"/>
@@ -14925,15 +15065,13 @@
           <t>B4</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n">
-        <v>2.444</v>
-      </c>
+      <c r="C11" s="9" t="n"/>
       <c r="D11" s="9" t="n"/>
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="9" t="n"/>
       <c r="H11" s="9" t="n">
-        <v>25.556</v>
+        <v>28</v>
       </c>
       <c r="I11" s="9" t="n"/>
       <c r="J11" s="9" t="n"/>
@@ -14978,9 +15116,7 @@
           <t>B5</t>
         </is>
       </c>
-      <c r="C12" s="8" t="n">
-        <v>2.181</v>
-      </c>
+      <c r="C12" s="8" t="n"/>
       <c r="D12" s="8" t="n"/>
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
@@ -14990,7 +15126,7 @@
       <c r="J12" s="8" t="n"/>
       <c r="K12" s="8" t="n"/>
       <c r="L12" s="8" t="n">
-        <v>22.819</v>
+        <v>25</v>
       </c>
       <c r="M12" s="8" t="n"/>
       <c r="N12" s="8" t="n"/>
@@ -15086,7 +15222,7 @@
       <c r="D14" s="8" t="n"/>
       <c r="E14" s="8" t="n"/>
       <c r="F14" s="8" t="n">
-        <v>53.287</v>
+        <v>55</v>
       </c>
       <c r="G14" s="8" t="n"/>
       <c r="H14" s="8" t="n"/>
@@ -15133,9 +15269,7 @@
           <t>B8</t>
         </is>
       </c>
-      <c r="C15" s="9" t="n">
-        <v>13.81</v>
-      </c>
+      <c r="C15" s="9" t="n"/>
       <c r="D15" s="9" t="n"/>
       <c r="E15" s="9" t="n"/>
       <c r="F15" s="9" t="n"/>
@@ -15143,7 +15277,7 @@
       <c r="H15" s="9" t="n"/>
       <c r="I15" s="9" t="n"/>
       <c r="J15" s="9" t="n">
-        <v>30.19</v>
+        <v>44</v>
       </c>
       <c r="K15" s="9" t="n"/>
       <c r="L15" s="9" t="n"/>
@@ -15190,7 +15324,7 @@
       <c r="D16" s="8" t="n"/>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n">
-        <v>34.094</v>
+        <v>45.121</v>
       </c>
       <c r="G16" s="8" t="n"/>
       <c r="H16" s="8" t="n"/>
@@ -15201,7 +15335,7 @@
       <c r="M16" s="8" t="n"/>
       <c r="N16" s="8" t="n"/>
       <c r="O16" s="8" t="n">
-        <v>15.906</v>
+        <v>4.879</v>
       </c>
       <c r="P16" s="8" t="n"/>
       <c r="Q16" s="8" t="n"/>
@@ -15240,11 +15374,13 @@
         </is>
       </c>
       <c r="C17" s="9" t="n"/>
-      <c r="D17" s="9" t="n"/>
+      <c r="D17" s="9" t="n">
+        <v>12.5</v>
+      </c>
       <c r="E17" s="9" t="n"/>
       <c r="F17" s="9" t="n"/>
       <c r="G17" s="9" t="n">
-        <v>25</v>
+        <v>12.5</v>
       </c>
       <c r="H17" s="9" t="n"/>
       <c r="I17" s="9" t="n"/>
@@ -15348,15 +15484,17 @@
       <c r="G19" s="9" t="n"/>
       <c r="H19" s="9" t="n"/>
       <c r="I19" s="9" t="n"/>
-      <c r="J19" s="9" t="n">
-        <v>45</v>
-      </c>
+      <c r="J19" s="9" t="n"/>
       <c r="K19" s="9" t="n"/>
       <c r="L19" s="9" t="n"/>
       <c r="M19" s="9" t="n"/>
-      <c r="N19" s="9" t="n"/>
+      <c r="N19" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="O19" s="9" t="n"/>
-      <c r="P19" s="9" t="n"/>
+      <c r="P19" s="9" t="n">
+        <v>35</v>
+      </c>
       <c r="Q19" s="9" t="n"/>
       <c r="R19" s="9" t="n"/>
       <c r="S19" s="9" t="n"/>
@@ -15393,21 +15531,27 @@
         </is>
       </c>
       <c r="C20" s="8" t="n"/>
-      <c r="D20" s="8" t="n"/>
+      <c r="D20" s="8" t="n">
+        <v>9.157999999999999</v>
+      </c>
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
       <c r="H20" s="8" t="n"/>
-      <c r="I20" s="8" t="n"/>
-      <c r="J20" s="8" t="n"/>
+      <c r="I20" s="8" t="n">
+        <v>3.416</v>
+      </c>
+      <c r="J20" s="8" t="n">
+        <v>17.895</v>
+      </c>
       <c r="K20" s="8" t="n"/>
       <c r="L20" s="8" t="n"/>
       <c r="M20" s="8" t="n"/>
       <c r="N20" s="8" t="n"/>
-      <c r="O20" s="8" t="n"/>
-      <c r="P20" s="8" t="n">
-        <v>35</v>
-      </c>
+      <c r="O20" s="8" t="n">
+        <v>4.532</v>
+      </c>
+      <c r="P20" s="8" t="n"/>
       <c r="Q20" s="8" t="n"/>
       <c r="R20" s="8" t="n"/>
       <c r="S20" s="8" t="n"/>
@@ -15444,7 +15588,7 @@
         </is>
       </c>
       <c r="C21" s="9" t="n">
-        <v>17.84</v>
+        <v>20</v>
       </c>
       <c r="D21" s="9" t="n"/>
       <c r="E21" s="9" t="n"/>
@@ -15501,16 +15645,16 @@
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n"/>
       <c r="I22" s="8" t="n"/>
-      <c r="J22" s="8" t="n">
-        <v>15</v>
-      </c>
+      <c r="J22" s="8" t="n"/>
       <c r="K22" s="8" t="n"/>
       <c r="L22" s="8" t="n"/>
       <c r="M22" s="8" t="n"/>
       <c r="N22" s="8" t="n"/>
       <c r="O22" s="8" t="n"/>
       <c r="P22" s="8" t="n"/>
-      <c r="Q22" s="8" t="n"/>
+      <c r="Q22" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="R22" s="8" t="n"/>
       <c r="S22" s="8" t="n"/>
       <c r="T22" s="8" t="n"/>
@@ -15549,16 +15693,16 @@
       <c r="D23" s="9" t="n"/>
       <c r="E23" s="9" t="n"/>
       <c r="F23" s="9" t="n"/>
-      <c r="G23" s="9" t="n"/>
+      <c r="G23" s="9" t="n">
+        <v>13</v>
+      </c>
       <c r="H23" s="9" t="n"/>
       <c r="I23" s="9" t="n"/>
       <c r="J23" s="9" t="n"/>
       <c r="K23" s="9" t="n"/>
       <c r="L23" s="9" t="n"/>
       <c r="M23" s="9" t="n"/>
-      <c r="N23" s="9" t="n">
-        <v>13</v>
-      </c>
+      <c r="N23" s="9" t="n"/>
       <c r="O23" s="9" t="n"/>
       <c r="P23" s="9" t="n"/>
       <c r="Q23" s="9" t="n"/>
@@ -15597,7 +15741,7 @@
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>7.284</v>
+        <v>15</v>
       </c>
       <c r="D24" s="8" t="n"/>
       <c r="E24" s="8" t="n"/>
@@ -15653,14 +15797,18 @@
       <c r="F25" s="9" t="n"/>
       <c r="G25" s="9" t="n"/>
       <c r="H25" s="9" t="n"/>
-      <c r="I25" s="9" t="n"/>
-      <c r="J25" s="9" t="n">
-        <v>18</v>
-      </c>
+      <c r="I25" s="9" t="n">
+        <v>2.783</v>
+      </c>
+      <c r="J25" s="9" t="n"/>
       <c r="K25" s="9" t="n"/>
       <c r="L25" s="9" t="n"/>
-      <c r="M25" s="9" t="n"/>
-      <c r="N25" s="9" t="n"/>
+      <c r="M25" s="9" t="n">
+        <v>1.797</v>
+      </c>
+      <c r="N25" s="9" t="n">
+        <v>2.444</v>
+      </c>
       <c r="O25" s="9" t="n"/>
       <c r="P25" s="9" t="n"/>
       <c r="Q25" s="9" t="n"/>
@@ -15703,10 +15851,10 @@
       <c r="E26" s="8" t="n"/>
       <c r="F26" s="8" t="n"/>
       <c r="G26" s="8" t="n"/>
-      <c r="H26" s="8" t="n"/>
-      <c r="I26" s="8" t="n">
+      <c r="H26" s="8" t="n">
         <v>27</v>
       </c>
+      <c r="I26" s="8" t="n"/>
       <c r="J26" s="8" t="n"/>
       <c r="K26" s="8" t="n"/>
       <c r="L26" s="8" t="n"/>
@@ -15754,9 +15902,7 @@
       <c r="E27" s="9" t="n"/>
       <c r="F27" s="9" t="n"/>
       <c r="G27" s="9" t="n"/>
-      <c r="H27" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="H27" s="9" t="n"/>
       <c r="I27" s="9" t="n"/>
       <c r="J27" s="9" t="n"/>
       <c r="K27" s="9" t="n"/>
@@ -15817,7 +15963,7 @@
       <c r="Q28" s="8" t="n"/>
       <c r="R28" s="8" t="n"/>
       <c r="S28" s="8" t="n">
-        <v>3.662</v>
+        <v>4.587</v>
       </c>
       <c r="T28" s="8" t="n"/>
       <c r="U28" s="8" t="n"/>
@@ -15830,7 +15976,7 @@
       <c r="AB28" s="8" t="n"/>
       <c r="AC28" s="8" t="n"/>
       <c r="AD28" s="8" t="n">
-        <v>11.338</v>
+        <v>10.413</v>
       </c>
       <c r="AE28" s="8" t="n"/>
       <c r="AF28" s="8" t="n"/>
@@ -15870,12 +16016,14 @@
       <c r="Q29" s="9" t="n"/>
       <c r="R29" s="9" t="n"/>
       <c r="S29" s="9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T29" s="9" t="n"/>
       <c r="U29" s="9" t="n"/>
       <c r="V29" s="9" t="n"/>
-      <c r="W29" s="9" t="n"/>
+      <c r="W29" s="9" t="n">
+        <v>5</v>
+      </c>
       <c r="X29" s="9" t="n"/>
       <c r="Y29" s="9" t="n"/>
       <c r="Z29" s="9" t="n"/>
@@ -15922,18 +16070,20 @@
       <c r="R30" s="8" t="n"/>
       <c r="S30" s="8" t="n"/>
       <c r="T30" s="8" t="n">
-        <v>7.014</v>
+        <v>13.44</v>
       </c>
       <c r="U30" s="8" t="n"/>
       <c r="V30" s="8" t="n"/>
       <c r="W30" s="8" t="n"/>
       <c r="X30" s="8" t="n">
-        <v>6.986</v>
+        <v>0.3</v>
       </c>
       <c r="Y30" s="8" t="n"/>
       <c r="Z30" s="8" t="n"/>
       <c r="AA30" s="8" t="n"/>
-      <c r="AB30" s="8" t="n"/>
+      <c r="AB30" s="8" t="n">
+        <v>0.26</v>
+      </c>
       <c r="AC30" s="8" t="n"/>
       <c r="AD30" s="8" t="n"/>
       <c r="AE30" s="8" t="n"/>
@@ -16026,17 +16176,23 @@
       <c r="R32" s="8" t="n"/>
       <c r="S32" s="8" t="n"/>
       <c r="T32" s="8" t="n"/>
-      <c r="U32" s="8" t="n"/>
+      <c r="U32" s="8" t="n">
+        <v>2.16</v>
+      </c>
       <c r="V32" s="8" t="n"/>
-      <c r="W32" s="8" t="n">
-        <v>10</v>
-      </c>
+      <c r="W32" s="8" t="n"/>
       <c r="X32" s="8" t="n"/>
       <c r="Y32" s="8" t="n"/>
-      <c r="Z32" s="8" t="n"/>
-      <c r="AA32" s="8" t="n"/>
+      <c r="Z32" s="8" t="n">
+        <v>1.088</v>
+      </c>
+      <c r="AA32" s="8" t="n">
+        <v>1.091</v>
+      </c>
       <c r="AB32" s="8" t="n"/>
-      <c r="AC32" s="8" t="n"/>
+      <c r="AC32" s="8" t="n">
+        <v>0.439</v>
+      </c>
       <c r="AD32" s="8" t="n"/>
       <c r="AE32" s="8" t="n"/>
       <c r="AF32" s="8" t="n"/>
@@ -16081,7 +16237,9 @@
       <c r="V33" s="9" t="n"/>
       <c r="W33" s="9" t="n"/>
       <c r="X33" s="9" t="n"/>
-      <c r="Y33" s="9" t="n"/>
+      <c r="Y33" s="9" t="n">
+        <v>0.333</v>
+      </c>
       <c r="Z33" s="9" t="n"/>
       <c r="AA33" s="9" t="n"/>
       <c r="AB33" s="9" t="n"/>
@@ -16090,13 +16248,15 @@
       <c r="AE33" s="9" t="n"/>
       <c r="AF33" s="9" t="n"/>
       <c r="AG33" s="9" t="n">
-        <v>2.42</v>
+        <v>0.75</v>
       </c>
       <c r="AH33" s="9" t="n"/>
       <c r="AI33" s="9" t="n">
-        <v>0.376</v>
-      </c>
-      <c r="AJ33" s="9" t="n"/>
+        <v>0.36</v>
+      </c>
+      <c r="AJ33" s="9" t="n">
+        <v>0.327</v>
+      </c>
       <c r="AK33" s="9" t="n"/>
       <c r="AL33" s="9" t="n"/>
       <c r="AM33" s="9" t="n"/>
@@ -16129,19 +16289,21 @@
       <c r="Q34" s="8" t="n"/>
       <c r="R34" s="8" t="n"/>
       <c r="S34" s="8" t="n">
-        <v>3.095</v>
+        <v>0.18</v>
       </c>
       <c r="T34" s="8" t="n"/>
       <c r="U34" s="8" t="n"/>
       <c r="V34" s="8" t="n">
-        <v>18.905</v>
+        <v>15</v>
       </c>
       <c r="W34" s="8" t="n"/>
       <c r="X34" s="8" t="n"/>
       <c r="Y34" s="8" t="n"/>
       <c r="Z34" s="8" t="n"/>
       <c r="AA34" s="8" t="n"/>
-      <c r="AB34" s="8" t="n"/>
+      <c r="AB34" s="8" t="n">
+        <v>0.17</v>
+      </c>
       <c r="AC34" s="8" t="n"/>
       <c r="AD34" s="8" t="n"/>
       <c r="AE34" s="8" t="n"/>
@@ -16180,10 +16342,10 @@
       <c r="O35" s="9" t="n"/>
       <c r="P35" s="9" t="n"/>
       <c r="Q35" s="9" t="n"/>
-      <c r="R35" s="9" t="n"/>
-      <c r="S35" s="9" t="n">
+      <c r="R35" s="9" t="n">
         <v>20</v>
       </c>
+      <c r="S35" s="9" t="n"/>
       <c r="T35" s="9" t="n"/>
       <c r="U35" s="9" t="n"/>
       <c r="V35" s="9" t="n"/>
@@ -16232,9 +16394,7 @@
       <c r="P36" s="8" t="n"/>
       <c r="Q36" s="8" t="n"/>
       <c r="R36" s="8" t="n"/>
-      <c r="S36" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S36" s="8" t="n"/>
       <c r="T36" s="8" t="n"/>
       <c r="U36" s="8" t="n"/>
       <c r="V36" s="8" t="n"/>
@@ -16246,7 +16406,9 @@
       <c r="AB36" s="8" t="n"/>
       <c r="AC36" s="8" t="n"/>
       <c r="AD36" s="8" t="n"/>
-      <c r="AE36" s="8" t="n"/>
+      <c r="AE36" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AF36" s="8" t="n"/>
       <c r="AG36" s="8" t="n"/>
       <c r="AH36" s="8" t="n"/>
@@ -16283,24 +16445,28 @@
       <c r="P37" s="9" t="n"/>
       <c r="Q37" s="9" t="n"/>
       <c r="R37" s="9" t="n"/>
-      <c r="S37" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S37" s="9" t="n"/>
       <c r="T37" s="9" t="n"/>
       <c r="U37" s="9" t="n"/>
       <c r="V37" s="9" t="n"/>
       <c r="W37" s="9" t="n"/>
-      <c r="X37" s="9" t="n"/>
+      <c r="X37" s="9" t="n">
+        <v>0.03</v>
+      </c>
       <c r="Y37" s="9" t="n"/>
       <c r="Z37" s="9" t="n"/>
       <c r="AA37" s="9" t="n"/>
       <c r="AB37" s="9" t="n"/>
       <c r="AC37" s="9" t="n"/>
       <c r="AD37" s="9" t="n"/>
-      <c r="AE37" s="9" t="n"/>
+      <c r="AE37" s="9" t="n">
+        <v>0.27</v>
+      </c>
       <c r="AF37" s="9" t="n"/>
       <c r="AG37" s="9" t="n"/>
-      <c r="AH37" s="9" t="n"/>
+      <c r="AH37" s="9" t="n">
+        <v>0.3</v>
+      </c>
       <c r="AI37" s="9" t="n"/>
       <c r="AJ37" s="9" t="n"/>
       <c r="AK37" s="9" t="n"/>
@@ -16334,14 +16500,14 @@
       <c r="P38" s="8" t="n"/>
       <c r="Q38" s="8" t="n"/>
       <c r="R38" s="8" t="n"/>
-      <c r="S38" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S38" s="8" t="n"/>
       <c r="T38" s="8" t="n"/>
       <c r="U38" s="8" t="n"/>
       <c r="V38" s="8" t="n"/>
       <c r="W38" s="8" t="n"/>
-      <c r="X38" s="8" t="n"/>
+      <c r="X38" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y38" s="8" t="n"/>
       <c r="Z38" s="8" t="n"/>
       <c r="AA38" s="8" t="n"/>
@@ -16385,14 +16551,14 @@
       <c r="P39" s="9" t="n"/>
       <c r="Q39" s="9" t="n"/>
       <c r="R39" s="9" t="n"/>
-      <c r="S39" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S39" s="9" t="n"/>
       <c r="T39" s="9" t="n"/>
       <c r="U39" s="9" t="n"/>
       <c r="V39" s="9" t="n"/>
       <c r="W39" s="9" t="n"/>
-      <c r="X39" s="9" t="n"/>
+      <c r="X39" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y39" s="9" t="n"/>
       <c r="Z39" s="9" t="n"/>
       <c r="AA39" s="9" t="n"/>
@@ -16436,14 +16602,14 @@
       <c r="P40" s="8" t="n"/>
       <c r="Q40" s="8" t="n"/>
       <c r="R40" s="8" t="n"/>
-      <c r="S40" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S40" s="8" t="n"/>
       <c r="T40" s="8" t="n"/>
       <c r="U40" s="8" t="n"/>
       <c r="V40" s="8" t="n"/>
       <c r="W40" s="8" t="n"/>
-      <c r="X40" s="8" t="n"/>
+      <c r="X40" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y40" s="8" t="n"/>
       <c r="Z40" s="8" t="n"/>
       <c r="AA40" s="8" t="n"/>
@@ -16487,16 +16653,14 @@
       <c r="P41" s="9" t="n"/>
       <c r="Q41" s="9" t="n"/>
       <c r="R41" s="9" t="n"/>
-      <c r="S41" s="9" t="n">
-        <v>0.048</v>
-      </c>
+      <c r="S41" s="9" t="n"/>
       <c r="T41" s="9" t="n"/>
       <c r="U41" s="9" t="n"/>
       <c r="V41" s="9" t="n"/>
-      <c r="W41" s="9" t="n">
-        <v>0.552</v>
-      </c>
-      <c r="X41" s="9" t="n"/>
+      <c r="W41" s="9" t="n"/>
+      <c r="X41" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y41" s="9" t="n"/>
       <c r="Z41" s="9" t="n"/>
       <c r="AA41" s="9" t="n"/>
@@ -16540,16 +16704,14 @@
       <c r="P42" s="8" t="n"/>
       <c r="Q42" s="8" t="n"/>
       <c r="R42" s="8" t="n"/>
-      <c r="S42" s="8" t="n">
-        <v>0.06</v>
-      </c>
+      <c r="S42" s="8" t="n"/>
       <c r="T42" s="8" t="n"/>
       <c r="U42" s="8" t="n"/>
       <c r="V42" s="8" t="n"/>
-      <c r="W42" s="8" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="X42" s="8" t="n"/>
+      <c r="W42" s="8" t="n"/>
+      <c r="X42" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y42" s="8" t="n"/>
       <c r="Z42" s="8" t="n"/>
       <c r="AA42" s="8" t="n"/>
@@ -16593,14 +16755,14 @@
       <c r="P43" s="9" t="n"/>
       <c r="Q43" s="9" t="n"/>
       <c r="R43" s="9" t="n"/>
-      <c r="S43" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S43" s="9" t="n"/>
       <c r="T43" s="9" t="n"/>
       <c r="U43" s="9" t="n"/>
       <c r="V43" s="9" t="n"/>
       <c r="W43" s="9" t="n"/>
-      <c r="X43" s="9" t="n"/>
+      <c r="X43" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y43" s="9" t="n"/>
       <c r="Z43" s="9" t="n"/>
       <c r="AA43" s="9" t="n"/>
@@ -16644,16 +16806,14 @@
       <c r="P44" s="8" t="n"/>
       <c r="Q44" s="8" t="n"/>
       <c r="R44" s="8" t="n"/>
-      <c r="S44" s="8" t="n">
-        <v>0.273</v>
-      </c>
+      <c r="S44" s="8" t="n"/>
       <c r="T44" s="8" t="n"/>
       <c r="U44" s="8" t="n"/>
       <c r="V44" s="8" t="n"/>
-      <c r="W44" s="8" t="n">
-        <v>0.327</v>
-      </c>
-      <c r="X44" s="8" t="n"/>
+      <c r="W44" s="8" t="n"/>
+      <c r="X44" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y44" s="8" t="n"/>
       <c r="Z44" s="8" t="n"/>
       <c r="AA44" s="8" t="n"/>
@@ -16697,16 +16857,14 @@
       <c r="P45" s="9" t="n"/>
       <c r="Q45" s="9" t="n"/>
       <c r="R45" s="9" t="n"/>
-      <c r="S45" s="9" t="n">
-        <v>0.176</v>
-      </c>
+      <c r="S45" s="9" t="n"/>
       <c r="T45" s="9" t="n"/>
       <c r="U45" s="9" t="n"/>
       <c r="V45" s="9" t="n"/>
-      <c r="W45" s="9" t="n">
-        <v>0.405</v>
-      </c>
-      <c r="X45" s="9" t="n"/>
+      <c r="W45" s="9" t="n"/>
+      <c r="X45" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y45" s="9" t="n"/>
       <c r="Z45" s="9" t="n"/>
       <c r="AA45" s="9" t="n"/>
@@ -16750,14 +16908,14 @@
       <c r="P46" s="8" t="n"/>
       <c r="Q46" s="8" t="n"/>
       <c r="R46" s="8" t="n"/>
-      <c r="S46" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S46" s="8" t="n"/>
       <c r="T46" s="8" t="n"/>
       <c r="U46" s="8" t="n"/>
       <c r="V46" s="8" t="n"/>
       <c r="W46" s="8" t="n"/>
-      <c r="X46" s="8" t="n"/>
+      <c r="X46" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y46" s="8" t="n"/>
       <c r="Z46" s="8" t="n"/>
       <c r="AA46" s="8" t="n"/>
@@ -16801,10 +16959,10 @@
       <c r="P47" s="9" t="n"/>
       <c r="Q47" s="9" t="n"/>
       <c r="R47" s="9" t="n"/>
-      <c r="S47" s="9" t="n"/>
-      <c r="T47" s="9" t="n">
-        <v>0.389</v>
-      </c>
+      <c r="S47" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T47" s="9" t="n"/>
       <c r="U47" s="9" t="n"/>
       <c r="V47" s="9" t="n"/>
       <c r="W47" s="9" t="n"/>
@@ -16852,10 +17010,10 @@
       <c r="P48" s="8" t="n"/>
       <c r="Q48" s="8" t="n"/>
       <c r="R48" s="8" t="n"/>
-      <c r="S48" s="8" t="n"/>
-      <c r="T48" s="8" t="n">
+      <c r="S48" s="8" t="n">
         <v>0.6</v>
       </c>
+      <c r="T48" s="8" t="n"/>
       <c r="U48" s="8" t="n"/>
       <c r="V48" s="8" t="n"/>
       <c r="W48" s="8" t="n"/>
@@ -16903,10 +17061,10 @@
       <c r="P49" s="9" t="n"/>
       <c r="Q49" s="9" t="n"/>
       <c r="R49" s="9" t="n"/>
-      <c r="S49" s="9" t="n"/>
-      <c r="T49" s="9" t="n">
-        <v>0.518</v>
-      </c>
+      <c r="S49" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T49" s="9" t="n"/>
       <c r="U49" s="9" t="n"/>
       <c r="V49" s="9" t="n"/>
       <c r="W49" s="9" t="n"/>
@@ -16954,10 +17112,10 @@
       <c r="P50" s="8" t="n"/>
       <c r="Q50" s="8" t="n"/>
       <c r="R50" s="8" t="n"/>
-      <c r="S50" s="8" t="n"/>
-      <c r="T50" s="8" t="n">
-        <v>0.553</v>
-      </c>
+      <c r="S50" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T50" s="8" t="n"/>
       <c r="U50" s="8" t="n"/>
       <c r="V50" s="8" t="n"/>
       <c r="W50" s="8" t="n"/>
@@ -17005,10 +17163,10 @@
       <c r="P51" s="9" t="n"/>
       <c r="Q51" s="9" t="n"/>
       <c r="R51" s="9" t="n"/>
-      <c r="S51" s="9" t="n"/>
-      <c r="T51" s="9" t="n">
-        <v>0.491</v>
-      </c>
+      <c r="S51" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T51" s="9" t="n"/>
       <c r="U51" s="9" t="n"/>
       <c r="V51" s="9" t="n"/>
       <c r="W51" s="9" t="n"/>
@@ -17019,9 +17177,7 @@
       <c r="AB51" s="9" t="n"/>
       <c r="AC51" s="9" t="n"/>
       <c r="AD51" s="9" t="n"/>
-      <c r="AE51" s="9" t="n">
-        <v>0.067</v>
-      </c>
+      <c r="AE51" s="9" t="n"/>
       <c r="AF51" s="9" t="n"/>
       <c r="AG51" s="9" t="n"/>
       <c r="AH51" s="9" t="n"/>
@@ -17058,7 +17214,9 @@
       <c r="P52" s="8" t="n"/>
       <c r="Q52" s="8" t="n"/>
       <c r="R52" s="8" t="n"/>
-      <c r="S52" s="8" t="n"/>
+      <c r="S52" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T52" s="8" t="n"/>
       <c r="U52" s="8" t="n"/>
       <c r="V52" s="8" t="n"/>
@@ -17068,9 +17226,7 @@
       <c r="Z52" s="8" t="n"/>
       <c r="AA52" s="8" t="n"/>
       <c r="AB52" s="8" t="n"/>
-      <c r="AC52" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AC52" s="8" t="n"/>
       <c r="AD52" s="8" t="n"/>
       <c r="AE52" s="8" t="n"/>
       <c r="AF52" s="8" t="n"/>
@@ -17109,10 +17265,10 @@
       <c r="P53" s="9" t="n"/>
       <c r="Q53" s="9" t="n"/>
       <c r="R53" s="9" t="n"/>
-      <c r="S53" s="9" t="n"/>
-      <c r="T53" s="9" t="n">
+      <c r="S53" s="9" t="n">
         <v>0.6</v>
       </c>
+      <c r="T53" s="9" t="n"/>
       <c r="U53" s="9" t="n"/>
       <c r="V53" s="9" t="n"/>
       <c r="W53" s="9" t="n"/>
@@ -17160,7 +17316,9 @@
       <c r="P54" s="8" t="n"/>
       <c r="Q54" s="8" t="n"/>
       <c r="R54" s="8" t="n"/>
-      <c r="S54" s="8" t="n"/>
+      <c r="S54" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T54" s="8" t="n"/>
       <c r="U54" s="8" t="n"/>
       <c r="V54" s="8" t="n"/>
@@ -17175,9 +17333,7 @@
       <c r="AE54" s="8" t="n"/>
       <c r="AF54" s="8" t="n"/>
       <c r="AG54" s="8" t="n"/>
-      <c r="AH54" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AH54" s="8" t="n"/>
       <c r="AI54" s="8" t="n"/>
       <c r="AJ54" s="8" t="n"/>
       <c r="AK54" s="8" t="n"/>
@@ -17220,11 +17376,11 @@
       <c r="Y55" s="9" t="n"/>
       <c r="Z55" s="9" t="n"/>
       <c r="AA55" s="9" t="n"/>
-      <c r="AB55" s="9" t="n">
+      <c r="AB55" s="9" t="n"/>
+      <c r="AC55" s="9" t="n"/>
+      <c r="AD55" s="9" t="n">
         <v>0.6</v>
       </c>
-      <c r="AC55" s="9" t="n"/>
-      <c r="AD55" s="9" t="n"/>
       <c r="AE55" s="9" t="n"/>
       <c r="AF55" s="9" t="n"/>
       <c r="AG55" s="9" t="n"/>
@@ -17337,10 +17493,10 @@
       <c r="AH57" s="9" t="n"/>
       <c r="AI57" s="9" t="n"/>
       <c r="AJ57" s="9" t="n"/>
-      <c r="AK57" s="9" t="n"/>
-      <c r="AL57" s="9" t="n">
+      <c r="AK57" s="9" t="n">
         <v>10</v>
       </c>
+      <c r="AL57" s="9" t="n"/>
       <c r="AM57" s="9" t="n"/>
       <c r="AN57" s="9" t="n"/>
       <c r="AO57" s="9" t="n"/>
@@ -17388,7 +17544,7 @@
       <c r="AI58" s="8" t="n"/>
       <c r="AJ58" s="8" t="n"/>
       <c r="AK58" s="8" t="n">
-        <v>13.882</v>
+        <v>14</v>
       </c>
       <c r="AL58" s="8" t="n"/>
       <c r="AM58" s="8" t="n"/>
@@ -17540,7 +17696,7 @@
       <c r="AK61" s="9" t="n"/>
       <c r="AL61" s="9" t="n"/>
       <c r="AM61" s="9" t="n">
-        <v>11.772</v>
+        <v>12</v>
       </c>
       <c r="AN61" s="9" t="n"/>
       <c r="AO61" s="9" t="n"/>
@@ -17588,7 +17744,7 @@
       <c r="AI62" s="8" t="n"/>
       <c r="AJ62" s="8" t="n"/>
       <c r="AK62" s="8" t="n">
-        <v>1.955</v>
+        <v>22</v>
       </c>
       <c r="AL62" s="8" t="n"/>
       <c r="AM62" s="8" t="n"/>
@@ -17637,9 +17793,7 @@
       <c r="AH63" s="9" t="n"/>
       <c r="AI63" s="9" t="n"/>
       <c r="AJ63" s="9" t="n"/>
-      <c r="AK63" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="AK63" s="9" t="n"/>
       <c r="AL63" s="9" t="n"/>
       <c r="AM63" s="9" t="n"/>
       <c r="AN63" s="9" t="n"/>
@@ -17690,12 +17844,12 @@
       <c r="AK64" s="8" t="n"/>
       <c r="AL64" s="8" t="n"/>
       <c r="AM64" s="8" t="n"/>
-      <c r="AN64" s="8" t="n"/>
+      <c r="AN64" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AO64" s="8" t="n"/>
       <c r="AP64" s="8" t="n"/>
-      <c r="AQ64" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AQ64" s="8" t="n"/>
     </row>
     <row r="65" ht="12" customHeight="1" s="19">
       <c r="B65" s="10" t="inlineStr">
@@ -17790,11 +17944,11 @@
       <c r="AK66" s="8" t="n"/>
       <c r="AL66" s="8" t="n"/>
       <c r="AM66" s="8" t="n"/>
-      <c r="AN66" s="8" t="n"/>
+      <c r="AN66" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AO66" s="8" t="n"/>
-      <c r="AP66" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AP66" s="8" t="n"/>
       <c r="AQ66" s="8" t="n"/>
     </row>
     <row r="67" ht="12" customHeight="1" s="19">
@@ -17842,10 +17996,10 @@
       <c r="AM67" s="9" t="n"/>
       <c r="AN67" s="9" t="n"/>
       <c r="AO67" s="9" t="n"/>
-      <c r="AP67" s="9" t="n"/>
-      <c r="AQ67" s="9" t="n">
+      <c r="AP67" s="9" t="n">
         <v>0.6</v>
       </c>
+      <c r="AQ67" s="9" t="n"/>
     </row>
     <row r="68" ht="12" customHeight="1" s="19">
       <c r="B68" s="10" t="inlineStr">
@@ -17890,12 +18044,10 @@
       <c r="AK68" s="8" t="n"/>
       <c r="AL68" s="8" t="n"/>
       <c r="AM68" s="8" t="n"/>
-      <c r="AN68" s="8" t="n">
-        <v>0.118</v>
-      </c>
+      <c r="AN68" s="8" t="n"/>
       <c r="AO68" s="8" t="n"/>
       <c r="AP68" s="8" t="n">
-        <v>0.482</v>
+        <v>0.6</v>
       </c>
       <c r="AQ68" s="8" t="n"/>
     </row>
@@ -17942,12 +18094,10 @@
       <c r="AK69" s="9" t="n"/>
       <c r="AL69" s="9" t="n"/>
       <c r="AM69" s="9" t="n"/>
-      <c r="AN69" s="9" t="n">
-        <v>0.191</v>
-      </c>
+      <c r="AN69" s="9" t="n"/>
       <c r="AO69" s="9" t="n"/>
       <c r="AP69" s="9" t="n">
-        <v>0.409</v>
+        <v>0.6</v>
       </c>
       <c r="AQ69" s="9" t="n"/>
     </row>
@@ -17996,11 +18146,9 @@
       <c r="AM70" s="8" t="n"/>
       <c r="AN70" s="8" t="n"/>
       <c r="AO70" s="8" t="n"/>
-      <c r="AP70" s="8" t="n">
-        <v>0.44</v>
-      </c>
+      <c r="AP70" s="8" t="n"/>
       <c r="AQ70" s="8" t="n">
-        <v>0.16</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="71" ht="12" customHeight="1" s="19">
@@ -18050,7 +18198,7 @@
       <c r="AO71" s="9" t="n"/>
       <c r="AP71" s="9" t="n"/>
       <c r="AQ71" s="9" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="72" ht="12" customHeight="1" s="19">
@@ -18096,13 +18244,11 @@
       <c r="AK72" s="8" t="n"/>
       <c r="AL72" s="8" t="n"/>
       <c r="AM72" s="8" t="n"/>
-      <c r="AN72" s="8" t="n">
-        <v>0.261</v>
-      </c>
+      <c r="AN72" s="8" t="n"/>
       <c r="AO72" s="8" t="n"/>
       <c r="AP72" s="8" t="n"/>
       <c r="AQ72" s="8" t="n">
-        <v>0.328</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="73" ht="12" customHeight="1" s="19">
@@ -18148,13 +18294,11 @@
       <c r="AK73" s="9" t="n"/>
       <c r="AL73" s="9" t="n"/>
       <c r="AM73" s="9" t="n"/>
-      <c r="AN73" s="9" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="AN73" s="9" t="n"/>
       <c r="AO73" s="9" t="n"/>
       <c r="AP73" s="9" t="n"/>
       <c r="AQ73" s="9" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="74" ht="12" customHeight="1" s="19">
@@ -18200,13 +18344,11 @@
       <c r="AK74" s="8" t="n"/>
       <c r="AL74" s="8" t="n"/>
       <c r="AM74" s="8" t="n"/>
-      <c r="AN74" s="8" t="n">
-        <v>0.03</v>
-      </c>
+      <c r="AN74" s="8" t="n"/>
       <c r="AO74" s="8" t="n"/>
       <c r="AP74" s="8" t="n"/>
       <c r="AQ74" s="8" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="75" ht="12" customHeight="1" s="19">
@@ -18252,13 +18394,11 @@
       <c r="AK75" s="9" t="n"/>
       <c r="AL75" s="9" t="n"/>
       <c r="AM75" s="9" t="n"/>
-      <c r="AN75" s="9" t="n">
-        <v>0.189</v>
-      </c>
+      <c r="AN75" s="9" t="n"/>
       <c r="AO75" s="9" t="n"/>
       <c r="AP75" s="9" t="n"/>
       <c r="AQ75" s="9" t="n">
-        <v>0.411</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="76" ht="12" customHeight="1" s="19">
@@ -18304,13 +18444,11 @@
       <c r="AK76" s="8" t="n"/>
       <c r="AL76" s="8" t="n"/>
       <c r="AM76" s="8" t="n"/>
-      <c r="AN76" s="8" t="n">
-        <v>0.142</v>
-      </c>
+      <c r="AN76" s="8" t="n"/>
       <c r="AO76" s="8" t="n"/>
       <c r="AP76" s="8" t="n"/>
       <c r="AQ76" s="8" t="n">
-        <v>0.458</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="77" ht="12" customHeight="1" s="19">
@@ -18356,11 +18494,9 @@
       <c r="AK77" s="9" t="n"/>
       <c r="AL77" s="9" t="n"/>
       <c r="AM77" s="9" t="n"/>
-      <c r="AN77" s="9" t="n">
-        <v>0.062</v>
-      </c>
+      <c r="AN77" s="9" t="n"/>
       <c r="AO77" s="9" t="n">
-        <v>0.538</v>
+        <v>0.6</v>
       </c>
       <c r="AP77" s="9" t="n"/>
       <c r="AQ77" s="9" t="n"/>
@@ -18408,11 +18544,9 @@
       <c r="AK78" s="8" t="n"/>
       <c r="AL78" s="8" t="n"/>
       <c r="AM78" s="8" t="n"/>
-      <c r="AN78" s="8" t="n">
-        <v>0.013</v>
-      </c>
+      <c r="AN78" s="8" t="n"/>
       <c r="AO78" s="8" t="n">
-        <v>0.411</v>
+        <v>0.6</v>
       </c>
       <c r="AP78" s="8" t="n"/>
       <c r="AQ78" s="8" t="n"/>
@@ -18460,11 +18594,9 @@
       <c r="AK79" s="9" t="n"/>
       <c r="AL79" s="9" t="n"/>
       <c r="AM79" s="9" t="n"/>
-      <c r="AN79" s="9" t="n">
-        <v>0.076</v>
-      </c>
+      <c r="AN79" s="9" t="n"/>
       <c r="AO79" s="9" t="n">
-        <v>0.524</v>
+        <v>0.6</v>
       </c>
       <c r="AP79" s="9" t="n"/>
       <c r="AQ79" s="9" t="n"/>
@@ -18500,12 +18632,12 @@
       <c r="Y80" s="8" t="n"/>
       <c r="Z80" s="8" t="n"/>
       <c r="AA80" s="8" t="n"/>
-      <c r="AB80" s="8" t="n"/>
+      <c r="AB80" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AC80" s="8" t="n"/>
       <c r="AD80" s="8" t="n"/>
-      <c r="AE80" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AE80" s="8" t="n"/>
       <c r="AF80" s="8" t="n"/>
       <c r="AG80" s="8" t="n"/>
       <c r="AH80" s="8" t="n"/>
@@ -18541,9 +18673,7 @@
       <c r="P81" s="9" t="n"/>
       <c r="Q81" s="9" t="n"/>
       <c r="R81" s="9" t="n"/>
-      <c r="S81" s="9" t="n">
-        <v>0.027</v>
-      </c>
+      <c r="S81" s="9" t="n"/>
       <c r="T81" s="9" t="n"/>
       <c r="U81" s="9" t="n"/>
       <c r="V81" s="9" t="n"/>
@@ -18557,7 +18687,7 @@
       <c r="AD81" s="9" t="n"/>
       <c r="AE81" s="9" t="n"/>
       <c r="AF81" s="9" t="n">
-        <v>0.573</v>
+        <v>0.6</v>
       </c>
       <c r="AG81" s="9" t="n"/>
       <c r="AH81" s="9" t="n"/>
@@ -18598,14 +18728,14 @@
       <c r="U82" s="8" t="n"/>
       <c r="V82" s="8" t="n"/>
       <c r="W82" s="8" t="n"/>
-      <c r="X82" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="X82" s="8" t="n"/>
       <c r="Y82" s="8" t="n"/>
       <c r="Z82" s="8" t="n"/>
       <c r="AA82" s="8" t="n"/>
       <c r="AB82" s="8" t="n"/>
-      <c r="AC82" s="8" t="n"/>
+      <c r="AC82" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AD82" s="8" t="n"/>
       <c r="AE82" s="8" t="n"/>
       <c r="AF82" s="8" t="n"/>
@@ -19043,18 +19173,22 @@
         </is>
       </c>
       <c r="C2" s="8" t="n"/>
-      <c r="D2" s="8" t="n"/>
+      <c r="D2" s="8" t="n">
+        <v>38.038</v>
+      </c>
       <c r="E2" s="8" t="n"/>
       <c r="F2" s="8" t="n"/>
       <c r="G2" s="8" t="n"/>
       <c r="H2" s="8" t="n"/>
       <c r="I2" s="8" t="n">
-        <v>80</v>
+        <v>35.824</v>
       </c>
       <c r="J2" s="8" t="n"/>
       <c r="K2" s="8" t="n"/>
       <c r="L2" s="8" t="n"/>
-      <c r="M2" s="8" t="n"/>
+      <c r="M2" s="8" t="n">
+        <v>6.138</v>
+      </c>
       <c r="N2" s="8" t="n"/>
       <c r="O2" s="8" t="n"/>
       <c r="P2" s="8" t="n"/>
@@ -19147,13 +19281,15 @@
       <c r="C4" s="8" t="n"/>
       <c r="D4" s="8" t="n"/>
       <c r="E4" s="8" t="n"/>
-      <c r="F4" s="8" t="n"/>
+      <c r="F4" s="8" t="n">
+        <v>11.517</v>
+      </c>
       <c r="G4" s="8" t="n"/>
       <c r="H4" s="8" t="n"/>
       <c r="I4" s="8" t="n"/>
       <c r="J4" s="8" t="n"/>
       <c r="K4" s="8" t="n">
-        <v>35</v>
+        <v>23.483</v>
       </c>
       <c r="L4" s="8" t="n"/>
       <c r="M4" s="8" t="n"/>
@@ -19198,11 +19334,11 @@
       <c r="C5" s="9" t="n"/>
       <c r="D5" s="9" t="n"/>
       <c r="E5" s="9" t="n"/>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="9" t="n"/>
+      <c r="G5" s="9" t="n"/>
+      <c r="H5" s="9" t="n">
         <v>72</v>
       </c>
-      <c r="G5" s="9" t="n"/>
-      <c r="H5" s="9" t="n"/>
       <c r="I5" s="9" t="n"/>
       <c r="J5" s="9" t="n"/>
       <c r="K5" s="9" t="n"/>
@@ -19298,15 +19434,17 @@
         </is>
       </c>
       <c r="C7" s="9" t="n"/>
-      <c r="D7" s="9" t="n"/>
+      <c r="D7" s="9" t="n">
+        <v>8.492000000000001</v>
+      </c>
       <c r="E7" s="9" t="n"/>
       <c r="F7" s="9" t="n"/>
       <c r="G7" s="9" t="n"/>
-      <c r="H7" s="9" t="n">
-        <v>55</v>
-      </c>
+      <c r="H7" s="9" t="n"/>
       <c r="I7" s="9" t="n"/>
-      <c r="J7" s="9" t="n"/>
+      <c r="J7" s="9" t="n">
+        <v>46.508</v>
+      </c>
       <c r="K7" s="9" t="n"/>
       <c r="L7" s="9" t="n"/>
       <c r="M7" s="9" t="n"/>
@@ -19350,15 +19488,19 @@
       </c>
       <c r="C8" s="8" t="n"/>
       <c r="D8" s="8" t="n">
-        <v>60</v>
+        <v>21.657</v>
       </c>
       <c r="E8" s="8" t="n"/>
       <c r="F8" s="8" t="n"/>
       <c r="G8" s="8" t="n"/>
       <c r="H8" s="8" t="n"/>
       <c r="I8" s="8" t="n"/>
-      <c r="J8" s="8" t="n"/>
-      <c r="K8" s="8" t="n"/>
+      <c r="J8" s="8" t="n">
+        <v>21.006</v>
+      </c>
+      <c r="K8" s="8" t="n">
+        <v>17.337</v>
+      </c>
       <c r="L8" s="8" t="n"/>
       <c r="M8" s="8" t="n"/>
       <c r="N8" s="8" t="n"/>
@@ -19511,12 +19653,12 @@
       <c r="J11" s="9" t="n"/>
       <c r="K11" s="9" t="n"/>
       <c r="L11" s="9" t="n">
-        <v>25</v>
+        <v>15.873</v>
       </c>
       <c r="M11" s="9" t="n"/>
       <c r="N11" s="9" t="n"/>
       <c r="O11" s="9" t="n">
-        <v>3</v>
+        <v>12.127</v>
       </c>
       <c r="P11" s="9" t="n"/>
       <c r="Q11" s="9" t="n"/>
@@ -19559,7 +19701,7 @@
       <c r="E12" s="8" t="n"/>
       <c r="F12" s="8" t="n"/>
       <c r="G12" s="8" t="n">
-        <v>25</v>
+        <v>24.228</v>
       </c>
       <c r="H12" s="8" t="n"/>
       <c r="I12" s="8" t="n"/>
@@ -19708,19 +19850,23 @@
         </is>
       </c>
       <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
+      <c r="D15" s="9" t="n">
+        <v>19.804</v>
+      </c>
       <c r="E15" s="9" t="n"/>
       <c r="F15" s="9" t="n"/>
       <c r="G15" s="9" t="n"/>
       <c r="H15" s="9" t="n">
-        <v>37.421</v>
+        <v>10.761</v>
       </c>
       <c r="I15" s="9" t="n"/>
       <c r="J15" s="9" t="n"/>
       <c r="K15" s="9" t="n"/>
-      <c r="L15" s="9" t="n"/>
+      <c r="L15" s="9" t="n">
+        <v>4.818</v>
+      </c>
       <c r="M15" s="9" t="n">
-        <v>6.579</v>
+        <v>8.617000000000001</v>
       </c>
       <c r="N15" s="9" t="n"/>
       <c r="O15" s="9" t="n"/>
@@ -19817,17 +19963,15 @@
       <c r="F17" s="9" t="n"/>
       <c r="G17" s="9" t="n"/>
       <c r="H17" s="9" t="n"/>
-      <c r="I17" s="9" t="n"/>
-      <c r="J17" s="9" t="n">
-        <v>22.895</v>
-      </c>
+      <c r="I17" s="9" t="n">
+        <v>25</v>
+      </c>
+      <c r="J17" s="9" t="n"/>
       <c r="K17" s="9" t="n"/>
       <c r="L17" s="9" t="n"/>
       <c r="M17" s="9" t="n"/>
       <c r="N17" s="9" t="n"/>
-      <c r="O17" s="9" t="n">
-        <v>2.105</v>
-      </c>
+      <c r="O17" s="9" t="n"/>
       <c r="P17" s="9" t="n"/>
       <c r="Q17" s="9" t="n"/>
       <c r="R17" s="9" t="n"/>
@@ -19871,15 +20015,19 @@
       <c r="G18" s="8" t="n"/>
       <c r="H18" s="8" t="n"/>
       <c r="I18" s="8" t="n"/>
-      <c r="J18" s="8" t="n">
-        <v>60</v>
-      </c>
-      <c r="K18" s="8" t="n"/>
+      <c r="J18" s="8" t="n"/>
+      <c r="K18" s="8" t="n">
+        <v>7.292</v>
+      </c>
       <c r="L18" s="8" t="n"/>
       <c r="M18" s="8" t="n"/>
-      <c r="N18" s="8" t="n"/>
+      <c r="N18" s="8" t="n">
+        <v>11.698</v>
+      </c>
       <c r="O18" s="8" t="n"/>
-      <c r="P18" s="8" t="n"/>
+      <c r="P18" s="8" t="n">
+        <v>41.009</v>
+      </c>
       <c r="Q18" s="8" t="n"/>
       <c r="R18" s="8" t="n"/>
       <c r="S18" s="8" t="n"/>
@@ -19916,7 +20064,7 @@
         </is>
       </c>
       <c r="C19" s="9" t="n">
-        <v>45</v>
+        <v>41.569</v>
       </c>
       <c r="D19" s="9" t="n"/>
       <c r="E19" s="9" t="n"/>
@@ -19971,20 +20119,18 @@
       <c r="E20" s="8" t="n"/>
       <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
-      <c r="H20" s="8" t="n"/>
+      <c r="H20" s="8" t="n">
+        <v>35</v>
+      </c>
       <c r="I20" s="8" t="n"/>
       <c r="J20" s="8" t="n"/>
       <c r="K20" s="8" t="n"/>
       <c r="L20" s="8" t="n"/>
-      <c r="M20" s="8" t="n">
-        <v>7.707</v>
-      </c>
+      <c r="M20" s="8" t="n"/>
       <c r="N20" s="8" t="n"/>
       <c r="O20" s="8" t="n"/>
       <c r="P20" s="8" t="n"/>
-      <c r="Q20" s="8" t="n">
-        <v>20</v>
-      </c>
+      <c r="Q20" s="8" t="n"/>
       <c r="R20" s="8" t="n"/>
       <c r="S20" s="8" t="n"/>
       <c r="T20" s="8" t="n"/>
@@ -20025,15 +20171,15 @@
       <c r="F21" s="9" t="n"/>
       <c r="G21" s="9" t="n"/>
       <c r="H21" s="9" t="n"/>
-      <c r="I21" s="9" t="n"/>
+      <c r="I21" s="9" t="n">
+        <v>20</v>
+      </c>
       <c r="J21" s="9" t="n"/>
       <c r="K21" s="9" t="n"/>
       <c r="L21" s="9" t="n"/>
       <c r="M21" s="9" t="n"/>
       <c r="N21" s="9" t="n"/>
-      <c r="O21" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="O21" s="9" t="n"/>
       <c r="P21" s="9" t="n"/>
       <c r="Q21" s="9" t="n"/>
       <c r="R21" s="9" t="n"/>
@@ -20071,7 +20217,7 @@
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>15</v>
+        <v>8.914999999999999</v>
       </c>
       <c r="D22" s="8" t="n"/>
       <c r="E22" s="8" t="n"/>
@@ -20081,7 +20227,9 @@
       <c r="I22" s="8" t="n"/>
       <c r="J22" s="8" t="n"/>
       <c r="K22" s="8" t="n"/>
-      <c r="L22" s="8" t="n"/>
+      <c r="L22" s="8" t="n">
+        <v>6.085</v>
+      </c>
       <c r="M22" s="8" t="n"/>
       <c r="N22" s="8" t="n"/>
       <c r="O22" s="8" t="n"/>
@@ -20121,15 +20269,15 @@
           <t>C2</t>
         </is>
       </c>
-      <c r="C23" s="9" t="n">
-        <v>13</v>
-      </c>
+      <c r="C23" s="9" t="n"/>
       <c r="D23" s="9" t="n"/>
       <c r="E23" s="9" t="n"/>
       <c r="F23" s="9" t="n"/>
       <c r="G23" s="9" t="n"/>
       <c r="H23" s="9" t="n"/>
-      <c r="I23" s="9" t="n"/>
+      <c r="I23" s="9" t="n">
+        <v>13</v>
+      </c>
       <c r="J23" s="9" t="n"/>
       <c r="K23" s="9" t="n"/>
       <c r="L23" s="9" t="n"/>
@@ -20180,13 +20328,13 @@
       <c r="H24" s="8" t="n"/>
       <c r="I24" s="8" t="n"/>
       <c r="J24" s="8" t="n"/>
-      <c r="K24" s="8" t="n">
-        <v>15</v>
-      </c>
+      <c r="K24" s="8" t="n"/>
       <c r="L24" s="8" t="n"/>
       <c r="M24" s="8" t="n"/>
       <c r="N24" s="8" t="n"/>
-      <c r="O24" s="8" t="n"/>
+      <c r="O24" s="8" t="n">
+        <v>2.51</v>
+      </c>
       <c r="P24" s="8" t="n"/>
       <c r="Q24" s="8" t="n"/>
       <c r="R24" s="8" t="n"/>
@@ -20223,14 +20371,14 @@
           <t>C4</t>
         </is>
       </c>
-      <c r="C25" s="9" t="n"/>
+      <c r="C25" s="9" t="n">
+        <v>12.263</v>
+      </c>
       <c r="D25" s="9" t="n"/>
       <c r="E25" s="9" t="n"/>
       <c r="F25" s="9" t="n"/>
       <c r="G25" s="9" t="n"/>
-      <c r="H25" s="9" t="n">
-        <v>18</v>
-      </c>
+      <c r="H25" s="9" t="n"/>
       <c r="I25" s="9" t="n"/>
       <c r="J25" s="9" t="n"/>
       <c r="K25" s="9" t="n"/>
@@ -20275,7 +20423,7 @@
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>27</v>
+        <v>25.018</v>
       </c>
       <c r="D26" s="8" t="n"/>
       <c r="E26" s="8" t="n"/>
@@ -20326,14 +20474,18 @@
         </is>
       </c>
       <c r="C27" s="9" t="n">
-        <v>20</v>
+        <v>11.301</v>
       </c>
       <c r="D27" s="9" t="n"/>
       <c r="E27" s="9" t="n"/>
       <c r="F27" s="9" t="n"/>
       <c r="G27" s="9" t="n"/>
-      <c r="H27" s="9" t="n"/>
-      <c r="I27" s="9" t="n"/>
+      <c r="H27" s="9" t="n">
+        <v>3.675</v>
+      </c>
+      <c r="I27" s="9" t="n">
+        <v>5.024</v>
+      </c>
       <c r="J27" s="9" t="n"/>
       <c r="K27" s="9" t="n"/>
       <c r="L27" s="9" t="n"/>
@@ -20397,11 +20549,13 @@
       <c r="U28" s="8" t="n"/>
       <c r="V28" s="8" t="n"/>
       <c r="W28" s="8" t="n">
-        <v>15</v>
+        <v>14.862</v>
       </c>
       <c r="X28" s="8" t="n"/>
       <c r="Y28" s="8" t="n"/>
-      <c r="Z28" s="8" t="n"/>
+      <c r="Z28" s="8" t="n">
+        <v>0.138</v>
+      </c>
       <c r="AA28" s="8" t="n"/>
       <c r="AB28" s="8" t="n"/>
       <c r="AC28" s="8" t="n"/>
@@ -20455,7 +20609,7 @@
       <c r="AB29" s="9" t="n"/>
       <c r="AC29" s="9" t="n"/>
       <c r="AD29" s="9" t="n">
-        <v>10</v>
+        <v>9.257999999999999</v>
       </c>
       <c r="AE29" s="9" t="n"/>
       <c r="AF29" s="9" t="n"/>
@@ -20494,12 +20648,12 @@
       <c r="P30" s="8" t="n"/>
       <c r="Q30" s="8" t="n"/>
       <c r="R30" s="8" t="n"/>
-      <c r="S30" s="8" t="n">
-        <v>14</v>
-      </c>
+      <c r="S30" s="8" t="n"/>
       <c r="T30" s="8" t="n"/>
       <c r="U30" s="8" t="n"/>
-      <c r="V30" s="8" t="n"/>
+      <c r="V30" s="8" t="n">
+        <v>11.162</v>
+      </c>
       <c r="W30" s="8" t="n"/>
       <c r="X30" s="8" t="n"/>
       <c r="Y30" s="8" t="n"/>
@@ -20547,7 +20701,7 @@
       <c r="R31" s="9" t="n"/>
       <c r="S31" s="9" t="n"/>
       <c r="T31" s="9" t="n">
-        <v>6</v>
+        <v>5.762</v>
       </c>
       <c r="U31" s="9" t="n"/>
       <c r="V31" s="9" t="n"/>
@@ -20598,11 +20752,11 @@
       <c r="R32" s="8" t="n"/>
       <c r="S32" s="8" t="n"/>
       <c r="T32" s="8" t="n">
-        <v>7.44</v>
+        <v>7.986</v>
       </c>
       <c r="U32" s="8" t="n"/>
       <c r="V32" s="8" t="n">
-        <v>2.56</v>
+        <v>1.046</v>
       </c>
       <c r="W32" s="8" t="n"/>
       <c r="X32" s="8" t="n"/>
@@ -20611,7 +20765,9 @@
       <c r="AA32" s="8" t="n"/>
       <c r="AB32" s="8" t="n"/>
       <c r="AC32" s="8" t="n"/>
-      <c r="AD32" s="8" t="n"/>
+      <c r="AD32" s="8" t="n">
+        <v>0.968</v>
+      </c>
       <c r="AE32" s="8" t="n"/>
       <c r="AF32" s="8" t="n"/>
       <c r="AG32" s="8" t="n"/>
@@ -20652,16 +20808,20 @@
       <c r="S33" s="9" t="n"/>
       <c r="T33" s="9" t="n"/>
       <c r="U33" s="9" t="n">
-        <v>2.16</v>
+        <v>2.367</v>
       </c>
       <c r="V33" s="9" t="n">
-        <v>4.12</v>
+        <v>6.315</v>
       </c>
       <c r="W33" s="9" t="n"/>
       <c r="X33" s="9" t="n"/>
       <c r="Y33" s="9" t="n"/>
-      <c r="Z33" s="9" t="n"/>
-      <c r="AA33" s="9" t="n"/>
+      <c r="Z33" s="9" t="n">
+        <v>1.892</v>
+      </c>
+      <c r="AA33" s="9" t="n">
+        <v>1.425</v>
+      </c>
       <c r="AB33" s="9" t="n"/>
       <c r="AC33" s="9" t="n"/>
       <c r="AD33" s="9" t="n"/>
@@ -20752,27 +20912,39 @@
       <c r="O35" s="9" t="n"/>
       <c r="P35" s="9" t="n"/>
       <c r="Q35" s="9" t="n"/>
-      <c r="R35" s="9" t="n">
-        <v>20</v>
-      </c>
-      <c r="S35" s="9" t="n"/>
+      <c r="R35" s="9" t="n"/>
+      <c r="S35" s="9" t="n">
+        <v>7.272</v>
+      </c>
       <c r="T35" s="9" t="n"/>
       <c r="U35" s="9" t="n"/>
       <c r="V35" s="9" t="n"/>
       <c r="W35" s="9" t="n"/>
-      <c r="X35" s="9" t="n"/>
-      <c r="Y35" s="9" t="n"/>
+      <c r="X35" s="9" t="n">
+        <v>2.075</v>
+      </c>
+      <c r="Y35" s="9" t="n">
+        <v>2.483</v>
+      </c>
       <c r="Z35" s="9" t="n"/>
-      <c r="AA35" s="9" t="n"/>
-      <c r="AB35" s="9" t="n"/>
+      <c r="AA35" s="9" t="n">
+        <v>1.154</v>
+      </c>
+      <c r="AB35" s="9" t="n">
+        <v>1.824</v>
+      </c>
       <c r="AC35" s="9" t="n"/>
-      <c r="AD35" s="9" t="n"/>
+      <c r="AD35" s="9" t="n">
+        <v>0.507</v>
+      </c>
       <c r="AE35" s="9" t="n"/>
       <c r="AF35" s="9" t="n"/>
       <c r="AG35" s="9" t="n"/>
       <c r="AH35" s="9" t="n"/>
       <c r="AI35" s="9" t="n"/>
-      <c r="AJ35" s="9" t="n"/>
+      <c r="AJ35" s="9" t="n">
+        <v>4.685</v>
+      </c>
       <c r="AK35" s="9" t="n"/>
       <c r="AL35" s="9" t="n"/>
       <c r="AM35" s="9" t="n"/>
@@ -20809,16 +20981,16 @@
       <c r="U36" s="8" t="n"/>
       <c r="V36" s="8" t="n"/>
       <c r="W36" s="8" t="n"/>
-      <c r="X36" s="8" t="n"/>
+      <c r="X36" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y36" s="8" t="n"/>
       <c r="Z36" s="8" t="n"/>
       <c r="AA36" s="8" t="n"/>
       <c r="AB36" s="8" t="n"/>
       <c r="AC36" s="8" t="n"/>
       <c r="AD36" s="8" t="n"/>
-      <c r="AE36" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AE36" s="8" t="n"/>
       <c r="AF36" s="8" t="n"/>
       <c r="AG36" s="8" t="n"/>
       <c r="AH36" s="8" t="n"/>
@@ -20855,12 +21027,18 @@
       <c r="P37" s="9" t="n"/>
       <c r="Q37" s="9" t="n"/>
       <c r="R37" s="9" t="n"/>
-      <c r="S37" s="9" t="n"/>
+      <c r="S37" s="9" t="n">
+        <v>0.184</v>
+      </c>
       <c r="T37" s="9" t="n"/>
       <c r="U37" s="9" t="n"/>
       <c r="V37" s="9" t="n"/>
-      <c r="W37" s="9" t="n"/>
-      <c r="X37" s="9" t="n"/>
+      <c r="W37" s="9" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="X37" s="9" t="n">
+        <v>0.014</v>
+      </c>
       <c r="Y37" s="9" t="n"/>
       <c r="Z37" s="9" t="n"/>
       <c r="AA37" s="9" t="n"/>
@@ -20868,12 +21046,12 @@
       <c r="AC37" s="9" t="n"/>
       <c r="AD37" s="9" t="n"/>
       <c r="AE37" s="9" t="n">
-        <v>0.27</v>
+        <v>0.131</v>
       </c>
       <c r="AF37" s="9" t="n"/>
       <c r="AG37" s="9" t="n"/>
       <c r="AH37" s="9" t="n">
-        <v>0.3</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="AI37" s="9" t="n"/>
       <c r="AJ37" s="9" t="n"/>
@@ -21010,13 +21188,15 @@
       <c r="P40" s="8" t="n"/>
       <c r="Q40" s="8" t="n"/>
       <c r="R40" s="8" t="n"/>
-      <c r="S40" s="8" t="n"/>
+      <c r="S40" s="8" t="n">
+        <v>0.286</v>
+      </c>
       <c r="T40" s="8" t="n"/>
       <c r="U40" s="8" t="n"/>
       <c r="V40" s="8" t="n"/>
       <c r="W40" s="8" t="n"/>
       <c r="X40" s="8" t="n">
-        <v>0.6</v>
+        <v>0.264</v>
       </c>
       <c r="Y40" s="8" t="n"/>
       <c r="Z40" s="8" t="n"/>
@@ -21026,7 +21206,9 @@
       <c r="AD40" s="8" t="n"/>
       <c r="AE40" s="8" t="n"/>
       <c r="AF40" s="8" t="n"/>
-      <c r="AG40" s="8" t="n"/>
+      <c r="AG40" s="8" t="n">
+        <v>0.05</v>
+      </c>
       <c r="AH40" s="8" t="n"/>
       <c r="AI40" s="8" t="n"/>
       <c r="AJ40" s="8" t="n"/>
@@ -21061,13 +21243,17 @@
       <c r="P41" s="9" t="n"/>
       <c r="Q41" s="9" t="n"/>
       <c r="R41" s="9" t="n"/>
-      <c r="S41" s="9" t="n"/>
-      <c r="T41" s="9" t="n"/>
+      <c r="S41" s="9" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="T41" s="9" t="n">
+        <v>0.004</v>
+      </c>
       <c r="U41" s="9" t="n"/>
       <c r="V41" s="9" t="n"/>
       <c r="W41" s="9" t="n"/>
       <c r="X41" s="9" t="n">
-        <v>0.6</v>
+        <v>0.138</v>
       </c>
       <c r="Y41" s="9" t="n"/>
       <c r="Z41" s="9" t="n"/>
@@ -21076,7 +21262,9 @@
       <c r="AC41" s="9" t="n"/>
       <c r="AD41" s="9" t="n"/>
       <c r="AE41" s="9" t="n"/>
-      <c r="AF41" s="9" t="n"/>
+      <c r="AF41" s="9" t="n">
+        <v>0.229</v>
+      </c>
       <c r="AG41" s="9" t="n"/>
       <c r="AH41" s="9" t="n"/>
       <c r="AI41" s="9" t="n"/>
@@ -21214,13 +21402,15 @@
       <c r="P44" s="8" t="n"/>
       <c r="Q44" s="8" t="n"/>
       <c r="R44" s="8" t="n"/>
-      <c r="S44" s="8" t="n"/>
+      <c r="S44" s="8" t="n">
+        <v>0.301</v>
+      </c>
       <c r="T44" s="8" t="n"/>
       <c r="U44" s="8" t="n"/>
       <c r="V44" s="8" t="n"/>
       <c r="W44" s="8" t="n"/>
       <c r="X44" s="8" t="n">
-        <v>0.6</v>
+        <v>0.299</v>
       </c>
       <c r="Y44" s="8" t="n"/>
       <c r="Z44" s="8" t="n"/>
@@ -21367,19 +21557,23 @@
       <c r="P47" s="9" t="n"/>
       <c r="Q47" s="9" t="n"/>
       <c r="R47" s="9" t="n"/>
-      <c r="S47" s="9" t="n"/>
+      <c r="S47" s="9" t="n">
+        <v>0.448</v>
+      </c>
       <c r="T47" s="9" t="n"/>
       <c r="U47" s="9" t="n"/>
-      <c r="V47" s="9" t="n"/>
+      <c r="V47" s="9" t="n">
+        <v>0.032</v>
+      </c>
       <c r="W47" s="9" t="n"/>
-      <c r="X47" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="X47" s="9" t="n"/>
       <c r="Y47" s="9" t="n"/>
       <c r="Z47" s="9" t="n"/>
       <c r="AA47" s="9" t="n"/>
       <c r="AB47" s="9" t="n"/>
-      <c r="AC47" s="9" t="n"/>
+      <c r="AC47" s="9" t="n">
+        <v>0.12</v>
+      </c>
       <c r="AD47" s="9" t="n"/>
       <c r="AE47" s="9" t="n"/>
       <c r="AF47" s="9" t="n"/>
@@ -21419,10 +21613,12 @@
       <c r="Q48" s="8" t="n"/>
       <c r="R48" s="8" t="n"/>
       <c r="S48" s="8" t="n">
-        <v>0.6</v>
+        <v>0.336</v>
       </c>
       <c r="T48" s="8" t="n"/>
-      <c r="U48" s="8" t="n"/>
+      <c r="U48" s="8" t="n">
+        <v>0.014</v>
+      </c>
       <c r="V48" s="8" t="n"/>
       <c r="W48" s="8" t="n"/>
       <c r="X48" s="8" t="n"/>
@@ -21430,7 +21626,9 @@
       <c r="Z48" s="8" t="n"/>
       <c r="AA48" s="8" t="n"/>
       <c r="AB48" s="8" t="n"/>
-      <c r="AC48" s="8" t="n"/>
+      <c r="AC48" s="8" t="n">
+        <v>0.251</v>
+      </c>
       <c r="AD48" s="8" t="n"/>
       <c r="AE48" s="8" t="n"/>
       <c r="AF48" s="8" t="n"/>
@@ -21470,7 +21668,7 @@
       <c r="Q49" s="9" t="n"/>
       <c r="R49" s="9" t="n"/>
       <c r="S49" s="9" t="n">
-        <v>0.6</v>
+        <v>0.5639999999999999</v>
       </c>
       <c r="T49" s="9" t="n"/>
       <c r="U49" s="9" t="n"/>
@@ -21521,7 +21719,7 @@
       <c r="Q50" s="8" t="n"/>
       <c r="R50" s="8" t="n"/>
       <c r="S50" s="8" t="n">
-        <v>0.6</v>
+        <v>0.599</v>
       </c>
       <c r="T50" s="8" t="n"/>
       <c r="U50" s="8" t="n"/>
@@ -21572,7 +21770,7 @@
       <c r="Q51" s="9" t="n"/>
       <c r="R51" s="9" t="n"/>
       <c r="S51" s="9" t="n">
-        <v>0.6</v>
+        <v>0.423</v>
       </c>
       <c r="T51" s="9" t="n"/>
       <c r="U51" s="9" t="n"/>
@@ -21585,7 +21783,9 @@
       <c r="AB51" s="9" t="n"/>
       <c r="AC51" s="9" t="n"/>
       <c r="AD51" s="9" t="n"/>
-      <c r="AE51" s="9" t="n"/>
+      <c r="AE51" s="9" t="n">
+        <v>0.177</v>
+      </c>
       <c r="AF51" s="9" t="n"/>
       <c r="AG51" s="9" t="n"/>
       <c r="AH51" s="9" t="n"/>
@@ -21623,13 +21823,13 @@
       <c r="Q52" s="8" t="n"/>
       <c r="R52" s="8" t="n"/>
       <c r="S52" s="8" t="n"/>
-      <c r="T52" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="T52" s="8" t="n"/>
       <c r="U52" s="8" t="n"/>
       <c r="V52" s="8" t="n"/>
       <c r="W52" s="8" t="n"/>
-      <c r="X52" s="8" t="n"/>
+      <c r="X52" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y52" s="8" t="n"/>
       <c r="Z52" s="8" t="n"/>
       <c r="AA52" s="8" t="n"/>
@@ -21673,11 +21873,11 @@
       <c r="P53" s="9" t="n"/>
       <c r="Q53" s="9" t="n"/>
       <c r="R53" s="9" t="n"/>
-      <c r="S53" s="9" t="n"/>
+      <c r="S53" s="9" t="n">
+        <v>0.591</v>
+      </c>
       <c r="T53" s="9" t="n"/>
-      <c r="U53" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U53" s="9" t="n"/>
       <c r="V53" s="9" t="n"/>
       <c r="W53" s="9" t="n"/>
       <c r="X53" s="9" t="n"/>
@@ -21724,13 +21924,15 @@
       <c r="P54" s="8" t="n"/>
       <c r="Q54" s="8" t="n"/>
       <c r="R54" s="8" t="n"/>
-      <c r="S54" s="8" t="n"/>
-      <c r="T54" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S54" s="8" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="T54" s="8" t="n"/>
       <c r="U54" s="8" t="n"/>
       <c r="V54" s="8" t="n"/>
-      <c r="W54" s="8" t="n"/>
+      <c r="W54" s="8" t="n">
+        <v>0.229</v>
+      </c>
       <c r="X54" s="8" t="n"/>
       <c r="Y54" s="8" t="n"/>
       <c r="Z54" s="8" t="n"/>
@@ -21775,7 +21977,9 @@
       <c r="P55" s="9" t="n"/>
       <c r="Q55" s="9" t="n"/>
       <c r="R55" s="9" t="n"/>
-      <c r="S55" s="9" t="n"/>
+      <c r="S55" s="9" t="n">
+        <v>0.257</v>
+      </c>
       <c r="T55" s="9" t="n"/>
       <c r="U55" s="9" t="n"/>
       <c r="V55" s="9" t="n"/>
@@ -21786,13 +21990,13 @@
       <c r="AA55" s="9" t="n"/>
       <c r="AB55" s="9" t="n"/>
       <c r="AC55" s="9" t="n"/>
-      <c r="AD55" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AD55" s="9" t="n"/>
       <c r="AE55" s="9" t="n"/>
       <c r="AF55" s="9" t="n"/>
       <c r="AG55" s="9" t="n"/>
-      <c r="AH55" s="9" t="n"/>
+      <c r="AH55" s="9" t="n">
+        <v>0.102</v>
+      </c>
       <c r="AI55" s="9" t="n"/>
       <c r="AJ55" s="9" t="n"/>
       <c r="AK55" s="9" t="n"/>
@@ -21903,7 +22107,7 @@
       <c r="AJ57" s="9" t="n"/>
       <c r="AK57" s="9" t="n"/>
       <c r="AL57" s="9" t="n">
-        <v>10</v>
+        <v>7.977</v>
       </c>
       <c r="AM57" s="9" t="n"/>
       <c r="AN57" s="9" t="n"/>
@@ -21953,7 +22157,7 @@
       <c r="AJ58" s="8" t="n"/>
       <c r="AK58" s="8" t="n"/>
       <c r="AL58" s="8" t="n">
-        <v>14</v>
+        <v>11.136</v>
       </c>
       <c r="AM58" s="8" t="n"/>
       <c r="AN58" s="8" t="n"/>
@@ -22004,7 +22208,7 @@
       <c r="AK59" s="9" t="n"/>
       <c r="AL59" s="9" t="n"/>
       <c r="AM59" s="9" t="n">
-        <v>6</v>
+        <v>5.915</v>
       </c>
       <c r="AN59" s="9" t="n"/>
       <c r="AO59" s="9" t="n"/>
@@ -22052,7 +22256,7 @@
       <c r="AI60" s="8" t="n"/>
       <c r="AJ60" s="8" t="n"/>
       <c r="AK60" s="8" t="n">
-        <v>10</v>
+        <v>8.869</v>
       </c>
       <c r="AL60" s="8" t="n"/>
       <c r="AM60" s="8" t="n"/>
@@ -22102,7 +22306,7 @@
       <c r="AI61" s="9" t="n"/>
       <c r="AJ61" s="9" t="n"/>
       <c r="AK61" s="9" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AL61" s="9" t="n"/>
       <c r="AM61" s="9" t="n"/>
@@ -22200,7 +22404,9 @@
       <c r="AI63" s="9" t="n"/>
       <c r="AJ63" s="9" t="n"/>
       <c r="AK63" s="9" t="n"/>
-      <c r="AL63" s="9" t="n"/>
+      <c r="AL63" s="9" t="n">
+        <v>7.713</v>
+      </c>
       <c r="AM63" s="9" t="n"/>
       <c r="AN63" s="9" t="n"/>
       <c r="AO63" s="9" t="n"/>
@@ -22301,7 +22507,7 @@
       <c r="AL65" s="9" t="n"/>
       <c r="AM65" s="9" t="n"/>
       <c r="AN65" s="9" t="n">
-        <v>0.6</v>
+        <v>0.546</v>
       </c>
       <c r="AO65" s="9" t="n"/>
       <c r="AP65" s="9" t="n"/>
@@ -22453,9 +22659,11 @@
       <c r="AN68" s="8" t="n"/>
       <c r="AO68" s="8" t="n"/>
       <c r="AP68" s="8" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AQ68" s="8" t="n"/>
+        <v>0.439</v>
+      </c>
+      <c r="AQ68" s="8" t="n">
+        <v>0.065</v>
+      </c>
     </row>
     <row r="69" ht="12" customHeight="1" s="19">
       <c r="B69" s="10" t="inlineStr">
@@ -22500,10 +22708,12 @@
       <c r="AK69" s="9" t="n"/>
       <c r="AL69" s="9" t="n"/>
       <c r="AM69" s="9" t="n"/>
-      <c r="AN69" s="9" t="n"/>
+      <c r="AN69" s="9" t="n">
+        <v>0.168</v>
+      </c>
       <c r="AO69" s="9" t="n"/>
       <c r="AP69" s="9" t="n">
-        <v>0.6</v>
+        <v>0.432</v>
       </c>
       <c r="AQ69" s="9" t="n"/>
     </row>
@@ -22652,9 +22862,11 @@
       <c r="AM72" s="8" t="n"/>
       <c r="AN72" s="8" t="n"/>
       <c r="AO72" s="8" t="n"/>
-      <c r="AP72" s="8" t="n"/>
+      <c r="AP72" s="8" t="n">
+        <v>0.331</v>
+      </c>
       <c r="AQ72" s="8" t="n">
-        <v>0.6</v>
+        <v>0.269</v>
       </c>
     </row>
     <row r="73" ht="12" customHeight="1" s="19">
@@ -22804,7 +23016,7 @@
       <c r="AO75" s="9" t="n"/>
       <c r="AP75" s="9" t="n"/>
       <c r="AQ75" s="9" t="n">
-        <v>0.6</v>
+        <v>0.599</v>
       </c>
     </row>
     <row r="76" ht="12" customHeight="1" s="19">
@@ -22854,7 +23066,7 @@
       <c r="AO76" s="8" t="n"/>
       <c r="AP76" s="8" t="n"/>
       <c r="AQ76" s="8" t="n">
-        <v>0.6</v>
+        <v>0.597</v>
       </c>
     </row>
     <row r="77" ht="12" customHeight="1" s="19">
@@ -22900,9 +23112,11 @@
       <c r="AK77" s="9" t="n"/>
       <c r="AL77" s="9" t="n"/>
       <c r="AM77" s="9" t="n"/>
-      <c r="AN77" s="9" t="n"/>
+      <c r="AN77" s="9" t="n">
+        <v>0.066</v>
+      </c>
       <c r="AO77" s="9" t="n">
-        <v>0.6</v>
+        <v>0.534</v>
       </c>
       <c r="AP77" s="9" t="n"/>
       <c r="AQ77" s="9" t="n"/>
@@ -22952,7 +23166,7 @@
       <c r="AM78" s="8" t="n"/>
       <c r="AN78" s="8" t="n"/>
       <c r="AO78" s="8" t="n">
-        <v>0.6</v>
+        <v>0.556</v>
       </c>
       <c r="AP78" s="8" t="n"/>
       <c r="AQ78" s="8" t="n"/>
@@ -23000,9 +23214,11 @@
       <c r="AK79" s="9" t="n"/>
       <c r="AL79" s="9" t="n"/>
       <c r="AM79" s="9" t="n"/>
-      <c r="AN79" s="9" t="n"/>
+      <c r="AN79" s="9" t="n">
+        <v>0.048</v>
+      </c>
       <c r="AO79" s="9" t="n">
-        <v>0.6</v>
+        <v>0.552</v>
       </c>
       <c r="AP79" s="9" t="n"/>
       <c r="AQ79" s="9" t="n"/>
@@ -23038,12 +23254,12 @@
       <c r="Y80" s="8" t="n"/>
       <c r="Z80" s="8" t="n"/>
       <c r="AA80" s="8" t="n"/>
-      <c r="AB80" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AB80" s="8" t="n"/>
       <c r="AC80" s="8" t="n"/>
       <c r="AD80" s="8" t="n"/>
-      <c r="AE80" s="8" t="n"/>
+      <c r="AE80" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AF80" s="8" t="n"/>
       <c r="AG80" s="8" t="n"/>
       <c r="AH80" s="8" t="n"/>
@@ -23082,7 +23298,9 @@
       <c r="S81" s="9" t="n"/>
       <c r="T81" s="9" t="n"/>
       <c r="U81" s="9" t="n"/>
-      <c r="V81" s="9" t="n"/>
+      <c r="V81" s="9" t="n">
+        <v>0.047</v>
+      </c>
       <c r="W81" s="9" t="n"/>
       <c r="X81" s="9" t="n"/>
       <c r="Y81" s="9" t="n"/>
@@ -23093,7 +23311,7 @@
       <c r="AD81" s="9" t="n"/>
       <c r="AE81" s="9" t="n"/>
       <c r="AF81" s="9" t="n">
-        <v>0.6</v>
+        <v>0.553</v>
       </c>
       <c r="AG81" s="9" t="n"/>
       <c r="AH81" s="9" t="n"/>
@@ -23179,9 +23397,7 @@
       <c r="P83" s="9" t="n"/>
       <c r="Q83" s="9" t="n"/>
       <c r="R83" s="9" t="n"/>
-      <c r="S83" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S83" s="9" t="n"/>
       <c r="T83" s="9" t="n"/>
       <c r="U83" s="9" t="n"/>
       <c r="V83" s="9" t="n"/>
@@ -23192,7 +23408,9 @@
       <c r="AA83" s="9" t="n"/>
       <c r="AB83" s="9" t="n"/>
       <c r="AC83" s="9" t="n"/>
-      <c r="AD83" s="9" t="n"/>
+      <c r="AD83" s="9" t="n">
+        <v>0.58</v>
+      </c>
       <c r="AE83" s="9" t="n"/>
       <c r="AF83" s="9" t="n"/>
       <c r="AG83" s="9" t="n"/>
@@ -23581,11 +23799,11 @@
       <c r="C2" s="8" t="n"/>
       <c r="D2" s="8" t="n"/>
       <c r="E2" s="8" t="n"/>
-      <c r="F2" s="8" t="n">
+      <c r="F2" s="8" t="n"/>
+      <c r="G2" s="8" t="n"/>
+      <c r="H2" s="8" t="n">
         <v>80</v>
       </c>
-      <c r="G2" s="8" t="n"/>
-      <c r="H2" s="8" t="n"/>
       <c r="I2" s="8" t="n"/>
       <c r="J2" s="8" t="n"/>
       <c r="K2" s="8" t="n"/>
@@ -23638,13 +23856,13 @@
       <c r="I3" s="9" t="n"/>
       <c r="J3" s="9" t="n"/>
       <c r="K3" s="9" t="n">
-        <v>47.446</v>
+        <v>47.619</v>
       </c>
       <c r="L3" s="9" t="n"/>
       <c r="M3" s="9" t="n"/>
       <c r="N3" s="9" t="n"/>
       <c r="O3" s="9" t="n">
-        <v>2.126</v>
+        <v>7.381</v>
       </c>
       <c r="P3" s="9" t="n"/>
       <c r="Q3" s="9" t="n"/>
@@ -23682,17 +23900,15 @@
           <t>A3</t>
         </is>
       </c>
-      <c r="C4" s="8" t="n">
-        <v>1.529</v>
-      </c>
-      <c r="D4" s="8" t="n">
-        <v>33.471</v>
-      </c>
+      <c r="C4" s="8" t="n"/>
+      <c r="D4" s="8" t="n"/>
       <c r="E4" s="8" t="n"/>
       <c r="F4" s="8" t="n"/>
       <c r="G4" s="8" t="n"/>
       <c r="H4" s="8" t="n"/>
-      <c r="I4" s="8" t="n"/>
+      <c r="I4" s="8" t="n">
+        <v>35</v>
+      </c>
       <c r="J4" s="8" t="n"/>
       <c r="K4" s="8" t="n"/>
       <c r="L4" s="8" t="n"/>
@@ -23736,13 +23952,15 @@
         </is>
       </c>
       <c r="C5" s="9" t="n"/>
-      <c r="D5" s="9" t="n"/>
+      <c r="D5" s="9" t="n">
+        <v>36</v>
+      </c>
       <c r="E5" s="9" t="n"/>
       <c r="F5" s="9" t="n"/>
       <c r="G5" s="9" t="n"/>
       <c r="H5" s="9" t="n"/>
       <c r="I5" s="9" t="n">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="J5" s="9" t="n"/>
       <c r="K5" s="9" t="n"/>
@@ -23789,7 +24007,7 @@
       <c r="C6" s="8" t="n"/>
       <c r="D6" s="8" t="n"/>
       <c r="E6" s="8" t="n">
-        <v>47.005</v>
+        <v>56</v>
       </c>
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="n"/>
@@ -23799,7 +24017,7 @@
       <c r="K6" s="8" t="n"/>
       <c r="L6" s="8" t="n"/>
       <c r="M6" s="8" t="n">
-        <v>20.995</v>
+        <v>12</v>
       </c>
       <c r="N6" s="8" t="n"/>
       <c r="O6" s="8" t="n"/>
@@ -23941,15 +24159,15 @@
           <t>B2</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n">
-        <v>3.038</v>
-      </c>
-      <c r="D9" s="9" t="n"/>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="9" t="n">
+        <v>23</v>
+      </c>
       <c r="E9" s="9" t="n"/>
       <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="n"/>
       <c r="H9" s="9" t="n">
-        <v>42.962</v>
+        <v>23</v>
       </c>
       <c r="I9" s="9" t="n"/>
       <c r="J9" s="9" t="n"/>
@@ -23994,17 +24212,17 @@
           <t>B3</t>
         </is>
       </c>
-      <c r="C10" s="8" t="n">
-        <v>4.746</v>
-      </c>
-      <c r="D10" s="8" t="n"/>
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="8" t="n">
+        <v>20</v>
+      </c>
       <c r="E10" s="8" t="n"/>
       <c r="F10" s="8" t="n"/>
       <c r="G10" s="8" t="n"/>
       <c r="H10" s="8" t="n"/>
       <c r="I10" s="8" t="n"/>
       <c r="J10" s="8" t="n">
-        <v>35.254</v>
+        <v>20</v>
       </c>
       <c r="K10" s="8" t="n"/>
       <c r="L10" s="8" t="n"/>
@@ -24047,15 +24265,15 @@
           <t>B4</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n">
-        <v>2.147</v>
-      </c>
-      <c r="D11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n">
+        <v>14</v>
+      </c>
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="9" t="n"/>
       <c r="G11" s="9" t="n"/>
       <c r="H11" s="9" t="n">
-        <v>25.853</v>
+        <v>14</v>
       </c>
       <c r="I11" s="9" t="n"/>
       <c r="J11" s="9" t="n"/>
@@ -24110,7 +24328,7 @@
       <c r="J12" s="8" t="n"/>
       <c r="K12" s="8" t="n"/>
       <c r="L12" s="8" t="n">
-        <v>23.36</v>
+        <v>25</v>
       </c>
       <c r="M12" s="8" t="n"/>
       <c r="N12" s="8" t="n"/>
@@ -24156,11 +24374,11 @@
       <c r="E13" s="9" t="n"/>
       <c r="F13" s="9" t="n"/>
       <c r="G13" s="9" t="n"/>
-      <c r="H13" s="9" t="n">
+      <c r="H13" s="9" t="n"/>
+      <c r="I13" s="9" t="n"/>
+      <c r="J13" s="9" t="n">
         <v>86</v>
       </c>
-      <c r="I13" s="9" t="n"/>
-      <c r="J13" s="9" t="n"/>
       <c r="K13" s="9" t="n"/>
       <c r="L13" s="9" t="n"/>
       <c r="M13" s="9" t="n"/>
@@ -24253,9 +24471,7 @@
           <t>B8</t>
         </is>
       </c>
-      <c r="C15" s="9" t="n">
-        <v>2.026</v>
-      </c>
+      <c r="C15" s="9" t="n"/>
       <c r="D15" s="9" t="n"/>
       <c r="E15" s="9" t="n"/>
       <c r="F15" s="9" t="n"/>
@@ -24263,7 +24479,7 @@
       <c r="H15" s="9" t="n"/>
       <c r="I15" s="9" t="n"/>
       <c r="J15" s="9" t="n">
-        <v>41.974</v>
+        <v>44</v>
       </c>
       <c r="K15" s="9" t="n"/>
       <c r="L15" s="9" t="n"/>
@@ -24310,7 +24526,7 @@
       <c r="D16" s="8" t="n"/>
       <c r="E16" s="8" t="n"/>
       <c r="F16" s="8" t="n">
-        <v>31.594</v>
+        <v>45.121</v>
       </c>
       <c r="G16" s="8" t="n"/>
       <c r="H16" s="8" t="n"/>
@@ -24321,7 +24537,7 @@
       <c r="M16" s="8" t="n"/>
       <c r="N16" s="8" t="n"/>
       <c r="O16" s="8" t="n">
-        <v>10.843</v>
+        <v>4.879</v>
       </c>
       <c r="P16" s="8" t="n"/>
       <c r="Q16" s="8" t="n"/>
@@ -24364,7 +24580,7 @@
       <c r="E17" s="9" t="n"/>
       <c r="F17" s="9" t="n"/>
       <c r="G17" s="9" t="n">
-        <v>22.603</v>
+        <v>25</v>
       </c>
       <c r="H17" s="9" t="n"/>
       <c r="I17" s="9" t="n"/>
@@ -24468,15 +24684,17 @@
       <c r="G19" s="9" t="n"/>
       <c r="H19" s="9" t="n"/>
       <c r="I19" s="9" t="n"/>
-      <c r="J19" s="9" t="n">
-        <v>45</v>
-      </c>
+      <c r="J19" s="9" t="n"/>
       <c r="K19" s="9" t="n"/>
       <c r="L19" s="9" t="n"/>
       <c r="M19" s="9" t="n"/>
-      <c r="N19" s="9" t="n"/>
+      <c r="N19" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="O19" s="9" t="n"/>
-      <c r="P19" s="9" t="n"/>
+      <c r="P19" s="9" t="n">
+        <v>35</v>
+      </c>
       <c r="Q19" s="9" t="n"/>
       <c r="R19" s="9" t="n"/>
       <c r="S19" s="9" t="n"/>
@@ -24514,15 +24732,13 @@
       </c>
       <c r="C20" s="8" t="n"/>
       <c r="D20" s="8" t="n"/>
-      <c r="E20" s="8" t="n">
-        <v>6.809</v>
-      </c>
+      <c r="E20" s="8" t="n"/>
       <c r="F20" s="8" t="n"/>
       <c r="G20" s="8" t="n"/>
       <c r="H20" s="8" t="n"/>
       <c r="I20" s="8" t="n"/>
       <c r="J20" s="8" t="n">
-        <v>26.413</v>
+        <v>35</v>
       </c>
       <c r="K20" s="8" t="n"/>
       <c r="L20" s="8" t="n"/>
@@ -24570,11 +24786,11 @@
       <c r="E21" s="9" t="n"/>
       <c r="F21" s="9" t="n"/>
       <c r="G21" s="9" t="n"/>
-      <c r="H21" s="9" t="n"/>
+      <c r="H21" s="9" t="n">
+        <v>20</v>
+      </c>
       <c r="I21" s="9" t="n"/>
-      <c r="J21" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="J21" s="9" t="n"/>
       <c r="K21" s="9" t="n"/>
       <c r="L21" s="9" t="n"/>
       <c r="M21" s="9" t="n"/>
@@ -24622,15 +24838,19 @@
       <c r="F22" s="8" t="n"/>
       <c r="G22" s="8" t="n"/>
       <c r="H22" s="8" t="n">
-        <v>10.859</v>
-      </c>
-      <c r="I22" s="8" t="n"/>
+        <v>6.944</v>
+      </c>
+      <c r="I22" s="8" t="n">
+        <v>2.783</v>
+      </c>
       <c r="J22" s="8" t="n"/>
       <c r="K22" s="8" t="n"/>
       <c r="L22" s="8" t="n"/>
-      <c r="M22" s="8" t="n"/>
+      <c r="M22" s="8" t="n">
+        <v>1.8</v>
+      </c>
       <c r="N22" s="8" t="n">
-        <v>4.141</v>
+        <v>2.444</v>
       </c>
       <c r="O22" s="8" t="n"/>
       <c r="P22" s="8" t="n"/>
@@ -24670,9 +24890,7 @@
         </is>
       </c>
       <c r="C23" s="9" t="n"/>
-      <c r="D23" s="9" t="n">
-        <v>13</v>
-      </c>
+      <c r="D23" s="9" t="n"/>
       <c r="E23" s="9" t="n"/>
       <c r="F23" s="9" t="n"/>
       <c r="G23" s="9" t="n"/>
@@ -24683,7 +24901,9 @@
       <c r="L23" s="9" t="n"/>
       <c r="M23" s="9" t="n"/>
       <c r="N23" s="9" t="n"/>
-      <c r="O23" s="9" t="n"/>
+      <c r="O23" s="9" t="n">
+        <v>13</v>
+      </c>
       <c r="P23" s="9" t="n"/>
       <c r="Q23" s="9" t="n"/>
       <c r="R23" s="9" t="n"/>
@@ -24773,12 +24993,12 @@
       </c>
       <c r="C25" s="9" t="n"/>
       <c r="D25" s="9" t="n"/>
-      <c r="E25" s="9" t="n">
-        <v>18</v>
-      </c>
+      <c r="E25" s="9" t="n"/>
       <c r="F25" s="9" t="n"/>
       <c r="G25" s="9" t="n"/>
-      <c r="H25" s="9" t="n"/>
+      <c r="H25" s="9" t="n">
+        <v>18</v>
+      </c>
       <c r="I25" s="9" t="n"/>
       <c r="J25" s="9" t="n"/>
       <c r="K25" s="9" t="n"/>
@@ -24829,9 +25049,7 @@
       <c r="G26" s="8" t="n"/>
       <c r="H26" s="8" t="n"/>
       <c r="I26" s="8" t="n"/>
-      <c r="J26" s="8" t="n">
-        <v>27</v>
-      </c>
+      <c r="J26" s="8" t="n"/>
       <c r="K26" s="8" t="n"/>
       <c r="L26" s="8" t="n"/>
       <c r="M26" s="8" t="n"/>
@@ -24879,10 +25097,10 @@
       <c r="F27" s="9" t="n"/>
       <c r="G27" s="9" t="n"/>
       <c r="H27" s="9" t="n"/>
-      <c r="I27" s="9" t="n">
+      <c r="I27" s="9" t="n"/>
+      <c r="J27" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="J27" s="9" t="n"/>
       <c r="K27" s="9" t="n"/>
       <c r="L27" s="9" t="n"/>
       <c r="M27" s="9" t="n"/>
@@ -24941,7 +25159,7 @@
       <c r="Q28" s="8" t="n"/>
       <c r="R28" s="8" t="n"/>
       <c r="S28" s="8" t="n">
-        <v>5.205</v>
+        <v>4.587</v>
       </c>
       <c r="T28" s="8" t="n"/>
       <c r="U28" s="8" t="n"/>
@@ -24954,7 +25172,7 @@
       <c r="AB28" s="8" t="n"/>
       <c r="AC28" s="8" t="n"/>
       <c r="AD28" s="8" t="n">
-        <v>9.795</v>
+        <v>10.413</v>
       </c>
       <c r="AE28" s="8" t="n"/>
       <c r="AF28" s="8" t="n"/>
@@ -24994,12 +25212,12 @@
       <c r="Q29" s="9" t="n"/>
       <c r="R29" s="9" t="n"/>
       <c r="S29" s="9" t="n"/>
-      <c r="T29" s="9" t="n">
-        <v>10</v>
-      </c>
+      <c r="T29" s="9" t="n"/>
       <c r="U29" s="9" t="n"/>
       <c r="V29" s="9" t="n"/>
-      <c r="W29" s="9" t="n"/>
+      <c r="W29" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="X29" s="9" t="n"/>
       <c r="Y29" s="9" t="n"/>
       <c r="Z29" s="9" t="n"/>
@@ -25045,17 +25263,21 @@
       <c r="Q30" s="8" t="n"/>
       <c r="R30" s="8" t="n"/>
       <c r="S30" s="8" t="n"/>
-      <c r="T30" s="8" t="n"/>
+      <c r="T30" s="8" t="n">
+        <v>13.44</v>
+      </c>
       <c r="U30" s="8" t="n"/>
       <c r="V30" s="8" t="n"/>
       <c r="W30" s="8" t="n"/>
       <c r="X30" s="8" t="n">
-        <v>14</v>
+        <v>0.3</v>
       </c>
       <c r="Y30" s="8" t="n"/>
       <c r="Z30" s="8" t="n"/>
       <c r="AA30" s="8" t="n"/>
-      <c r="AB30" s="8" t="n"/>
+      <c r="AB30" s="8" t="n">
+        <v>0.26</v>
+      </c>
       <c r="AC30" s="8" t="n"/>
       <c r="AD30" s="8" t="n"/>
       <c r="AE30" s="8" t="n"/>
@@ -25148,17 +25370,23 @@
       <c r="R32" s="8" t="n"/>
       <c r="S32" s="8" t="n"/>
       <c r="T32" s="8" t="n"/>
-      <c r="U32" s="8" t="n"/>
+      <c r="U32" s="8" t="n">
+        <v>2.16</v>
+      </c>
       <c r="V32" s="8" t="n"/>
-      <c r="W32" s="8" t="n">
-        <v>10</v>
-      </c>
+      <c r="W32" s="8" t="n"/>
       <c r="X32" s="8" t="n"/>
       <c r="Y32" s="8" t="n"/>
-      <c r="Z32" s="8" t="n"/>
-      <c r="AA32" s="8" t="n"/>
+      <c r="Z32" s="8" t="n">
+        <v>1.088</v>
+      </c>
+      <c r="AA32" s="8" t="n">
+        <v>1.091</v>
+      </c>
       <c r="AB32" s="8" t="n"/>
-      <c r="AC32" s="8" t="n"/>
+      <c r="AC32" s="8" t="n">
+        <v>0.439</v>
+      </c>
       <c r="AD32" s="8" t="n"/>
       <c r="AE32" s="8" t="n"/>
       <c r="AF32" s="8" t="n"/>
@@ -25203,7 +25431,9 @@
       <c r="V33" s="9" t="n"/>
       <c r="W33" s="9" t="n"/>
       <c r="X33" s="9" t="n"/>
-      <c r="Y33" s="9" t="n"/>
+      <c r="Y33" s="9" t="n">
+        <v>0.333</v>
+      </c>
       <c r="Z33" s="9" t="n"/>
       <c r="AA33" s="9" t="n"/>
       <c r="AB33" s="9" t="n"/>
@@ -25212,11 +25442,15 @@
       <c r="AE33" s="9" t="n"/>
       <c r="AF33" s="9" t="n"/>
       <c r="AG33" s="9" t="n">
-        <v>6.681</v>
+        <v>0.75</v>
       </c>
       <c r="AH33" s="9" t="n"/>
-      <c r="AI33" s="9" t="n"/>
-      <c r="AJ33" s="9" t="n"/>
+      <c r="AI33" s="9" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AJ33" s="9" t="n">
+        <v>0.327</v>
+      </c>
       <c r="AK33" s="9" t="n"/>
       <c r="AL33" s="9" t="n"/>
       <c r="AM33" s="9" t="n"/>
@@ -25248,18 +25482,22 @@
       <c r="P34" s="8" t="n"/>
       <c r="Q34" s="8" t="n"/>
       <c r="R34" s="8" t="n"/>
-      <c r="S34" s="8" t="n"/>
-      <c r="T34" s="8" t="n">
-        <v>22</v>
-      </c>
+      <c r="S34" s="8" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="T34" s="8" t="n"/>
       <c r="U34" s="8" t="n"/>
-      <c r="V34" s="8" t="n"/>
+      <c r="V34" s="8" t="n">
+        <v>15</v>
+      </c>
       <c r="W34" s="8" t="n"/>
       <c r="X34" s="8" t="n"/>
       <c r="Y34" s="8" t="n"/>
       <c r="Z34" s="8" t="n"/>
       <c r="AA34" s="8" t="n"/>
-      <c r="AB34" s="8" t="n"/>
+      <c r="AB34" s="8" t="n">
+        <v>0.17</v>
+      </c>
       <c r="AC34" s="8" t="n"/>
       <c r="AD34" s="8" t="n"/>
       <c r="AE34" s="8" t="n"/>
@@ -25298,11 +25536,11 @@
       <c r="O35" s="9" t="n"/>
       <c r="P35" s="9" t="n"/>
       <c r="Q35" s="9" t="n"/>
-      <c r="R35" s="9" t="n"/>
+      <c r="R35" s="9" t="n">
+        <v>20</v>
+      </c>
       <c r="S35" s="9" t="n"/>
-      <c r="T35" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="T35" s="9" t="n"/>
       <c r="U35" s="9" t="n"/>
       <c r="V35" s="9" t="n"/>
       <c r="W35" s="9" t="n"/>
@@ -25401,9 +25639,7 @@
       <c r="P37" s="9" t="n"/>
       <c r="Q37" s="9" t="n"/>
       <c r="R37" s="9" t="n"/>
-      <c r="S37" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S37" s="9" t="n"/>
       <c r="T37" s="9" t="n"/>
       <c r="U37" s="9" t="n"/>
       <c r="V37" s="9" t="n"/>
@@ -25415,7 +25651,9 @@
       <c r="AB37" s="9" t="n"/>
       <c r="AC37" s="9" t="n"/>
       <c r="AD37" s="9" t="n"/>
-      <c r="AE37" s="9" t="n"/>
+      <c r="AE37" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AF37" s="9" t="n"/>
       <c r="AG37" s="9" t="n"/>
       <c r="AH37" s="9" t="n"/>
@@ -25453,16 +25691,16 @@
       <c r="Q38" s="8" t="n"/>
       <c r="R38" s="8" t="n"/>
       <c r="S38" s="8" t="n">
-        <v>0.034</v>
+        <v>0.3</v>
       </c>
       <c r="T38" s="8" t="n"/>
       <c r="U38" s="8" t="n"/>
       <c r="V38" s="8" t="n"/>
       <c r="W38" s="8" t="n"/>
-      <c r="X38" s="8" t="n"/>
-      <c r="Y38" s="8" t="n">
-        <v>0.5590000000000001</v>
-      </c>
+      <c r="X38" s="8" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="Y38" s="8" t="n"/>
       <c r="Z38" s="8" t="n"/>
       <c r="AA38" s="8" t="n"/>
       <c r="AB38" s="8" t="n"/>
@@ -25506,13 +25744,15 @@
       <c r="Q39" s="9" t="n"/>
       <c r="R39" s="9" t="n"/>
       <c r="S39" s="9" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="T39" s="9" t="n"/>
       <c r="U39" s="9" t="n"/>
       <c r="V39" s="9" t="n"/>
       <c r="W39" s="9" t="n"/>
-      <c r="X39" s="9" t="n"/>
+      <c r="X39" s="9" t="n">
+        <v>0.3</v>
+      </c>
       <c r="Y39" s="9" t="n"/>
       <c r="Z39" s="9" t="n"/>
       <c r="AA39" s="9" t="n"/>
@@ -25556,14 +25796,14 @@
       <c r="P40" s="8" t="n"/>
       <c r="Q40" s="8" t="n"/>
       <c r="R40" s="8" t="n"/>
-      <c r="S40" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S40" s="8" t="n"/>
       <c r="T40" s="8" t="n"/>
       <c r="U40" s="8" t="n"/>
       <c r="V40" s="8" t="n"/>
       <c r="W40" s="8" t="n"/>
-      <c r="X40" s="8" t="n"/>
+      <c r="X40" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y40" s="8" t="n"/>
       <c r="Z40" s="8" t="n"/>
       <c r="AA40" s="8" t="n"/>
@@ -25607,14 +25847,14 @@
       <c r="P41" s="9" t="n"/>
       <c r="Q41" s="9" t="n"/>
       <c r="R41" s="9" t="n"/>
-      <c r="S41" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S41" s="9" t="n"/>
       <c r="T41" s="9" t="n"/>
       <c r="U41" s="9" t="n"/>
       <c r="V41" s="9" t="n"/>
       <c r="W41" s="9" t="n"/>
-      <c r="X41" s="9" t="n"/>
+      <c r="X41" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y41" s="9" t="n"/>
       <c r="Z41" s="9" t="n"/>
       <c r="AA41" s="9" t="n"/>
@@ -25659,13 +25899,15 @@
       <c r="Q42" s="8" t="n"/>
       <c r="R42" s="8" t="n"/>
       <c r="S42" s="8" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="T42" s="8" t="n"/>
       <c r="U42" s="8" t="n"/>
       <c r="V42" s="8" t="n"/>
       <c r="W42" s="8" t="n"/>
-      <c r="X42" s="8" t="n"/>
+      <c r="X42" s="8" t="n">
+        <v>0.3</v>
+      </c>
       <c r="Y42" s="8" t="n"/>
       <c r="Z42" s="8" t="n"/>
       <c r="AA42" s="8" t="n"/>
@@ -25710,13 +25952,15 @@
       <c r="Q43" s="9" t="n"/>
       <c r="R43" s="9" t="n"/>
       <c r="S43" s="9" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="T43" s="9" t="n"/>
       <c r="U43" s="9" t="n"/>
       <c r="V43" s="9" t="n"/>
       <c r="W43" s="9" t="n"/>
-      <c r="X43" s="9" t="n"/>
+      <c r="X43" s="9" t="n">
+        <v>0.3</v>
+      </c>
       <c r="Y43" s="9" t="n"/>
       <c r="Z43" s="9" t="n"/>
       <c r="AA43" s="9" t="n"/>
@@ -25760,14 +26004,14 @@
       <c r="P44" s="8" t="n"/>
       <c r="Q44" s="8" t="n"/>
       <c r="R44" s="8" t="n"/>
-      <c r="S44" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S44" s="8" t="n"/>
       <c r="T44" s="8" t="n"/>
       <c r="U44" s="8" t="n"/>
       <c r="V44" s="8" t="n"/>
       <c r="W44" s="8" t="n"/>
-      <c r="X44" s="8" t="n"/>
+      <c r="X44" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y44" s="8" t="n"/>
       <c r="Z44" s="8" t="n"/>
       <c r="AA44" s="8" t="n"/>
@@ -25812,13 +26056,15 @@
       <c r="Q45" s="9" t="n"/>
       <c r="R45" s="9" t="n"/>
       <c r="S45" s="9" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="T45" s="9" t="n"/>
       <c r="U45" s="9" t="n"/>
       <c r="V45" s="9" t="n"/>
       <c r="W45" s="9" t="n"/>
-      <c r="X45" s="9" t="n"/>
+      <c r="X45" s="9" t="n">
+        <v>0.3</v>
+      </c>
       <c r="Y45" s="9" t="n"/>
       <c r="Z45" s="9" t="n"/>
       <c r="AA45" s="9" t="n"/>
@@ -25863,13 +26109,15 @@
       <c r="Q46" s="8" t="n"/>
       <c r="R46" s="8" t="n"/>
       <c r="S46" s="8" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="T46" s="8" t="n"/>
       <c r="U46" s="8" t="n"/>
       <c r="V46" s="8" t="n"/>
       <c r="W46" s="8" t="n"/>
-      <c r="X46" s="8" t="n"/>
+      <c r="X46" s="8" t="n">
+        <v>0.3</v>
+      </c>
       <c r="Y46" s="8" t="n"/>
       <c r="Z46" s="8" t="n"/>
       <c r="AA46" s="8" t="n"/>
@@ -25918,16 +26166,16 @@
       <c r="U47" s="9" t="n"/>
       <c r="V47" s="9" t="n"/>
       <c r="W47" s="9" t="n"/>
-      <c r="X47" s="9" t="n"/>
+      <c r="X47" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y47" s="9" t="n"/>
       <c r="Z47" s="9" t="n"/>
       <c r="AA47" s="9" t="n"/>
       <c r="AB47" s="9" t="n"/>
       <c r="AC47" s="9" t="n"/>
       <c r="AD47" s="9" t="n"/>
-      <c r="AE47" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AE47" s="9" t="n"/>
       <c r="AF47" s="9" t="n"/>
       <c r="AG47" s="9" t="n"/>
       <c r="AH47" s="9" t="n"/>
@@ -25969,13 +26217,13 @@
       <c r="U48" s="8" t="n"/>
       <c r="V48" s="8" t="n"/>
       <c r="W48" s="8" t="n"/>
-      <c r="X48" s="8" t="n"/>
+      <c r="X48" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y48" s="8" t="n"/>
       <c r="Z48" s="8" t="n"/>
       <c r="AA48" s="8" t="n"/>
-      <c r="AB48" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AB48" s="8" t="n"/>
       <c r="AC48" s="8" t="n"/>
       <c r="AD48" s="8" t="n"/>
       <c r="AE48" s="8" t="n"/>
@@ -26015,10 +26263,10 @@
       <c r="P49" s="9" t="n"/>
       <c r="Q49" s="9" t="n"/>
       <c r="R49" s="9" t="n"/>
-      <c r="S49" s="9" t="n"/>
-      <c r="T49" s="9" t="n">
-        <v>0.501</v>
-      </c>
+      <c r="S49" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T49" s="9" t="n"/>
       <c r="U49" s="9" t="n"/>
       <c r="V49" s="9" t="n"/>
       <c r="W49" s="9" t="n"/>
@@ -26066,10 +26314,10 @@
       <c r="P50" s="8" t="n"/>
       <c r="Q50" s="8" t="n"/>
       <c r="R50" s="8" t="n"/>
-      <c r="S50" s="8" t="n"/>
-      <c r="T50" s="8" t="n">
-        <v>0.53</v>
-      </c>
+      <c r="S50" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T50" s="8" t="n"/>
       <c r="U50" s="8" t="n"/>
       <c r="V50" s="8" t="n"/>
       <c r="W50" s="8" t="n"/>
@@ -26117,10 +26365,10 @@
       <c r="P51" s="9" t="n"/>
       <c r="Q51" s="9" t="n"/>
       <c r="R51" s="9" t="n"/>
-      <c r="S51" s="9" t="n"/>
-      <c r="T51" s="9" t="n">
-        <v>0.578</v>
-      </c>
+      <c r="S51" s="9" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="T51" s="9" t="n"/>
       <c r="U51" s="9" t="n"/>
       <c r="V51" s="9" t="n"/>
       <c r="W51" s="9" t="n"/>
@@ -26168,14 +26416,14 @@
       <c r="P52" s="8" t="n"/>
       <c r="Q52" s="8" t="n"/>
       <c r="R52" s="8" t="n"/>
-      <c r="S52" s="8" t="n"/>
+      <c r="S52" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T52" s="8" t="n"/>
       <c r="U52" s="8" t="n"/>
       <c r="V52" s="8" t="n"/>
       <c r="W52" s="8" t="n"/>
-      <c r="X52" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="X52" s="8" t="n"/>
       <c r="Y52" s="8" t="n"/>
       <c r="Z52" s="8" t="n"/>
       <c r="AA52" s="8" t="n"/>
@@ -26219,14 +26467,14 @@
       <c r="P53" s="9" t="n"/>
       <c r="Q53" s="9" t="n"/>
       <c r="R53" s="9" t="n"/>
-      <c r="S53" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="S53" s="9" t="n"/>
       <c r="T53" s="9" t="n"/>
       <c r="U53" s="9" t="n"/>
       <c r="V53" s="9" t="n"/>
       <c r="W53" s="9" t="n"/>
-      <c r="X53" s="9" t="n"/>
+      <c r="X53" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="Y53" s="9" t="n"/>
       <c r="Z53" s="9" t="n"/>
       <c r="AA53" s="9" t="n"/>
@@ -26271,7 +26519,7 @@
       <c r="Q54" s="8" t="n"/>
       <c r="R54" s="8" t="n"/>
       <c r="S54" s="8" t="n">
-        <v>0.5659999999999999</v>
+        <v>0.6</v>
       </c>
       <c r="T54" s="8" t="n"/>
       <c r="U54" s="8" t="n"/>
@@ -26321,11 +26569,11 @@
       <c r="P55" s="9" t="n"/>
       <c r="Q55" s="9" t="n"/>
       <c r="R55" s="9" t="n"/>
-      <c r="S55" s="9" t="n"/>
+      <c r="S55" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T55" s="9" t="n"/>
-      <c r="U55" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="U55" s="9" t="n"/>
       <c r="V55" s="9" t="n"/>
       <c r="W55" s="9" t="n"/>
       <c r="X55" s="9" t="n"/>
@@ -26399,7 +26647,7 @@
       <c r="AJ56" s="8" t="n"/>
       <c r="AK56" s="8" t="n"/>
       <c r="AL56" s="8" t="n">
-        <v>14.649</v>
+        <v>15</v>
       </c>
       <c r="AM56" s="8" t="n"/>
       <c r="AN56" s="8" t="n"/>
@@ -26650,7 +26898,7 @@
       <c r="AK61" s="9" t="n"/>
       <c r="AL61" s="9" t="n"/>
       <c r="AM61" s="9" t="n">
-        <v>11.308</v>
+        <v>12</v>
       </c>
       <c r="AN61" s="9" t="n"/>
       <c r="AO61" s="9" t="n"/>
@@ -26697,10 +26945,10 @@
       <c r="AH62" s="8" t="n"/>
       <c r="AI62" s="8" t="n"/>
       <c r="AJ62" s="8" t="n"/>
-      <c r="AK62" s="8" t="n"/>
-      <c r="AL62" s="8" t="n">
+      <c r="AK62" s="8" t="n">
         <v>22</v>
       </c>
+      <c r="AL62" s="8" t="n"/>
       <c r="AM62" s="8" t="n"/>
       <c r="AN62" s="8" t="n"/>
       <c r="AO62" s="8" t="n"/>
@@ -26747,9 +26995,7 @@
       <c r="AH63" s="9" t="n"/>
       <c r="AI63" s="9" t="n"/>
       <c r="AJ63" s="9" t="n"/>
-      <c r="AK63" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="AK63" s="9" t="n"/>
       <c r="AL63" s="9" t="n"/>
       <c r="AM63" s="9" t="n"/>
       <c r="AN63" s="9" t="n"/>
@@ -27452,7 +27698,7 @@
       <c r="AM77" s="9" t="n"/>
       <c r="AN77" s="9" t="n"/>
       <c r="AO77" s="9" t="n">
-        <v>0.5590000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AP77" s="9" t="n"/>
       <c r="AQ77" s="9" t="n"/>
@@ -27502,7 +27748,7 @@
       <c r="AM78" s="8" t="n"/>
       <c r="AN78" s="8" t="n"/>
       <c r="AO78" s="8" t="n">
-        <v>0.527</v>
+        <v>0.6</v>
       </c>
       <c r="AP78" s="8" t="n"/>
       <c r="AQ78" s="8" t="n"/>
@@ -27552,7 +27798,7 @@
       <c r="AM79" s="9" t="n"/>
       <c r="AN79" s="9" t="n"/>
       <c r="AO79" s="9" t="n">
-        <v>0.598</v>
+        <v>0.6</v>
       </c>
       <c r="AP79" s="9" t="n"/>
       <c r="AQ79" s="9" t="n"/>
@@ -27591,12 +27837,12 @@
       <c r="AB80" s="8" t="n"/>
       <c r="AC80" s="8" t="n"/>
       <c r="AD80" s="8" t="n"/>
-      <c r="AE80" s="8" t="n"/>
+      <c r="AE80" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AF80" s="8" t="n"/>
       <c r="AG80" s="8" t="n"/>
-      <c r="AH80" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AH80" s="8" t="n"/>
       <c r="AI80" s="8" t="n"/>
       <c r="AJ80" s="8" t="n"/>
       <c r="AK80" s="8" t="n"/>
@@ -27631,22 +27877,20 @@
       <c r="R81" s="9" t="n"/>
       <c r="S81" s="9" t="n"/>
       <c r="T81" s="9" t="n"/>
-      <c r="U81" s="9" t="n">
-        <v>0.037</v>
-      </c>
+      <c r="U81" s="9" t="n"/>
       <c r="V81" s="9" t="n"/>
       <c r="W81" s="9" t="n"/>
       <c r="X81" s="9" t="n"/>
       <c r="Y81" s="9" t="n"/>
       <c r="Z81" s="9" t="n"/>
       <c r="AA81" s="9" t="n"/>
-      <c r="AB81" s="9" t="n"/>
+      <c r="AB81" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AC81" s="9" t="n"/>
       <c r="AD81" s="9" t="n"/>
       <c r="AE81" s="9" t="n"/>
-      <c r="AF81" s="9" t="n">
-        <v>0.5629999999999999</v>
-      </c>
+      <c r="AF81" s="9" t="n"/>
       <c r="AG81" s="9" t="n"/>
       <c r="AH81" s="9" t="n"/>
       <c r="AI81" s="9" t="n"/>
@@ -27691,12 +27935,12 @@
       <c r="Z82" s="8" t="n"/>
       <c r="AA82" s="8" t="n"/>
       <c r="AB82" s="8" t="n"/>
-      <c r="AC82" s="8" t="n">
-        <v>0.573</v>
-      </c>
+      <c r="AC82" s="8" t="n"/>
       <c r="AD82" s="8" t="n"/>
       <c r="AE82" s="8" t="n"/>
-      <c r="AF82" s="8" t="n"/>
+      <c r="AF82" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="AG82" s="8" t="n"/>
       <c r="AH82" s="8" t="n"/>
       <c r="AI82" s="8" t="n"/>
@@ -27742,10 +27986,10 @@
       <c r="AA83" s="9" t="n"/>
       <c r="AB83" s="9" t="n"/>
       <c r="AC83" s="9" t="n"/>
-      <c r="AD83" s="9" t="n"/>
-      <c r="AE83" s="9" t="n">
+      <c r="AD83" s="9" t="n">
         <v>0.6</v>
       </c>
+      <c r="AE83" s="9" t="n"/>
       <c r="AF83" s="9" t="n"/>
       <c r="AG83" s="9" t="n"/>
       <c r="AH83" s="9" t="n"/>
@@ -28967,7 +29211,9 @@
       </c>
       <c r="L18" s="8" t="n"/>
       <c r="M18" s="8" t="n"/>
-      <c r="N18" s="8" t="n"/>
+      <c r="N18" s="8" t="n">
+        <v>11.75</v>
+      </c>
       <c r="O18" s="8" t="n"/>
       <c r="P18" s="8" t="n">
         <v>35</v>
@@ -29061,7 +29307,9 @@
       <c r="C20" s="8" t="n"/>
       <c r="D20" s="8" t="n"/>
       <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="n"/>
+      <c r="F20" s="8" t="n">
+        <v>7.293</v>
+      </c>
       <c r="G20" s="8" t="n"/>
       <c r="H20" s="8" t="n"/>
       <c r="I20" s="8" t="n"/>
@@ -29111,7 +29359,9 @@
           <t>B14</t>
         </is>
       </c>
-      <c r="C21" s="9" t="n"/>
+      <c r="C21" s="9" t="n">
+        <v>3.646</v>
+      </c>
       <c r="D21" s="9" t="n"/>
       <c r="E21" s="9" t="n"/>
       <c r="F21" s="9" t="n">
@@ -29215,7 +29465,9 @@
           <t>C2</t>
         </is>
       </c>
-      <c r="C23" s="9" t="n"/>
+      <c r="C23" s="9" t="n">
+        <v>13</v>
+      </c>
       <c r="D23" s="9" t="n"/>
       <c r="E23" s="9" t="n"/>
       <c r="F23" s="9" t="n"/>
@@ -29226,9 +29478,7 @@
       <c r="K23" s="9" t="n"/>
       <c r="L23" s="9" t="n"/>
       <c r="M23" s="9" t="n"/>
-      <c r="N23" s="9" t="n">
-        <v>13</v>
-      </c>
+      <c r="N23" s="9" t="n"/>
       <c r="O23" s="9" t="n"/>
       <c r="P23" s="9" t="n"/>
       <c r="Q23" s="9" t="n"/>
@@ -29282,7 +29532,9 @@
       <c r="N24" s="8" t="n">
         <v>0.597</v>
       </c>
-      <c r="O24" s="8" t="n"/>
+      <c r="O24" s="8" t="n">
+        <v>0.209</v>
+      </c>
       <c r="P24" s="8" t="n"/>
       <c r="Q24" s="8" t="n"/>
       <c r="R24" s="8" t="n"/>
@@ -29539,7 +29791,9 @@
       <c r="P29" s="9" t="n"/>
       <c r="Q29" s="9" t="n"/>
       <c r="R29" s="9" t="n"/>
-      <c r="S29" s="9" t="n"/>
+      <c r="S29" s="9" t="n">
+        <v>10</v>
+      </c>
       <c r="T29" s="9" t="n"/>
       <c r="U29" s="9" t="n"/>
       <c r="V29" s="9" t="n"/>
@@ -29550,9 +29804,7 @@
       <c r="AA29" s="9" t="n"/>
       <c r="AB29" s="9" t="n"/>
       <c r="AC29" s="9" t="n"/>
-      <c r="AD29" s="9" t="n">
-        <v>10</v>
-      </c>
+      <c r="AD29" s="9" t="n"/>
       <c r="AE29" s="9" t="n"/>
       <c r="AF29" s="9" t="n"/>
       <c r="AG29" s="9" t="n"/>
@@ -29590,9 +29842,7 @@
       <c r="P30" s="8" t="n"/>
       <c r="Q30" s="8" t="n"/>
       <c r="R30" s="8" t="n"/>
-      <c r="S30" s="8" t="n">
-        <v>14</v>
-      </c>
+      <c r="S30" s="8" t="n"/>
       <c r="T30" s="8" t="n"/>
       <c r="U30" s="8" t="n"/>
       <c r="V30" s="8" t="n"/>
@@ -29603,7 +29853,9 @@
       <c r="AA30" s="8" t="n"/>
       <c r="AB30" s="8" t="n"/>
       <c r="AC30" s="8" t="n"/>
-      <c r="AD30" s="8" t="n"/>
+      <c r="AD30" s="8" t="n">
+        <v>14</v>
+      </c>
       <c r="AE30" s="8" t="n"/>
       <c r="AF30" s="8" t="n"/>
       <c r="AG30" s="8" t="n"/>
@@ -29756,8 +30008,12 @@
       <c r="W33" s="9" t="n"/>
       <c r="X33" s="9" t="n"/>
       <c r="Y33" s="9" t="n"/>
-      <c r="Z33" s="9" t="n"/>
-      <c r="AA33" s="9" t="n"/>
+      <c r="Z33" s="9" t="n">
+        <v>1.088</v>
+      </c>
+      <c r="AA33" s="9" t="n">
+        <v>1.091</v>
+      </c>
       <c r="AB33" s="9" t="n"/>
       <c r="AC33" s="9" t="n"/>
       <c r="AD33" s="9" t="n"/>
@@ -29797,26 +30053,32 @@
       <c r="O34" s="8" t="n"/>
       <c r="P34" s="8" t="n"/>
       <c r="Q34" s="8" t="n"/>
-      <c r="R34" s="8" t="n">
-        <v>22</v>
-      </c>
+      <c r="R34" s="8" t="n"/>
       <c r="S34" s="8" t="n"/>
       <c r="T34" s="8" t="n"/>
       <c r="U34" s="8" t="n"/>
       <c r="V34" s="8" t="n"/>
       <c r="W34" s="8" t="n"/>
-      <c r="X34" s="8" t="n"/>
+      <c r="X34" s="8" t="n">
+        <v>0.3</v>
+      </c>
       <c r="Y34" s="8" t="n"/>
       <c r="Z34" s="8" t="n"/>
       <c r="AA34" s="8" t="n"/>
       <c r="AB34" s="8" t="n"/>
-      <c r="AC34" s="8" t="n"/>
+      <c r="AC34" s="8" t="n">
+        <v>0.439</v>
+      </c>
       <c r="AD34" s="8" t="n"/>
       <c r="AE34" s="8" t="n"/>
       <c r="AF34" s="8" t="n"/>
-      <c r="AG34" s="8" t="n"/>
+      <c r="AG34" s="8" t="n">
+        <v>0.75</v>
+      </c>
       <c r="AH34" s="8" t="n"/>
-      <c r="AI34" s="8" t="n"/>
+      <c r="AI34" s="8" t="n">
+        <v>0.36</v>
+      </c>
       <c r="AJ34" s="8" t="n"/>
       <c r="AK34" s="8" t="n"/>
       <c r="AL34" s="8" t="n"/>
@@ -29848,27 +30110,33 @@
       <c r="O35" s="9" t="n"/>
       <c r="P35" s="9" t="n"/>
       <c r="Q35" s="9" t="n"/>
-      <c r="R35" s="9" t="n">
-        <v>20</v>
-      </c>
+      <c r="R35" s="9" t="n"/>
       <c r="S35" s="9" t="n"/>
       <c r="T35" s="9" t="n"/>
       <c r="U35" s="9" t="n"/>
       <c r="V35" s="9" t="n"/>
       <c r="W35" s="9" t="n"/>
       <c r="X35" s="9" t="n"/>
-      <c r="Y35" s="9" t="n"/>
+      <c r="Y35" s="9" t="n">
+        <v>0.333</v>
+      </c>
       <c r="Z35" s="9" t="n"/>
       <c r="AA35" s="9" t="n"/>
-      <c r="AB35" s="9" t="n"/>
+      <c r="AB35" s="9" t="n">
+        <v>0.43</v>
+      </c>
       <c r="AC35" s="9" t="n"/>
-      <c r="AD35" s="9" t="n"/>
+      <c r="AD35" s="9" t="n">
+        <v>0.413</v>
+      </c>
       <c r="AE35" s="9" t="n"/>
       <c r="AF35" s="9" t="n"/>
       <c r="AG35" s="9" t="n"/>
       <c r="AH35" s="9" t="n"/>
       <c r="AI35" s="9" t="n"/>
-      <c r="AJ35" s="9" t="n"/>
+      <c r="AJ35" s="9" t="n">
+        <v>0.327</v>
+      </c>
       <c r="AK35" s="9" t="n"/>
       <c r="AL35" s="9" t="n"/>
       <c r="AM35" s="9" t="n"/>
@@ -29956,7 +30224,9 @@
       <c r="U37" s="9" t="n"/>
       <c r="V37" s="9" t="n"/>
       <c r="W37" s="9" t="n"/>
-      <c r="X37" s="9" t="n"/>
+      <c r="X37" s="9" t="n">
+        <v>0.03</v>
+      </c>
       <c r="Y37" s="9" t="n"/>
       <c r="Z37" s="9" t="n"/>
       <c r="AA37" s="9" t="n"/>
@@ -30514,14 +30784,14 @@
       <c r="P48" s="8" t="n"/>
       <c r="Q48" s="8" t="n"/>
       <c r="R48" s="8" t="n"/>
-      <c r="S48" s="8" t="n"/>
+      <c r="S48" s="8" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T48" s="8" t="n"/>
       <c r="U48" s="8" t="n"/>
       <c r="V48" s="8" t="n"/>
       <c r="W48" s="8" t="n"/>
-      <c r="X48" s="8" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="X48" s="8" t="n"/>
       <c r="Y48" s="8" t="n"/>
       <c r="Z48" s="8" t="n"/>
       <c r="AA48" s="8" t="n"/>
@@ -30718,10 +30988,10 @@
       <c r="P52" s="8" t="n"/>
       <c r="Q52" s="8" t="n"/>
       <c r="R52" s="8" t="n"/>
-      <c r="S52" s="8" t="n"/>
-      <c r="T52" s="8" t="n">
+      <c r="S52" s="8" t="n">
         <v>0.6</v>
       </c>
+      <c r="T52" s="8" t="n"/>
       <c r="U52" s="8" t="n"/>
       <c r="V52" s="8" t="n"/>
       <c r="W52" s="8" t="n"/>
@@ -30769,10 +31039,10 @@
       <c r="P53" s="9" t="n"/>
       <c r="Q53" s="9" t="n"/>
       <c r="R53" s="9" t="n"/>
-      <c r="S53" s="9" t="n"/>
-      <c r="T53" s="9" t="n">
+      <c r="S53" s="9" t="n">
         <v>0.6</v>
       </c>
+      <c r="T53" s="9" t="n"/>
       <c r="U53" s="9" t="n"/>
       <c r="V53" s="9" t="n"/>
       <c r="W53" s="9" t="n"/>
@@ -30820,10 +31090,10 @@
       <c r="P54" s="8" t="n"/>
       <c r="Q54" s="8" t="n"/>
       <c r="R54" s="8" t="n"/>
-      <c r="S54" s="8" t="n"/>
-      <c r="T54" s="8" t="n">
+      <c r="S54" s="8" t="n">
         <v>0.6</v>
       </c>
+      <c r="T54" s="8" t="n"/>
       <c r="U54" s="8" t="n"/>
       <c r="V54" s="8" t="n"/>
       <c r="W54" s="8" t="n"/>
@@ -30871,7 +31141,9 @@
       <c r="P55" s="9" t="n"/>
       <c r="Q55" s="9" t="n"/>
       <c r="R55" s="9" t="n"/>
-      <c r="S55" s="9" t="n"/>
+      <c r="S55" s="9" t="n">
+        <v>0.6</v>
+      </c>
       <c r="T55" s="9" t="n"/>
       <c r="U55" s="9" t="n"/>
       <c r="V55" s="9" t="n"/>
@@ -30882,9 +31154,7 @@
       <c r="AA55" s="9" t="n"/>
       <c r="AB55" s="9" t="n"/>
       <c r="AC55" s="9" t="n"/>
-      <c r="AD55" s="9" t="n">
-        <v>0.6</v>
-      </c>
+      <c r="AD55" s="9" t="n"/>
       <c r="AE55" s="9" t="n"/>
       <c r="AF55" s="9" t="n"/>
       <c r="AG55" s="9" t="n"/>
@@ -31249,7 +31519,9 @@
       <c r="AJ62" s="8" t="n"/>
       <c r="AK62" s="8" t="n"/>
       <c r="AL62" s="8" t="n"/>
-      <c r="AM62" s="8" t="n"/>
+      <c r="AM62" s="8" t="n">
+        <v>6</v>
+      </c>
       <c r="AN62" s="8" t="n"/>
       <c r="AO62" s="8" t="n"/>
       <c r="AP62" s="8" t="n"/>
@@ -31296,7 +31568,9 @@
       <c r="AI63" s="9" t="n"/>
       <c r="AJ63" s="9" t="n"/>
       <c r="AK63" s="9" t="n"/>
-      <c r="AL63" s="9" t="n"/>
+      <c r="AL63" s="9" t="n">
+        <v>1</v>
+      </c>
       <c r="AM63" s="9" t="n"/>
       <c r="AN63" s="9" t="n"/>
       <c r="AO63" s="9" t="n"/>
